--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2710E24-90EC-9547-8B43-25B5ADBFA9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D002743F-BD2A-264F-9B23-C72B8E4EAC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -140,12 +161,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2329,9 +2359,6 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2341,6 +2368,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2348,12 +2384,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12747,7 +12777,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12786,11 +12816,9 @@
     <v>Powered by Refinitiv</v>
     <v>370.86</v>
     <v>190.12</v>
-    <v>1.3321000000000001</v>
-    <v>2.5099999999999998</v>
-    <v>1.0125E-2</v>
-    <v>-1.41</v>
-    <v>-5.6310000000000006E-3</v>
+    <v>1.4041999999999999</v>
+    <v>3.87</v>
+    <v>1.5455000000000002E-2</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12798,36 +12826,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>250.71</v>
+    <v>262.14999999999998</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46234.91680143516</v>
+    <v>46237.707026214841</v>
     <v>4</v>
-    <v>241.23</v>
-    <v>99537975000</v>
+    <v>251.68</v>
+    <v>101076300000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>244.73</v>
-    <v>14.3302</v>
-    <v>247.9</v>
+    <v>258</v>
+    <v>14.5517</v>
     <v>250.41</v>
-    <v>249</v>
+    <v>254.28</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>5586806</v>
-    <v>6067664</v>
+    <v>2109755</v>
+    <v>6012751</v>
     <v>1997</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12839,30 +12881,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.14</v>
+    <v>47.47</v>
     <v>39.47</v>
-    <v>0.41</v>
-    <v>8.8710000000000004E-3</v>
+    <v>0.82</v>
+    <v>1.7585E-2</v>
     <v>US</v>
-    <v>46.86</v>
+    <v>47.47</v>
     <v>Index</v>
-    <v>7</v>
-    <v>46.51</v>
+    <v>10</v>
+    <v>46.82</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.69</v>
-    <v>46.22</v>
+    <v>46.84</v>
     <v>46.63</v>
+    <v>47.45</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12896,8 +12938,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12919,7 +12959,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12929,6 +12968,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12964,7 +13008,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12975,16 +13019,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13085,19 +13126,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13178,9 +13213,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13188,9 +13220,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13682,18 +13711,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="238" t="s">
+      <c r="B2" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="239"/>
-      <c r="E2" s="238" t="s">
+      <c r="C2" s="238"/>
+      <c r="E2" s="237" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="H2" s="238" t="s">
+      <c r="F2" s="238"/>
+      <c r="H2" s="237" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="239"/>
+      <c r="I2" s="238"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13708,7 +13737,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>99663.18</v>
+        <v>101203.44</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13716,7 +13745,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>329.21405366448226</v>
+        <v>313.64871490723368</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13732,7 +13761,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>100682.18</v>
+        <v>102222.44</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13740,7 +13769,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>442.07082695442529</v>
+        <v>434.35854482668265</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13749,7 +13778,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>250.41</v>
+        <v>254.28</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13771,16 +13800,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>249</v>
+      <c r="C6" s="210" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>14.325514874141879</v>
+        <v>14.546910755148744</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13788,7 +13817,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>323.96495462385826</v>
+        <v>318.30572668993443</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13797,14 +13826,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>2.5099999999999998</v>
+        <v>3.87</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>4.1092362489086431</v>
+        <v>4.1727430748472099</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13812,23 +13841,23 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>354.66037083977426</v>
+        <v>347.42615863504545</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.41</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>8.2066416102717171E-2</v>
+        <v>8.0817410949667323E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13836,7 +13865,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.4163187206572192</v>
+        <v>0.36631334998838072</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13845,30 +13874,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.0125E-2</v>
+        <v>1.5455000000000002E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>6.9805518948923756E-2</v>
+        <v>6.8743117822872415E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-5.6310000000000006E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>9.1508217979799564E-2</v>
+        <v>9.0115513860003174E-2</v>
       </c>
       <c r="H10" s="186" t="s">
         <v>408</v>
@@ -13916,7 +13945,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3321000000000001</v>
+        <v>1.4041999999999999</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13932,7 +13961,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>6067664</v>
+        <v>6012751</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13948,7 +13977,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0224437951909623E-2</v>
+        <v>-1.0068827699927986E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13961,10 +13990,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="240" t="s">
+      <c r="B17" s="239" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="240"/>
+      <c r="C17" s="239"/>
       <c r="E17" s="186" t="s">
         <v>302</v>
       </c>
@@ -14037,14 +14066,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="240" t="s">
+      <c r="B25" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="240"/>
-      <c r="E25" s="238" t="s">
+      <c r="C25" s="239"/>
+      <c r="E25" s="237" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="239"/>
+      <c r="F25" s="238"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14053,12 +14082,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="2">
+      <c r="E26" s="187" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.63</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14073,7 +14102,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.7450000000000006E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14093,15 +14122,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="240" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="237"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14120,24 +14149,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="237"/>
-      <c r="C39" s="237"/>
-      <c r="D39" s="237"/>
-      <c r="E39" s="237"/>
-      <c r="F39" s="237"/>
-      <c r="G39" s="237"/>
-      <c r="H39" s="237"/>
+      <c r="B39" s="240"/>
+      <c r="C39" s="240"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="240"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="237" t="s">
+      <c r="B42" s="240" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="237"/>
-      <c r="D42" s="237"/>
-      <c r="E42" s="237"/>
-      <c r="F42" s="237"/>
-      <c r="G42" s="237"/>
-      <c r="H42" s="237"/>
+      <c r="C42" s="240"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
+      <c r="G42" s="240"/>
+      <c r="H42" s="240"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14152,24 +14181,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="237"/>
-      <c r="C49" s="237"/>
-      <c r="D49" s="237"/>
-      <c r="E49" s="237"/>
-      <c r="F49" s="237"/>
-      <c r="G49" s="237"/>
-      <c r="H49" s="237"/>
+      <c r="B49" s="240"/>
+      <c r="C49" s="240"/>
+      <c r="D49" s="240"/>
+      <c r="E49" s="240"/>
+      <c r="F49" s="240"/>
+      <c r="G49" s="240"/>
+      <c r="H49" s="240"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="237" t="s">
+      <c r="B52" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="237"/>
-      <c r="D52" s="237"/>
-      <c r="E52" s="237"/>
-      <c r="F52" s="237"/>
-      <c r="G52" s="237"/>
-      <c r="H52" s="237"/>
+      <c r="C52" s="240"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
+      <c r="G52" s="240"/>
+      <c r="H52" s="240"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14195,28 +14224,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="237"/>
-      <c r="C59" s="237"/>
-      <c r="D59" s="237"/>
-      <c r="E59" s="237"/>
-      <c r="F59" s="237"/>
-      <c r="G59" s="237"/>
-      <c r="H59" s="237"/>
+      <c r="B59" s="240"/>
+      <c r="C59" s="240"/>
+      <c r="D59" s="240"/>
+      <c r="E59" s="240"/>
+      <c r="F59" s="240"/>
+      <c r="G59" s="240"/>
+      <c r="H59" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14286,36 +14315,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="237" t="s">
+      <c r="S2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
-      <c r="AA2" s="237" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15335,35 +15364,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="P2" s="237" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="237"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="237"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -17304,20 +17333,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -18710,6 +18739,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18717,12 +18752,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18760,20 +18789,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="S2" s="251"/>
       <c r="T2" s="251"/>
       <c r="U2" s="251"/>
@@ -19782,16 +19811,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19854,10 +19883,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19874,7 +19903,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>250.41</v>
+        <v>254.28</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19883,7 +19912,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>99663.18</v>
+        <v>101203.44</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19901,7 +19930,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.6630000000000005E-2</v>
+        <v>4.7450000000000006E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19910,7 +19939,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3321000000000001</v>
+        <v>1.4041999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19942,10 +19971,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="240" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="237"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19953,7 +19982,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.2506949135993112E-2</v>
+        <v>6.1614243098926602E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19962,7 +19991,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93749305086400692</v>
+        <v>0.9383857569010734</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19980,7 +20009,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1065745</v>
+        <v>0.110639</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19989,7 +20018,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10243125812999526</v>
+        <v>0.10630449961223361</v>
       </c>
     </row>
   </sheetData>
@@ -20034,20 +20063,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -20240,7 +20269,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>153577.73265625874</v>
+        <v>146685.34990049319</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20294,23 +20323,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7359.728739217433</v>
+        <v>7333.9618670219852</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7548.0901024180375</v>
+        <v>7495.3299483845831</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7602.5517194416525</v>
+        <v>7522.9799245950971</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7601.1330866992666</v>
+        <v>7495.2426298115024</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7621.8854082526814</v>
+        <v>7489.3928954466992</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20329,14 +20358,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>94312.804302434859</v>
+        <v>88514.28126781914</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="240" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="237"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20352,14 +20381,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10243125812999526</v>
+        <v>0.10630449961223361</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="240" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="237"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20367,7 +20396,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37733.389056029075</v>
+        <v>37336.90726525987</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20376,7 +20405,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>94312.804302434859</v>
+        <v>88514.28126781914</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20385,7 +20414,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>132046.19335846393</v>
+        <v>125851.18853307901</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20412,7 +20441,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>131027.19335846393</v>
+        <v>124832.188533079</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20430,7 +20459,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>329.21405366448226</v>
+        <v>313.64871490723368</v>
       </c>
     </row>
   </sheetData>
@@ -20473,20 +20502,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21418,10 +21447,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="240" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="237"/>
+      <c r="C37" s="240"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21439,7 +21468,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10243125812999526</v>
+        <v>0.10630449961223361</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21465,7 +21494,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>176963.18912786126</v>
+        <v>173893.70084101969</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21492,7 +21521,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>175944.18912786126</v>
+        <v>172874.70084101969</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21510,14 +21539,14 @@
       </c>
       <c r="C47" s="144">
         <f ca="1">C45/C46</f>
-        <v>442.07082695442529</v>
+        <v>434.35854482668265</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="237" t="s">
+      <c r="B49" s="240" t="s">
         <v>211</v>
       </c>
-      <c r="C49" s="237"/>
+      <c r="C49" s="240"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21573,10 +21602,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="237" t="s">
+      <c r="B57" s="240" t="s">
         <v>328</v>
       </c>
-      <c r="C57" s="237"/>
+      <c r="C57" s="240"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21593,7 +21622,7 @@
       </c>
       <c r="C59" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10243125812999526</v>
+        <v>0.10630449961223361</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21619,7 +21648,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>129957.05194029558</v>
+        <v>127704.67922259388</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21646,7 +21675,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>128938.05194029558</v>
+        <v>126685.6792225939</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21664,7 +21693,7 @@
       </c>
       <c r="C67" s="144">
         <f ca="1">C65/C66</f>
-        <v>323.96495462385826</v>
+        <v>318.30572668993443</v>
       </c>
     </row>
   </sheetData>
@@ -21716,10 +21745,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21728,7 +21757,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>329.21405366448226</v>
+        <v>313.64871490723368</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21737,7 +21766,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C47</f>
-        <v>442.07082695442529</v>
+        <v>434.35854482668265</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21755,7 +21784,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C67</f>
-        <v>323.96495462385826</v>
+        <v>318.30572668993443</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21764,7 +21793,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>354.66037083977426</v>
+        <v>347.42615863504545</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21773,7 +21802,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>250.41</v>
+        <v>254.28</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21782,7 +21811,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.4163187206572192</v>
+        <v>0.36631334998838072</v>
       </c>
     </row>
   </sheetData>
@@ -21838,20 +21867,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22214,10 +22243,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="240" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="237"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22318,20 +22347,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -22506,7 +22535,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>79798.974526803446</v>
+        <v>76217.693136308197</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22560,23 +22589,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9323.4688001019076</v>
+        <v>9290.8267507135461</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7526.8976372876359</v>
+        <v>7474.2856157896258</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6076.5139302645557</v>
+        <v>6012.9143471660591</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4905.6096314875604</v>
+        <v>4837.2701827150877</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3960.330895760128</v>
+        <v>3891.4877993585101</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22595,7 +22624,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>49004.923682044529</v>
+        <v>45992.011693247005</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22611,7 +22640,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>250.41</v>
+        <v>254.28</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22620,7 +22649,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>200.44910697725206</v>
+        <v>192.16029243464783</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22659,7 +22688,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10243125812999526</v>
+        <v>0.10630449961223361</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22677,7 +22706,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>99663.18</v>
+        <v>101203.44</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22704,7 +22733,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>100682.18</v>
+        <v>102222.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22720,7 +22749,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31792.82089490179</v>
+        <v>31506.784695742826</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22729,7 +22758,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>49004.923682044529</v>
+        <v>45992.011693247005</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22738,7 +22767,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>80797.744576946323</v>
+        <v>77498.796388989838</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22765,7 +22794,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>79778.744576946323</v>
+        <v>76479.796388989838</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22783,7 +22812,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>200.44910697725206</v>
+        <v>192.16029243464783</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -23230,17 +23259,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29754,7 +29783,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>250.41</v>
+        <v>254.28</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29825,7 +29854,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>250.41</v>
+        <v>254.28</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31131,7 +31160,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>14.325514874141879</v>
+        <v>14.546910755148744</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31168,7 +31197,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.1092362489086431</v>
+        <v>4.1727430748472099</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31229,7 +31258,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.6528199340163212</v>
+        <v>8.7865462753950343</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31290,7 +31319,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>99663.18</v>
+        <v>101203.44</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31351,7 +31380,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>100682.18</v>
+        <v>102222.44</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31388,7 +31417,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>3.9956417175966346</v>
+        <v>4.0567679974601161</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31425,7 +31454,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>11.076147414741474</v>
+        <v>11.24559295929593</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31560,7 +31589,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="94">AC153/AC157</f>
-        <v>12.185252475852792</v>
+        <v>12.37357134123976</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31597,7 +31626,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="94"/>
-        <v>12.404877922383085</v>
+        <v>12.594650703114789</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31634,7 +31663,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="97">AC157/AC153</f>
-        <v>8.2066416102717171E-2</v>
+        <v>8.0817410949667323E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31671,7 +31700,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>6.9805518948923756E-2</v>
+        <v>6.8743117822872415E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31745,7 +31774,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>9.1508217979799564E-2</v>
+        <v>9.0115513860003174E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31782,7 +31811,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.1508217979799564E-2</v>
+        <v>9.0115513860003174E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32285,7 +32314,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.0224437951909623E-2</v>
+        <v>-1.0068827699927986E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33546,15 +33575,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="E4" s="237" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33562,7 +33591,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>250.41</v>
+        <v>254.28</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33578,7 +33607,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>99663.18</v>
+        <v>101203.44</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33598,7 +33627,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>100682.18</v>
+        <v>102222.44</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33618,7 +33647,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>14.325514874141879</v>
+        <v>14.546910755148744</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -33638,7 +33667,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.1092362489086431</v>
+        <v>4.1727430748472099</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -33658,7 +33687,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>8.6528199340163212</v>
+        <v>8.7865462753950343</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33678,7 +33707,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.9956417175966346</v>
+        <v>4.0567679974601161</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33687,18 +33716,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>11.076147414741474</v>
+        <v>11.24559295929593</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="240" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="237"/>
-      <c r="E15" s="237" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="237"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33749,14 +33778,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="240" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="237"/>
-      <c r="E21" s="237" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="237"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33825,14 +33854,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="237" t="s">
+      <c r="B29" s="240" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="237"/>
-      <c r="E29" s="237" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="237"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33908,14 +33937,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="240" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="237"/>
-      <c r="E37" s="237" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="237"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33923,7 +33952,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>6.9805518948923756E-2</v>
+        <v>6.8743117822872415E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33939,7 +33968,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>8.2066416102717171E-2</v>
+        <v>8.0817410949667323E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -33971,7 +34000,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>9.1508217979799564E-2</v>
+        <v>9.0115513860003174E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33980,18 +34009,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>9.1508217979799564E-2</v>
+        <v>9.0115513860003174E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="237" t="s">
+      <c r="B45" s="240" t="s">
         <v>285</v>
       </c>
-      <c r="C45" s="237"/>
-      <c r="E45" s="237" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="237"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34024,18 +34053,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0224437951909623E-2</v>
+        <v>-1.0068827699927986E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="237" t="s">
+      <c r="B51" s="240" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="237"/>
-      <c r="E51" s="237" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>309</v>
       </c>
-      <c r="F51" s="237"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34203,7 +34232,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>250.41</v>
+        <v>254.28</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34232,7 +34261,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>99663.18</v>
+        <v>101203.44</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34261,7 +34290,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>100682.18</v>
+        <v>102222.44</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34290,7 +34319,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>14.325514874141879</v>
+        <v>14.546910755148744</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34319,7 +34348,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.1092362489086431</v>
+        <v>4.1727430748472099</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34348,7 +34377,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>8.6528199340163212</v>
+        <v>8.7865462753950343</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34377,7 +34406,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>3.9956417175966346</v>
+        <v>4.0567679974601161</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34406,7 +34435,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>11.076147414741474</v>
+        <v>11.24559295929593</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35179,7 +35208,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>6.9805518948923756E-2</v>
+        <v>6.8743117822872415E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35208,7 +35237,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>8.2066416102717171E-2</v>
+        <v>8.0817410949667323E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35266,7 +35295,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>9.1508217979799564E-2</v>
+        <v>9.0115513860003174E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35295,7 +35324,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>9.1508217979799564E-2</v>
+        <v>9.0115513860003174E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35531,7 +35560,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0224437951909623E-2</v>
+        <v>-1.0068827699927986E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36017,14 +36046,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>319</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>320</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36091,19 +36120,19 @@
       <c r="B7" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="241">
         <f>Statement!AA89</f>
         <v>3.4385745545482967E-2</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="242"/>
+      <c r="F7" s="241">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1268516941937681</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -36130,19 +36159,19 @@
       <c r="B9" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="241">
         <f>Statement!AA90</f>
         <v>7.6807228915662648E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="242"/>
+      <c r="F9" s="241">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1206896551724138</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="242"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -36169,19 +36198,19 @@
       <c r="B11" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="241">
         <f>Statement!AA91</f>
         <v>2.9473317056156263E-2</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="242"/>
+      <c r="F11" s="241">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12760267430754538</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="242"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -36208,19 +36237,19 @@
       <c r="B13" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="241">
         <f>Statement!AA95</f>
         <v>0.10524728588661038</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="242"/>
+      <c r="F13" s="241">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.172424824056302</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="242"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -36247,19 +36276,19 @@
       <c r="B15" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="241">
         <f>Statement!AA96</f>
         <v>-7.4441687344913146E-2</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="242"/>
+      <c r="F15" s="241">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.1166429587482217E-2</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -36286,19 +36315,19 @@
       <c r="B17" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="241">
         <f>Statement!AA98</f>
         <v>-9.3700370566437263E-2</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="242"/>
+      <c r="F17" s="241">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2418687167356593E-2</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="242"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -36325,22 +36354,22 @@
       <c r="B19" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="241">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.1897810218978103E-2</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="242"/>
+      <c r="F19" s="241">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.2937062937062943E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="242"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -36367,22 +36396,22 @@
       <c r="B21" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="241">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-7.6086956521739066E-2</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="242"/>
+      <c r="F21" s="241">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>7.8680203045685293E-2</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="242"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36430,22 +36459,22 @@
       <c r="B25" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="241">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5172636334301385E-2</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="242"/>
+      <c r="F25" s="241">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13738698812267328</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="242"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36472,22 +36501,22 @@
       <c r="B27" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="241">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-1.1111111111111112E-2</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="242"/>
+      <c r="F27" s="241">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="242"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36514,49 +36543,49 @@
       <c r="B29" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="241">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="242"/>
+      <c r="F29" s="241">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.21527777777777779</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D002743F-BD2A-264F-9B23-C72B8E4EAC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95344235-2317-3B4C-97A9-32F6251B646F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2359,6 +2329,9 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2368,15 +2341,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2384,6 +2348,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12777,7 +12747,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12816,9 +12786,11 @@
     <v>Powered by Refinitiv</v>
     <v>370.86</v>
     <v>190.12</v>
-    <v>1.4041999999999999</v>
-    <v>3.87</v>
-    <v>1.5455000000000002E-2</v>
+    <v>1.3960999999999999</v>
+    <v>-19.239999999999998</v>
+    <v>-6.7332000000000003E-2</v>
+    <v>0.42249999999999999</v>
+    <v>1.585E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12826,50 +12798,36 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>262.14999999999998</v>
+    <v>275.91000000000003</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46237.707026214841</v>
+    <v>46269.897377904686</v>
     <v>4</v>
-    <v>251.68</v>
-    <v>101076300000</v>
+    <v>263.93</v>
+    <v>105937725000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>258</v>
-    <v>14.5517</v>
-    <v>250.41</v>
-    <v>254.28</v>
+    <v>274.47000000000003</v>
+    <v>15.2515</v>
+    <v>285.75</v>
+    <v>266.51</v>
+    <v>266.9325</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>2109755</v>
-    <v>6012751</v>
+    <v>6586756</v>
+    <v>4304496</v>
     <v>1997</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12881,30 +12839,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.47</v>
+    <v>48.06</v>
     <v>39.47</v>
-    <v>0.82</v>
-    <v>1.7585E-2</v>
+    <v>-0.34</v>
+    <v>-7.0889999999999998E-3</v>
     <v>US</v>
-    <v>47.47</v>
+    <v>47.68</v>
     <v>Index</v>
-    <v>10</v>
-    <v>46.82</v>
+    <v>7</v>
+    <v>47.32</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.84</v>
-    <v>46.63</v>
-    <v>47.45</v>
+    <v>47.66</v>
+    <v>47.96</v>
+    <v>47.62</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12938,6 +12896,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12959,6 +12919,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12968,11 +12929,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13008,7 +12964,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13019,13 +12975,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13126,13 +13085,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13213,6 +13178,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13220,6 +13188,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13711,18 +13682,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="238" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="238"/>
-      <c r="E2" s="237" t="s">
+      <c r="C2" s="239"/>
+      <c r="E2" s="238" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="238"/>
-      <c r="H2" s="237" t="s">
+      <c r="F2" s="239"/>
+      <c r="H2" s="238" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="238"/>
+      <c r="I2" s="239"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13737,7 +13708,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>101203.44</v>
+        <v>106070.98</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13745,7 +13716,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>313.64871490723368</v>
+        <v>313.63279917500302</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13761,7 +13732,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>102222.44</v>
+        <v>107089.98</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13769,7 +13740,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>434.35854482668265</v>
+        <v>434.3503720484008</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13778,7 +13749,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>254.28</v>
+        <v>266.51</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13800,16 +13771,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="210" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>266.9325</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>14.546910755148744</v>
+        <v>15.246567505720826</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13817,7 +13788,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>318.30572668993443</v>
+        <v>318.29972955259109</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13826,14 +13797,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>3.87</v>
+        <v>-19.239999999999998</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>4.1727430748472099</v>
+        <v>4.3734377728391145</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13841,23 +13812,23 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>347.42615863504545</v>
+        <v>347.41863722308153</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.42249999999999999</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>8.0817410949667323E-2</v>
+        <v>7.7108743597919055E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13865,7 +13836,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.36631334998838072</v>
+        <v>0.3035857462124556</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13874,30 +13845,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.5455000000000002E-2</v>
+        <v>-6.7332000000000003E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>6.8743117822872415E-2</v>
+        <v>6.558853326329217E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>1.585E-3</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>9.0115513860003174E-2</v>
+        <v>8.5980161586137888E-2</v>
       </c>
       <c r="H10" s="186" t="s">
         <v>408</v>
@@ -13945,7 +13916,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4041999999999999</v>
+        <v>1.3960999999999999</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13961,7 +13932,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>6012751</v>
+        <v>4304496</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13977,7 +13948,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0068827699927986E-2</v>
+        <v>-9.6067746333634331E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13990,10 +13961,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="239" t="s">
+      <c r="B17" s="240" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="239"/>
+      <c r="C17" s="240"/>
       <c r="E17" s="186" t="s">
         <v>302</v>
       </c>
@@ -14066,14 +14037,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="239" t="s">
+      <c r="B25" s="240" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="239"/>
-      <c r="E25" s="237" t="s">
+      <c r="C25" s="240"/>
+      <c r="E25" s="238" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="238"/>
+      <c r="F25" s="239"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14082,12 +14053,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="5">
+      <c r="E26" s="187" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.45</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14102,7 +14073,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.7450000000000006E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14122,15 +14093,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="240" t="s">
+      <c r="B33" s="237" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="240"/>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14149,24 +14120,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="240"/>
-      <c r="C39" s="240"/>
-      <c r="D39" s="240"/>
-      <c r="E39" s="240"/>
-      <c r="F39" s="240"/>
-      <c r="G39" s="240"/>
-      <c r="H39" s="240"/>
+      <c r="B39" s="237"/>
+      <c r="C39" s="237"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="240" t="s">
+      <c r="B42" s="237" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="240"/>
-      <c r="D42" s="240"/>
-      <c r="E42" s="240"/>
-      <c r="F42" s="240"/>
-      <c r="G42" s="240"/>
-      <c r="H42" s="240"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14181,24 +14152,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="240"/>
-      <c r="C49" s="240"/>
-      <c r="D49" s="240"/>
-      <c r="E49" s="240"/>
-      <c r="F49" s="240"/>
-      <c r="G49" s="240"/>
-      <c r="H49" s="240"/>
+      <c r="B49" s="237"/>
+      <c r="C49" s="237"/>
+      <c r="D49" s="237"/>
+      <c r="E49" s="237"/>
+      <c r="F49" s="237"/>
+      <c r="G49" s="237"/>
+      <c r="H49" s="237"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="240" t="s">
+      <c r="B52" s="237" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="240"/>
-      <c r="D52" s="240"/>
-      <c r="E52" s="240"/>
-      <c r="F52" s="240"/>
-      <c r="G52" s="240"/>
-      <c r="H52" s="240"/>
+      <c r="C52" s="237"/>
+      <c r="D52" s="237"/>
+      <c r="E52" s="237"/>
+      <c r="F52" s="237"/>
+      <c r="G52" s="237"/>
+      <c r="H52" s="237"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14224,28 +14195,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="240"/>
-      <c r="C59" s="240"/>
-      <c r="D59" s="240"/>
-      <c r="E59" s="240"/>
-      <c r="F59" s="240"/>
-      <c r="G59" s="240"/>
-      <c r="H59" s="240"/>
+      <c r="B59" s="237"/>
+      <c r="C59" s="237"/>
+      <c r="D59" s="237"/>
+      <c r="E59" s="237"/>
+      <c r="F59" s="237"/>
+      <c r="G59" s="237"/>
+      <c r="H59" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14315,36 +14286,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="240" t="s">
+      <c r="S2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240" t="s">
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
+      <c r="AA2" s="237" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15364,35 +15335,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="P2" s="240" t="s">
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
+      <c r="P2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="240"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240" t="s">
+      <c r="Q2" s="237"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="237"/>
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -17333,20 +17304,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -18739,12 +18710,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18752,6 +18717,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18789,20 +18760,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="S2" s="251"/>
       <c r="T2" s="251"/>
       <c r="U2" s="251"/>
@@ -19811,16 +19782,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19883,10 +19854,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="237"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19903,7 +19874,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>254.28</v>
+        <v>266.51</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19912,7 +19883,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>101203.44</v>
+        <v>106070.98</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19930,7 +19901,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.7450000000000006E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19939,7 +19910,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4041999999999999</v>
+        <v>1.3960999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19971,10 +19942,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="237" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="240"/>
+      <c r="C15" s="237"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19982,7 +19953,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.1614243098926602E-2</v>
+        <v>5.8953486453296157E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19991,7 +19962,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9383857569010734</v>
+        <v>0.94104651354670388</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20009,7 +19980,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.110639</v>
+        <v>0.11044449999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20018,7 +19989,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10630449961223361</v>
+        <v>0.10630864763461223</v>
       </c>
     </row>
   </sheetData>
@@ -20063,20 +20034,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -20269,7 +20240,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>146685.34990049319</v>
+        <v>146678.30015367549</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20323,23 +20294,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7333.9618670219852</v>
+        <v>7333.9343688748686</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7495.3299483845831</v>
+        <v>7495.2737421203692</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7522.9799245950971</v>
+        <v>7522.8953043433812</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7495.2426298115024</v>
+        <v>7495.1302190141269</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7489.3928954466992</v>
+        <v>7489.2524918783101</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20358,14 +20329,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>88514.28126781914</v>
+        <v>88508.367945420148</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="240" t="s">
+      <c r="B13" s="237" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="240"/>
+      <c r="C13" s="237"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20381,14 +20352,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10630449961223361</v>
+        <v>0.10630864763461223</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="240" t="s">
+      <c r="B18" s="237" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="240"/>
+      <c r="C18" s="237"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20396,7 +20367,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37336.90726525987</v>
+        <v>37336.486126231059</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20405,7 +20376,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>88514.28126781914</v>
+        <v>88508.367945420148</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20414,7 +20385,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>125851.18853307901</v>
+        <v>125844.85407165121</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20441,7 +20412,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>124832.188533079</v>
+        <v>124825.85407165121</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20459,7 +20430,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>313.64871490723368</v>
+        <v>313.63279917500302</v>
       </c>
     </row>
   </sheetData>
@@ -20502,20 +20473,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21447,10 +21418,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="237" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="240"/>
+      <c r="C37" s="237"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21468,7 +21439,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10630449961223361</v>
+        <v>0.10630864763461223</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21494,7 +21465,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>173893.70084101969</v>
+        <v>173890.44807526353</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21521,7 +21492,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>172874.70084101969</v>
+        <v>172871.44807526353</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21539,14 +21510,14 @@
       </c>
       <c r="C47" s="144">
         <f ca="1">C45/C46</f>
-        <v>434.35854482668265</v>
+        <v>434.3503720484008</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="240" t="s">
+      <c r="B49" s="237" t="s">
         <v>211</v>
       </c>
-      <c r="C49" s="240"/>
+      <c r="C49" s="237"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21602,10 +21573,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="240" t="s">
+      <c r="B57" s="237" t="s">
         <v>328</v>
       </c>
-      <c r="C57" s="240"/>
+      <c r="C57" s="237"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21622,7 +21593,7 @@
       </c>
       <c r="C59" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10630449961223361</v>
+        <v>0.10630864763461223</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21648,7 +21619,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>127704.67922259388</v>
+        <v>127702.29236193126</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21675,7 +21646,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>126685.6792225939</v>
+        <v>126683.29236193126</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21693,7 +21664,7 @@
       </c>
       <c r="C67" s="144">
         <f ca="1">C65/C66</f>
-        <v>318.30572668993443</v>
+        <v>318.29972955259109</v>
       </c>
     </row>
   </sheetData>
@@ -21745,10 +21716,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="237"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21757,7 +21728,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>313.64871490723368</v>
+        <v>313.63279917500302</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21766,7 +21737,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C47</f>
-        <v>434.35854482668265</v>
+        <v>434.3503720484008</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21784,7 +21755,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C67</f>
-        <v>318.30572668993443</v>
+        <v>318.29972955259109</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21793,7 +21764,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>347.42615863504545</v>
+        <v>347.41863722308153</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21802,7 +21773,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>254.28</v>
+        <v>266.51</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21811,7 +21782,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.36631334998838072</v>
+        <v>0.3035857462124556</v>
       </c>
     </row>
   </sheetData>
@@ -21867,20 +21838,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22243,10 +22214,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="240" t="s">
+      <c r="B20" s="237" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="240"/>
+      <c r="C20" s="237"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22347,20 +22318,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="237" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -22535,7 +22506,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>76217.693136308197</v>
+        <v>76214.030088566855</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22589,23 +22560,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9290.8267507135461</v>
+        <v>9290.7919154464089</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7474.2856157896258</v>
+        <v>7474.2295673334502</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6012.9143471660591</v>
+        <v>6012.8467124879517</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4837.2701827150877</v>
+        <v>4837.197635177241</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3891.4877993585101</v>
+        <v>3891.4148456784183</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22624,7 +22595,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>45992.011693247005</v>
+        <v>45988.939131519968</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22640,7 +22611,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>254.28</v>
+        <v>266.51</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22649,7 +22620,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>192.16029243464783</v>
+        <v>192.15180856191816</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22688,7 +22659,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10630449961223361</v>
+        <v>0.10630864763461223</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22706,7 +22677,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>101203.44</v>
+        <v>106070.98</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22733,7 +22704,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>102222.44</v>
+        <v>107089.98</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22749,7 +22720,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31506.784695742826</v>
+        <v>31506.480676123465</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22758,7 +22729,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>45992.011693247005</v>
+        <v>45988.939131519968</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22767,7 +22738,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>77498.796388989838</v>
+        <v>77495.419807643426</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22794,7 +22765,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>76479.796388989838</v>
+        <v>76476.419807643426</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22812,7 +22783,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>192.16029243464783</v>
+        <v>192.15180856191816</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -23259,17 +23230,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29783,7 +29754,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>254.28</v>
+        <v>266.51</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29854,7 +29825,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>254.28</v>
+        <v>266.51</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31160,7 +31131,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>14.546910755148744</v>
+        <v>15.246567505720826</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31197,7 +31168,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.1727430748472099</v>
+        <v>4.3734377728391145</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31258,7 +31229,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.7865462753950343</v>
+        <v>9.209149157839903</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31319,7 +31290,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>101203.44</v>
+        <v>106070.98</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31380,7 +31351,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>102222.44</v>
+        <v>107089.98</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31417,7 +31388,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>4.0567679974601161</v>
+        <v>4.2499396777522023</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31454,7 +31425,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>11.24559295929593</v>
+        <v>11.781075907590759</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31589,7 +31560,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="94">AC153/AC157</f>
-        <v>12.37357134123976</v>
+        <v>12.968697884826996</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31626,7 +31597,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="94"/>
-        <v>12.594650703114789</v>
+        <v>13.194371919742363</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31663,7 +31634,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="97">AC157/AC153</f>
-        <v>8.0817410949667323E-2</v>
+        <v>7.7108743597919055E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31700,7 +31671,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>6.8743117822872415E-2</v>
+        <v>6.558853326329217E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31774,7 +31745,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>9.0115513860003174E-2</v>
+        <v>8.5980161586137888E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31811,7 +31782,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.0115513860003174E-2</v>
+        <v>8.5980161586137888E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32314,7 +32285,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.0068827699927986E-2</v>
+        <v>-9.6067746333634331E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33575,15 +33546,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="237" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="240"/>
-      <c r="E4" s="240" t="s">
+      <c r="C4" s="237"/>
+      <c r="E4" s="237" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33591,7 +33562,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>254.28</v>
+        <v>266.51</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33607,7 +33578,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>101203.44</v>
+        <v>106070.98</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33627,7 +33598,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>102222.44</v>
+        <v>107089.98</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33647,7 +33618,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>14.546910755148744</v>
+        <v>15.246567505720826</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -33667,7 +33638,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.1727430748472099</v>
+        <v>4.3734377728391145</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -33687,7 +33658,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>8.7865462753950343</v>
+        <v>9.209149157839903</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33707,7 +33678,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>4.0567679974601161</v>
+        <v>4.2499396777522023</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33716,18 +33687,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>11.24559295929593</v>
+        <v>11.781075907590759</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="237" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="240"/>
-      <c r="E15" s="240" t="s">
+      <c r="C15" s="237"/>
+      <c r="E15" s="237" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="240"/>
+      <c r="F15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33778,14 +33749,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="240" t="s">
+      <c r="B21" s="237" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="240"/>
-      <c r="E21" s="240" t="s">
+      <c r="C21" s="237"/>
+      <c r="E21" s="237" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="240"/>
+      <c r="F21" s="237"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33854,14 +33825,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="240" t="s">
+      <c r="B29" s="237" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="240"/>
-      <c r="E29" s="240" t="s">
+      <c r="C29" s="237"/>
+      <c r="E29" s="237" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="240"/>
+      <c r="F29" s="237"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33937,14 +33908,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="237" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="240"/>
-      <c r="E37" s="240" t="s">
+      <c r="C37" s="237"/>
+      <c r="E37" s="237" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="240"/>
+      <c r="F37" s="237"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33952,7 +33923,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>6.8743117822872415E-2</v>
+        <v>6.558853326329217E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33968,7 +33939,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>8.0817410949667323E-2</v>
+        <v>7.7108743597919055E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -34000,7 +33971,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>9.0115513860003174E-2</v>
+        <v>8.5980161586137888E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34009,18 +33980,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>9.0115513860003174E-2</v>
+        <v>8.5980161586137888E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="240" t="s">
+      <c r="B45" s="237" t="s">
         <v>285</v>
       </c>
-      <c r="C45" s="240"/>
-      <c r="E45" s="240" t="s">
+      <c r="C45" s="237"/>
+      <c r="E45" s="237" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="240"/>
+      <c r="F45" s="237"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34053,18 +34024,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0068827699927986E-2</v>
+        <v>-9.6067746333634331E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="240" t="s">
+      <c r="B51" s="237" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="240"/>
-      <c r="E51" s="240" t="s">
+      <c r="C51" s="237"/>
+      <c r="E51" s="237" t="s">
         <v>309</v>
       </c>
-      <c r="F51" s="240"/>
+      <c r="F51" s="237"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34232,7 +34203,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>254.28</v>
+        <v>266.51</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34261,7 +34232,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>101203.44</v>
+        <v>106070.98</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34290,7 +34261,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>102222.44</v>
+        <v>107089.98</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34319,7 +34290,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>14.546910755148744</v>
+        <v>15.246567505720826</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34348,7 +34319,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.1727430748472099</v>
+        <v>4.3734377728391145</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34377,7 +34348,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>8.7865462753950343</v>
+        <v>9.209149157839903</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34406,7 +34377,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>4.0567679974601161</v>
+        <v>4.2499396777522023</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34435,7 +34406,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>11.24559295929593</v>
+        <v>11.781075907590759</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35208,7 +35179,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>6.8743117822872415E-2</v>
+        <v>6.558853326329217E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35237,7 +35208,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>8.0817410949667323E-2</v>
+        <v>7.7108743597919055E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35295,7 +35266,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>9.0115513860003174E-2</v>
+        <v>8.5980161586137888E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35324,7 +35295,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>9.0115513860003174E-2</v>
+        <v>8.5980161586137888E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35560,7 +35531,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0068827699927986E-2</v>
+        <v>-9.6067746333634331E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36046,14 +36017,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="241" t="s">
         <v>319</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>320</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36120,19 +36091,19 @@
       <c r="B7" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C7" s="241">
+      <c r="C7" s="244">
         <f>Statement!AA89</f>
         <v>3.4385745545482967E-2</v>
       </c>
-      <c r="D7" s="242"/>
-      <c r="F7" s="241">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1268516941937681</v>
       </c>
-      <c r="G7" s="242"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -36159,19 +36130,19 @@
       <c r="B9" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="241">
+      <c r="C9" s="244">
         <f>Statement!AA90</f>
         <v>7.6807228915662648E-2</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="F9" s="241">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1206896551724138</v>
       </c>
-      <c r="G9" s="242"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -36198,19 +36169,19 @@
       <c r="B11" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C11" s="241">
+      <c r="C11" s="244">
         <f>Statement!AA91</f>
         <v>2.9473317056156263E-2</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="F11" s="241">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12760267430754538</v>
       </c>
-      <c r="G11" s="242"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -36237,19 +36208,19 @@
       <c r="B13" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="241">
+      <c r="C13" s="244">
         <f>Statement!AA95</f>
         <v>0.10524728588661038</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="F13" s="241">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.172424824056302</v>
       </c>
-      <c r="G13" s="242"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -36276,19 +36247,19 @@
       <c r="B15" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C15" s="241">
+      <c r="C15" s="244">
         <f>Statement!AA96</f>
         <v>-7.4441687344913146E-2</v>
       </c>
-      <c r="D15" s="242"/>
-      <c r="F15" s="241">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.1166429587482217E-2</v>
       </c>
-      <c r="G15" s="242"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -36315,19 +36286,19 @@
       <c r="B17" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C17" s="241">
+      <c r="C17" s="244">
         <f>Statement!AA98</f>
         <v>-9.3700370566437263E-2</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="F17" s="241">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2418687167356593E-2</v>
       </c>
-      <c r="G17" s="242"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -36354,22 +36325,22 @@
       <c r="B19" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C19" s="241">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.1897810218978103E-2</v>
       </c>
-      <c r="D19" s="242"/>
-      <c r="F19" s="241">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.2937062937062943E-2</v>
       </c>
-      <c r="G19" s="242"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -36396,22 +36367,22 @@
       <c r="B21" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C21" s="241">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-7.6086956521739066E-2</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="F21" s="241">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>7.8680203045685293E-2</v>
       </c>
-      <c r="G21" s="242"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36459,22 +36430,22 @@
       <c r="B25" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C25" s="241">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5172636334301385E-2</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="F25" s="241">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13738698812267328</v>
       </c>
-      <c r="G25" s="242"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36501,22 +36472,22 @@
       <c r="B27" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="241">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-1.1111111111111112E-2</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="F27" s="241">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="G27" s="242"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36543,49 +36514,49 @@
       <c r="B29" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C29" s="241">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D29" s="242"/>
-      <c r="F29" s="241">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.21527777777777779</v>
       </c>
-      <c r="G29" s="242"/>
+      <c r="G29" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95344235-2317-3B4C-97A9-32F6251B646F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11137C0-E273-104B-81D4-F2482BA85556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -140,12 +161,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2329,9 +2359,6 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2341,6 +2368,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2348,12 +2384,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12532,7 +12562,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -12747,7 +12777,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12784,13 +12814,11 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>370.86</v>
+    <v>368.73</v>
     <v>190.12</v>
-    <v>1.3960999999999999</v>
-    <v>-19.239999999999998</v>
-    <v>-6.7332000000000003E-2</v>
-    <v>0.42249999999999999</v>
-    <v>1.585E-3</v>
+    <v>1.3965000000000001</v>
+    <v>-10.595000000000001</v>
+    <v>-4.2462E-2</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12798,36 +12826,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>275.91000000000003</v>
+    <v>254.67</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46269.897377904686</v>
+    <v>46287.768830462497</v>
     <v>4</v>
-    <v>263.93</v>
-    <v>105937725000</v>
+    <v>238.595</v>
+    <v>94972687500</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>274.47000000000003</v>
-    <v>15.2515</v>
-    <v>285.75</v>
-    <v>266.51</v>
-    <v>266.9325</v>
+    <v>254.51</v>
+    <v>13.332599999999999</v>
+    <v>249.52</v>
+    <v>238.92500000000001</v>
     <v>397500000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>6586756</v>
-    <v>4304496</v>
+    <v>3880262</v>
+    <v>5274656</v>
     <v>1997</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12839,30 +12881,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>7</v>
-    <v>47.32</v>
+    <v>10</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
-    <v>47.62</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12896,8 +12938,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12919,7 +12959,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12929,6 +12968,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12964,7 +13008,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12975,16 +13019,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13085,19 +13126,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13178,9 +13213,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13188,9 +13220,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13682,18 +13711,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="238" t="s">
+      <c r="B2" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="239"/>
-      <c r="E2" s="238" t="s">
+      <c r="C2" s="238"/>
+      <c r="E2" s="237" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="H2" s="238" t="s">
+      <c r="F2" s="238"/>
+      <c r="H2" s="237" t="s">
         <v>334</v>
       </c>
-      <c r="I2" s="239"/>
+      <c r="I2" s="238"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -13708,7 +13737,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC153</f>
-        <v>106070.98</v>
+        <v>95092.150000000009</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -13716,7 +13745,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>313.63279917500302</v>
+        <v>313.08146845045064</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13732,7 +13761,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC154</f>
-        <v>107089.98</v>
+        <v>96111.150000000009</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -13740,7 +13769,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>434.3503720484008</v>
+        <v>434.06688669652146</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13749,7 +13778,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>266.51</v>
+        <v>238.92500000000001</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>249</v>
@@ -13771,16 +13800,16 @@
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>266.9325</v>
+      <c r="C6" s="210" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>243</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC150</f>
-        <v>15.246567505720826</v>
+        <v>13.668478260869568</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -13788,7 +13817,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>318.29972955259109</v>
+        <v>318.09170964413323</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13797,14 +13826,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-19.239999999999998</v>
+        <v>-10.595000000000001</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC151</f>
-        <v>4.3734377728391145</v>
+        <v>3.9207670251607274</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -13812,23 +13841,23 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>347.41863722308153</v>
+        <v>347.15792822685916</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.42249999999999999</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>271</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC161</f>
-        <v>7.7108743597919055E-2</v>
+        <v>8.6011305875406105E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -13836,7 +13865,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.3035857462124556</v>
+        <v>0.4529995949643576</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13845,30 +13874,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.7332000000000003E-2</v>
+        <v>-4.2462E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>294</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC162</f>
-        <v>6.558853326329217E-2</v>
+        <v>7.3161033797216682E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.585E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>299</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC164</f>
-        <v>8.5980161586137888E-2</v>
+        <v>9.5906970238868294E-2</v>
       </c>
       <c r="H10" s="186" t="s">
         <v>408</v>
@@ -13884,7 +13913,7 @@
       </c>
       <c r="C11" s="211" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>370.86</v>
+        <v>368.73</v>
       </c>
       <c r="E11" s="188" t="s">
         <v>295</v>
@@ -13916,7 +13945,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3960999999999999</v>
+        <v>1.3965000000000001</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>105</v>
@@ -13932,7 +13961,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4304496</v>
+        <v>5274656</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>106</v>
@@ -13948,7 +13977,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-9.6067746333634331E-3</v>
+        <v>-1.0715921345768289E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13961,10 +13990,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="240" t="s">
+      <c r="B17" s="239" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="240"/>
+      <c r="C17" s="239"/>
       <c r="E17" s="186" t="s">
         <v>302</v>
       </c>
@@ -14037,14 +14066,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="240" t="s">
+      <c r="B25" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="240"/>
-      <c r="E25" s="238" t="s">
+      <c r="C25" s="239"/>
+      <c r="E25" s="237" t="s">
         <v>352</v>
       </c>
-      <c r="F25" s="239"/>
+      <c r="F25" s="238"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -14053,12 +14082,12 @@
       <c r="C26" s="172">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="2">
+      <c r="E26" s="187" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="221" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14073,7 +14102,7 @@
       </c>
       <c r="F27" s="222">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14093,15 +14122,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="240" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="237"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
+      <c r="C33" s="240"/>
+      <c r="D33" s="240"/>
+      <c r="E33" s="240"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="240"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14120,24 +14149,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="237"/>
-      <c r="C39" s="237"/>
-      <c r="D39" s="237"/>
-      <c r="E39" s="237"/>
-      <c r="F39" s="237"/>
-      <c r="G39" s="237"/>
-      <c r="H39" s="237"/>
+      <c r="B39" s="240"/>
+      <c r="C39" s="240"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="240"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="237" t="s">
+      <c r="B42" s="240" t="s">
         <v>347</v>
       </c>
-      <c r="C42" s="237"/>
-      <c r="D42" s="237"/>
-      <c r="E42" s="237"/>
-      <c r="F42" s="237"/>
-      <c r="G42" s="237"/>
-      <c r="H42" s="237"/>
+      <c r="C42" s="240"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
+      <c r="G42" s="240"/>
+      <c r="H42" s="240"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14152,24 +14181,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="237"/>
-      <c r="C49" s="237"/>
-      <c r="D49" s="237"/>
-      <c r="E49" s="237"/>
-      <c r="F49" s="237"/>
-      <c r="G49" s="237"/>
-      <c r="H49" s="237"/>
+      <c r="B49" s="240"/>
+      <c r="C49" s="240"/>
+      <c r="D49" s="240"/>
+      <c r="E49" s="240"/>
+      <c r="F49" s="240"/>
+      <c r="G49" s="240"/>
+      <c r="H49" s="240"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="237" t="s">
+      <c r="B52" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="237"/>
-      <c r="D52" s="237"/>
-      <c r="E52" s="237"/>
-      <c r="F52" s="237"/>
-      <c r="G52" s="237"/>
-      <c r="H52" s="237"/>
+      <c r="C52" s="240"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
+      <c r="G52" s="240"/>
+      <c r="H52" s="240"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14195,28 +14224,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="237"/>
-      <c r="C59" s="237"/>
-      <c r="D59" s="237"/>
-      <c r="E59" s="237"/>
-      <c r="F59" s="237"/>
-      <c r="G59" s="237"/>
-      <c r="H59" s="237"/>
+      <c r="B59" s="240"/>
+      <c r="C59" s="240"/>
+      <c r="D59" s="240"/>
+      <c r="E59" s="240"/>
+      <c r="F59" s="240"/>
+      <c r="G59" s="240"/>
+      <c r="H59" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14286,36 +14315,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="237" t="s">
+      <c r="S2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
-      <c r="AA2" s="237" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15335,35 +15364,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="P2" s="237" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="237"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="237"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -17304,20 +17333,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -18710,6 +18739,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18717,12 +18752,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18760,20 +18789,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="S2" s="251"/>
       <c r="T2" s="251"/>
       <c r="U2" s="251"/>
@@ -19236,24 +19265,24 @@
         <v>73</v>
       </c>
       <c r="C15" s="131">
-        <f>-Statement!M83</f>
-        <v>-0.15477651183172655</v>
+        <f>Statement!M83</f>
+        <v>0.15477651183172655</v>
       </c>
       <c r="D15" s="131">
-        <f>-Statement!N83</f>
-        <v>-0.20838881491344874</v>
+        <f>Statement!N83</f>
+        <v>0.20838881491344874</v>
       </c>
       <c r="E15" s="131">
-        <f>-Statement!O83</f>
-        <v>-0.20164730107368731</v>
+        <f>Statement!O83</f>
+        <v>0.20164730107368731</v>
       </c>
       <c r="F15" s="131">
-        <f>-Statement!P83</f>
-        <v>-0.19780695426345404</v>
+        <f>Statement!P83</f>
+        <v>0.19780695426345404</v>
       </c>
       <c r="G15" s="132">
-        <f>-Statement!Q83</f>
-        <v>-0.18365010304556903</v>
+        <f>Statement!Q83</f>
+        <v>0.18365010304556903</v>
       </c>
       <c r="H15" s="131">
         <f>Overview!$C$26</f>
@@ -19547,23 +19576,23 @@
       </c>
       <c r="C27" s="128">
         <f>C10*(1-C15)</f>
-        <v>6700.0133216476779</v>
+        <v>4903.9866783523221</v>
       </c>
       <c r="D27" s="128">
         <f t="shared" ref="D27:L27" si="6">D10*(1-D15)</f>
-        <v>7368.7549933422106</v>
+        <v>4827.2450066577894</v>
       </c>
       <c r="E27" s="128">
         <f t="shared" si="6"/>
-        <v>7990.9545521400196</v>
+        <v>5309.0454478599795</v>
       </c>
       <c r="F27" s="128">
         <f t="shared" si="6"/>
-        <v>8074.4166786899432</v>
+        <v>5407.5833213100559</v>
       </c>
       <c r="G27" s="133">
         <f t="shared" si="6"/>
-        <v>10304.857797114724</v>
+        <v>7107.1422028852758</v>
       </c>
       <c r="H27" s="128">
         <f t="shared" si="6"/>
@@ -19592,23 +19621,23 @@
       </c>
       <c r="C28" s="94">
         <f>C27+C20-C21+C22</f>
-        <v>7432.0133216476779</v>
+        <v>5635.9866783523221</v>
       </c>
       <c r="D28" s="94">
         <f t="shared" ref="D28:L28" si="7">D27+D20-D21+D22</f>
-        <v>8118.7549933422106</v>
+        <v>5577.2450066577894</v>
       </c>
       <c r="E28" s="94">
         <f t="shared" si="7"/>
-        <v>8147.9545521400196</v>
+        <v>5466.0454478599795</v>
       </c>
       <c r="F28" s="94">
         <f t="shared" si="7"/>
-        <v>8892.4166786899441</v>
+        <v>6225.5833213100559</v>
       </c>
       <c r="G28" s="129">
         <f t="shared" si="7"/>
-        <v>11548.857797114724</v>
+        <v>8351.1422028852758</v>
       </c>
       <c r="H28" s="94">
         <f t="shared" si="7"/>
@@ -19782,16 +19811,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19854,10 +19883,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19874,7 +19903,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>266.51</v>
+        <v>238.92500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19883,7 +19912,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>106070.98</v>
+        <v>95092.150000000009</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19901,7 +19930,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19910,7 +19939,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3960999999999999</v>
+        <v>1.3965000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19919,7 +19948,7 @@
       </c>
       <c r="C11" s="137">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19942,10 +19971,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="240" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="237"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19953,7 +19982,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.8953486453296157E-2</v>
+        <v>6.5315373980890948E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19962,7 +19991,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.94104651354670388</v>
+        <v>0.93468462601910907</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19980,7 +20009,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11044449999999999</v>
+        <v>0.11107600000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19989,7 +20018,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10630864763461223</v>
+        <v>0.10645258593738867</v>
       </c>
     </row>
   </sheetData>
@@ -20034,20 +20063,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -20154,23 +20183,23 @@
       </c>
       <c r="C7" s="114">
         <f>'FCF &amp; Other'!C28</f>
-        <v>7432.0133216476779</v>
+        <v>5635.9866783523221</v>
       </c>
       <c r="D7" s="114">
         <f>'FCF &amp; Other'!D28</f>
-        <v>8118.7549933422106</v>
+        <v>5577.2450066577894</v>
       </c>
       <c r="E7" s="114">
         <f>'FCF &amp; Other'!E28</f>
-        <v>8147.9545521400196</v>
+        <v>5466.0454478599795</v>
       </c>
       <c r="F7" s="114">
         <f>'FCF &amp; Other'!F28</f>
-        <v>8892.4166786899441</v>
+        <v>6225.5833213100559</v>
       </c>
       <c r="G7" s="115">
         <f>'FCF &amp; Other'!G28</f>
-        <v>11548.857797114724</v>
+        <v>8351.1422028852758</v>
       </c>
       <c r="H7" s="114">
         <f>'FCF &amp; Other'!H28</f>
@@ -20240,7 +20269,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>146678.30015367549</v>
+        <v>146434.08969600862</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20294,23 +20323,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7333.9343688748686</v>
+        <v>7332.9802981093017</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7495.2737421203692</v>
+        <v>7493.3237501897638</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7522.8953043433812</v>
+        <v>7519.9597282427831</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7495.1302190141269</v>
+        <v>7491.2308171374661</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7489.2524918783101</v>
+        <v>7484.3823787273559</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20329,14 +20358,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>88508.367945420148</v>
+        <v>88303.547470872698</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="240" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="237"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20352,14 +20381,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10630864763461223</v>
+        <v>0.10645258593738867</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="240" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="237"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20367,7 +20396,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37336.486126231059</v>
+        <v>37321.876972406673</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20376,7 +20405,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>88508.367945420148</v>
+        <v>88303.547470872698</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20385,7 +20414,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>125844.85407165121</v>
+        <v>125625.42444327936</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20412,7 +20441,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>124825.85407165121</v>
+        <v>124606.42444327936</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20430,7 +20459,7 @@
       </c>
       <c r="C26" s="144">
         <f ca="1">C24/C25</f>
-        <v>313.63279917500302</v>
+        <v>313.08146845045064</v>
       </c>
     </row>
   </sheetData>
@@ -20473,20 +20502,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20648,23 +20677,23 @@
       </c>
       <c r="C8" s="92">
         <f>'FCF &amp; Other'!C28</f>
-        <v>7432.0133216476779</v>
+        <v>5635.9866783523221</v>
       </c>
       <c r="D8" s="92">
         <f>'FCF &amp; Other'!D28</f>
-        <v>8118.7549933422106</v>
+        <v>5577.2450066577894</v>
       </c>
       <c r="E8" s="92">
         <f>'FCF &amp; Other'!E28</f>
-        <v>8147.9545521400196</v>
+        <v>5466.0454478599795</v>
       </c>
       <c r="F8" s="92">
         <f>'FCF &amp; Other'!F28</f>
-        <v>8892.4166786899441</v>
+        <v>6225.5833213100559</v>
       </c>
       <c r="G8" s="93">
         <f>'FCF &amp; Other'!G28</f>
-        <v>11548.857797114724</v>
+        <v>8351.1422028852758</v>
       </c>
       <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
@@ -20854,26 +20883,26 @@
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
 (D8-C8)/ABS(C8)
 )</f>
-        <v>9.2403180938093632E-2</v>
+        <v>-1.0422606554440219E-2</v>
       </c>
       <c r="E14" s="95">
         <f t="shared" ref="E14:L14" si="3">IF(D8=0,
 IF(E8=0,0,IF(E8&gt;0,1,-1)),
 (E8-D8)/ABS(D8)
 )</f>
-        <v>3.5965562234300846E-3</v>
+        <v>-1.9938080300411113E-2</v>
       </c>
       <c r="F14" s="95">
         <f t="shared" si="3"/>
-        <v>9.1367977298596401E-2</v>
+        <v>0.1389556454835999</v>
       </c>
       <c r="G14" s="96">
         <f t="shared" si="3"/>
-        <v>0.29873106652669074</v>
+        <v>0.34142324853310874</v>
       </c>
       <c r="H14" s="95">
         <f t="shared" si="3"/>
-        <v>-0.29745476513720726</v>
+        <v>-2.8444874203225189E-2</v>
       </c>
       <c r="I14" s="95">
         <f t="shared" si="3"/>
@@ -21386,23 +21415,23 @@
       </c>
       <c r="C34" s="151">
         <f>C32/C8</f>
-        <v>43.258706098325931</v>
+        <v>57.044009921966342</v>
       </c>
       <c r="D34" s="151">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
-        <v>19.720857462911162</v>
+        <v>28.707508780566652</v>
       </c>
       <c r="E34" s="151">
         <f t="shared" si="13"/>
-        <v>33.903673398306502</v>
+        <v>50.538472948144502</v>
       </c>
       <c r="F34" s="151">
         <f t="shared" si="13"/>
-        <v>25.750930064799341</v>
+        <v>36.781774201973704</v>
       </c>
       <c r="G34" s="152">
         <f t="shared" si="13"/>
-        <v>11.706442522287901</v>
+        <v>16.188928019126589</v>
       </c>
       <c r="H34" s="139"/>
       <c r="I34" s="139"/>
@@ -21418,10 +21447,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="240" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="237"/>
+      <c r="C37" s="240"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21439,7 +21468,7 @@
       </c>
       <c r="C39" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10630864763461223</v>
+        <v>0.10645258593738867</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21465,7 +21494,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>173890.44807526353</v>
+        <v>173777.62090521553</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21492,7 +21521,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>172871.44807526353</v>
+        <v>172758.62090521553</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21510,14 +21539,14 @@
       </c>
       <c r="C47" s="144">
         <f ca="1">C45/C46</f>
-        <v>434.3503720484008</v>
+        <v>434.06688669652146</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="237" t="s">
+      <c r="B49" s="240" t="s">
         <v>211</v>
       </c>
-      <c r="C49" s="237"/>
+      <c r="C49" s="240"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21573,10 +21602,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="237" t="s">
+      <c r="B57" s="240" t="s">
         <v>328</v>
       </c>
-      <c r="C57" s="237"/>
+      <c r="C57" s="240"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21593,7 +21622,7 @@
       </c>
       <c r="C59" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10630864763461223</v>
+        <v>0.10645258593738867</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21619,7 +21648,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>127702.29236193126</v>
+        <v>127619.50043836504</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21646,7 +21675,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>126683.29236193126</v>
+        <v>126600.50043836504</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21664,7 +21693,7 @@
       </c>
       <c r="C67" s="144">
         <f ca="1">C65/C66</f>
-        <v>318.29972955259109</v>
+        <v>318.09170964413323</v>
       </c>
     </row>
   </sheetData>
@@ -21716,10 +21745,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21728,7 +21757,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>313.63279917500302</v>
+        <v>313.08146845045064</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21737,7 +21766,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C47</f>
-        <v>434.3503720484008</v>
+        <v>434.06688669652146</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21755,7 +21784,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C67</f>
-        <v>318.29972955259109</v>
+        <v>318.09170964413323</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21764,7 +21793,7 @@
       </c>
       <c r="C9" s="144">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>347.41863722308153</v>
+        <v>347.15792822685916</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21773,7 +21802,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>266.51</v>
+        <v>238.92500000000001</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21782,7 +21811,7 @@
       </c>
       <c r="C11" s="156">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.3035857462124556</v>
+        <v>0.4529995949643576</v>
       </c>
     </row>
   </sheetData>
@@ -21838,20 +21867,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="249"/>
       <c r="H2" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22214,10 +22243,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="240" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="237"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22318,20 +22347,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="240" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
       <c r="G3" s="249"/>
       <c r="H3" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
       <c r="P3" s="251"/>
       <c r="Q3" s="251"/>
       <c r="R3" s="251"/>
@@ -22438,43 +22467,43 @@
       </c>
       <c r="C7" s="114">
         <f>'FCF &amp; Other'!C28</f>
-        <v>7432.0133216476779</v>
+        <v>5635.9866783523221</v>
       </c>
       <c r="D7" s="114">
         <f>'FCF &amp; Other'!D28</f>
-        <v>8118.7549933422106</v>
+        <v>5577.2450066577894</v>
       </c>
       <c r="E7" s="114">
         <f>'FCF &amp; Other'!E28</f>
-        <v>8147.9545521400196</v>
+        <v>5466.0454478599795</v>
       </c>
       <c r="F7" s="114">
         <f>'FCF &amp; Other'!F28</f>
-        <v>8892.4166786899441</v>
+        <v>6225.5833213100559</v>
       </c>
       <c r="G7" s="115">
         <f>'FCF &amp; Other'!G28</f>
-        <v>11548.857797114724</v>
+        <v>8351.1422028852758</v>
       </c>
       <c r="H7" s="128">
         <f>G7*(1+$C$17)</f>
-        <v>10278.483439432104</v>
+        <v>7432.5165605678958</v>
       </c>
       <c r="I7" s="128">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>9147.8502610945725</v>
+        <v>6614.9397389054275</v>
       </c>
       <c r="J7" s="128">
         <f t="shared" si="0"/>
-        <v>8141.5867323741695</v>
+        <v>5887.2963676258305</v>
       </c>
       <c r="K7" s="128">
         <f t="shared" si="0"/>
-        <v>7246.0121918130108</v>
+        <v>5239.6937671869891</v>
       </c>
       <c r="L7" s="128">
         <f t="shared" si="0"/>
-        <v>6448.9508507135797</v>
+        <v>4663.3274527964204</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22506,7 +22535,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>76214.030088566855</v>
+        <v>55019.684492690649</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22560,23 +22589,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>9290.7919154464089</v>
+        <v>6717.4288849178793</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7474.2295673334502</v>
+        <v>5403.3148673170726</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6012.8467124879517</v>
+        <v>4346.2777285102038</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>4837.197635177241</v>
+        <v>3496.0261537975862</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3891.4148456784183</v>
+        <v>2812.1071941314276</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22595,7 +22624,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>45988.939131519968</v>
+        <v>33178.294285973046</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22611,7 +22640,7 @@
       </c>
       <c r="C15" s="158">
         <f ca="1">Overview!C5</f>
-        <v>266.51</v>
+        <v>238.92500000000001</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22620,7 +22649,7 @@
       </c>
       <c r="C16" s="158">
         <f ca="1">C36</f>
-        <v>192.15180856191816</v>
+        <v>138.02625405690256</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22659,7 +22688,7 @@
       </c>
       <c r="C21" s="224">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10630864763461223</v>
+        <v>0.10645258593738867</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22677,7 +22706,7 @@
       </c>
       <c r="C23" s="163">
         <f ca="1">C15*C22</f>
-        <v>106070.98</v>
+        <v>95092.150000000009</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22704,7 +22733,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C23+C25-C24</f>
-        <v>107089.98</v>
+        <v>96111.150000000009</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22720,7 +22749,7 @@
       </c>
       <c r="C29" s="163">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31506.480676123465</v>
+        <v>22775.154828674167</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22729,7 +22758,7 @@
       </c>
       <c r="C30" s="163">
         <f ca="1">L11</f>
-        <v>45988.939131519968</v>
+        <v>33178.294285973046</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22738,7 +22767,7 @@
       </c>
       <c r="C31" s="166">
         <f ca="1">C29+C30</f>
-        <v>77495.419807643426</v>
+        <v>55953.449114647214</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22765,7 +22794,7 @@
       </c>
       <c r="C34" s="166">
         <f ca="1">C31+C32-C33</f>
-        <v>76476.419807643426</v>
+        <v>54934.449114647214</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22783,7 +22812,7 @@
       </c>
       <c r="C36" s="169">
         <f ca="1">C34/C35</f>
-        <v>192.15180856191816</v>
+        <v>138.02625405690256</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22848,43 +22877,43 @@
       </c>
       <c r="C41" s="114">
         <f>C7</f>
-        <v>7432.0133216476779</v>
+        <v>5635.9866783523221</v>
       </c>
       <c r="D41" s="114">
         <f t="shared" si="2"/>
-        <v>8118.7549933422106</v>
+        <v>5577.2450066577894</v>
       </c>
       <c r="E41" s="114">
         <f t="shared" si="2"/>
-        <v>8147.9545521400196</v>
+        <v>5466.0454478599795</v>
       </c>
       <c r="F41" s="114">
         <f t="shared" si="2"/>
-        <v>8892.4166786899441</v>
+        <v>6225.5833213100559</v>
       </c>
       <c r="G41" s="115">
         <f t="shared" si="2"/>
-        <v>11548.857797114724</v>
+        <v>8351.1422028852758</v>
       </c>
       <c r="H41" s="145">
         <f t="shared" si="2"/>
-        <v>10278.483439432104</v>
+        <v>7432.5165605678958</v>
       </c>
       <c r="I41" s="145">
         <f t="shared" si="2"/>
-        <v>9147.8502610945725</v>
+        <v>6614.9397389054275</v>
       </c>
       <c r="J41" s="145">
         <f t="shared" si="2"/>
-        <v>8141.5867323741695</v>
+        <v>5887.2963676258305</v>
       </c>
       <c r="K41" s="145">
         <f t="shared" si="2"/>
-        <v>7246.0121918130108</v>
+        <v>5239.6937671869891</v>
       </c>
       <c r="L41" s="145">
         <f t="shared" si="2"/>
-        <v>6448.9508507135797</v>
+        <v>4663.3274527964204</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -22913,23 +22942,23 @@
       </c>
       <c r="H42" s="145">
         <f>H41/H43</f>
-        <v>9344.0758540291845</v>
+        <v>6756.8332368799047</v>
       </c>
       <c r="I42" s="145">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>8316.2275100859752</v>
+        <v>6013.5815808231155</v>
       </c>
       <c r="J42" s="145">
         <f t="shared" si="3"/>
-        <v>7401.442483976517</v>
+        <v>5352.0876069325732</v>
       </c>
       <c r="K42" s="145">
         <f t="shared" si="3"/>
-        <v>6587.2838107390999</v>
+        <v>4763.35797016999</v>
       </c>
       <c r="L42" s="145">
         <f t="shared" si="3"/>
-        <v>5862.6825915577992</v>
+        <v>4239.3885934512909</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -22938,23 +22967,23 @@
       </c>
       <c r="C43" s="95">
         <f>C41/C42</f>
-        <v>1.2809399037655425</v>
+        <v>0.97138688010208929</v>
       </c>
       <c r="D43" s="95">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
-        <v>1.3313799595510349</v>
+        <v>0.91460232972413735</v>
       </c>
       <c r="E43" s="95">
         <f t="shared" si="4"/>
-        <v>1.2252563236300782</v>
+        <v>0.82196172148270363</v>
       </c>
       <c r="F43" s="95">
         <f t="shared" si="4"/>
-        <v>1.3191539354235193</v>
+        <v>0.92354002689661119</v>
       </c>
       <c r="G43" s="96">
         <f t="shared" si="4"/>
-        <v>1.3265400639920428</v>
+        <v>0.9592398579009046</v>
       </c>
       <c r="H43" s="170">
         <v>1.1000000000000001</v>
@@ -22998,23 +23027,23 @@
       </c>
       <c r="H44" s="145">
         <f>H41/H45</f>
-        <v>1027848.3439432104</v>
+        <v>743251.65605678956</v>
       </c>
       <c r="I44" s="145">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>457392.51305472862</v>
+        <v>330746.98694527138</v>
       </c>
       <c r="J44" s="145">
         <f t="shared" si="5"/>
-        <v>193847.30315176593</v>
+        <v>140173.72303871025</v>
       </c>
       <c r="K44" s="145">
         <f t="shared" si="5"/>
-        <v>103514.459883043</v>
+        <v>74852.768102671267</v>
       </c>
       <c r="L44" s="145">
         <f t="shared" si="5"/>
-        <v>42993.005671423867</v>
+        <v>31088.849685309469</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -23023,23 +23052,23 @@
       </c>
       <c r="C45" s="95">
         <f>C41/C44</f>
-        <v>0.47082757818483861</v>
+        <v>0.35704698627509168</v>
       </c>
       <c r="D45" s="95">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
-        <v>0.46113569199944399</v>
+        <v>0.3167809273348739</v>
       </c>
       <c r="E45" s="95">
         <f t="shared" si="6"/>
-        <v>0.41980290340254622</v>
+        <v>0.28162426955845121</v>
       </c>
       <c r="F45" s="95">
         <f t="shared" si="6"/>
-        <v>0.41350461188979049</v>
+        <v>0.28949469059800309</v>
       </c>
       <c r="G45" s="96">
         <f t="shared" si="6"/>
-        <v>0.48587899352579933</v>
+        <v>0.35134596335080465</v>
       </c>
       <c r="H45" s="170">
         <v>0.01</v>
@@ -23064,19 +23093,19 @@
       <c r="C46" s="139"/>
       <c r="D46" s="95">
         <f>D41/C41-1</f>
-        <v>9.2403180938093632E-2</v>
+        <v>-1.0422606554440272E-2</v>
       </c>
       <c r="E46" s="95">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
-        <v>3.5965562234301363E-3</v>
+        <v>-1.993808030041111E-2</v>
       </c>
       <c r="F46" s="95">
         <f t="shared" si="7"/>
-        <v>9.136797729859647E-2</v>
+        <v>0.13895564548359984</v>
       </c>
       <c r="G46" s="96">
         <f t="shared" si="7"/>
-        <v>0.29873106652669068</v>
+        <v>0.34142324853310879</v>
       </c>
       <c r="H46" s="171">
         <f t="shared" si="7"/>
@@ -23122,15 +23151,15 @@
       </c>
       <c r="H47" s="171">
         <f t="shared" si="7"/>
-        <v>7.3291506320834365E-2</v>
+        <v>-0.22388775133472261</v>
       </c>
       <c r="I47" s="171">
         <f t="shared" si="7"/>
-        <v>-0.10999999999999988</v>
+        <v>-0.10999999999999999</v>
       </c>
       <c r="J47" s="171">
         <f t="shared" si="7"/>
-        <v>-0.1100000000000001</v>
+        <v>-0.10999999999999999</v>
       </c>
       <c r="K47" s="171">
         <f t="shared" si="7"/>
@@ -23164,7 +23193,7 @@
       </c>
       <c r="H48" s="171">
         <f t="shared" si="8"/>
-        <v>42.243230423796142</v>
+        <v>30.269790738221616</v>
       </c>
       <c r="I48" s="171">
         <f t="shared" si="8"/>
@@ -23176,7 +23205,7 @@
       </c>
       <c r="K48" s="171">
         <f t="shared" si="8"/>
-        <v>-0.46599999999999997</v>
+        <v>-0.46600000000000008</v>
       </c>
       <c r="L48" s="171">
         <f t="shared" si="8"/>
@@ -23217,11 +23246,11 @@
       </c>
       <c r="J49" s="171">
         <f t="shared" si="9"/>
-        <v>3.8181818181818178E-2</v>
+        <v>3.8181818181818185E-2</v>
       </c>
       <c r="K49" s="171">
         <f t="shared" si="9"/>
-        <v>6.363636363636363E-2</v>
+        <v>6.3636363636363644E-2</v>
       </c>
       <c r="L49" s="171">
         <f t="shared" si="9"/>
@@ -23230,17 +23259,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29754,7 +29783,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>266.51</v>
+        <v>238.92500000000001</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29825,7 +29854,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>266.51</v>
+        <v>238.92500000000001</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31131,7 +31160,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>15.246567505720826</v>
+        <v>13.668478260869568</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31168,7 +31197,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.3734377728391145</v>
+        <v>3.9207670251607274</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31229,7 +31258,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>9.209149157839903</v>
+        <v>8.2559602361521094</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31290,7 +31319,7 @@
       </c>
       <c r="AC153" s="145">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>106070.98</v>
+        <v>95092.150000000009</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31351,7 +31380,7 @@
       </c>
       <c r="AC154" s="145">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>107089.98</v>
+        <v>96111.150000000009</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31388,7 +31417,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="185">
         <f ca="1">AC154/AC5</f>
-        <v>4.2499396777522023</v>
+        <v>3.8142372410508774</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31425,7 +31454,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="185">
         <f ca="1">AC154/AC12</f>
-        <v>11.781075907590759</v>
+        <v>10.57328382838284</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31560,7 +31589,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="94">AC153/AC157</f>
-        <v>12.968697884826996</v>
+        <v>11.626378530382688</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31597,7 +31626,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="94"/>
-        <v>13.194371919742363</v>
+        <v>11.841689191968721</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31634,7 +31663,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="97">AC157/AC153</f>
-        <v>7.7108743597919055E-2</v>
+        <v>8.6011305875406105E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31671,7 +31700,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>6.558853326329217E-2</v>
+        <v>7.3161033797216682E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31745,7 +31774,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="156">
         <f ca="1">-AC63/AC153</f>
-        <v>8.5980161586137888E-2</v>
+        <v>9.5906970238868294E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31782,7 +31811,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="156">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>8.5980161586137888E-2</v>
+        <v>9.5906970238868294E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32285,7 +32314,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="156">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-9.6067746333634331E-3</v>
+        <v>-1.0715921345768289E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33546,15 +33575,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="240" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="E4" s="237" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33562,7 +33591,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>266.51</v>
+        <v>238.92500000000001</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33578,7 +33607,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>106070.98</v>
+        <v>95092.150000000009</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33598,7 +33627,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>107089.98</v>
+        <v>96111.150000000009</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33618,7 +33647,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>15.246567505720826</v>
+        <v>13.668478260869568</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>249</v>
@@ -33638,7 +33667,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.3734377728391145</v>
+        <v>3.9207670251607274</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>250</v>
@@ -33658,7 +33687,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>9.209149157839903</v>
+        <v>8.2559602361521094</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33678,7 +33707,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>4.2499396777522023</v>
+        <v>3.8142372410508774</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33687,18 +33716,18 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>11.781075907590759</v>
+        <v>10.57328382838284</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="240" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="237"/>
-      <c r="E15" s="237" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="237"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33749,14 +33778,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="240" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="237"/>
-      <c r="E21" s="237" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>255</v>
       </c>
-      <c r="F21" s="237"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33825,14 +33854,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="237" t="s">
+      <c r="B29" s="240" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="237"/>
-      <c r="E29" s="237" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="237"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33908,14 +33937,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="240" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="237"/>
-      <c r="E37" s="237" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="237"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33923,7 +33952,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>6.558853326329217E-2</v>
+        <v>7.3161033797216682E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>276</v>
@@ -33939,7 +33968,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC161</f>
-        <v>7.7108743597919055E-2</v>
+        <v>8.6011305875406105E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>278</v>
@@ -33971,7 +34000,7 @@
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>8.5980161586137888E-2</v>
+        <v>9.5906970238868294E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33980,18 +34009,18 @@
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>8.5980161586137888E-2</v>
+        <v>9.5906970238868294E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="237" t="s">
+      <c r="B45" s="240" t="s">
         <v>285</v>
       </c>
-      <c r="C45" s="237"/>
-      <c r="E45" s="237" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>291</v>
       </c>
-      <c r="F45" s="237"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34024,18 +34053,18 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC176</f>
-        <v>-9.6067746333634331E-3</v>
+        <v>-1.0715921345768289E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="237" t="s">
+      <c r="B51" s="240" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="237"/>
-      <c r="E51" s="237" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>309</v>
       </c>
-      <c r="F51" s="237"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34203,7 +34232,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC116</f>
-        <v>266.51</v>
+        <v>238.92500000000001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34232,7 +34261,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC153</f>
-        <v>106070.98</v>
+        <v>95092.150000000009</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34261,7 +34290,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC154</f>
-        <v>107089.98</v>
+        <v>96111.150000000009</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34290,7 +34319,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC150</f>
-        <v>15.246567505720826</v>
+        <v>13.668478260869568</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34319,7 +34348,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC151</f>
-        <v>4.3734377728391145</v>
+        <v>3.9207670251607274</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34348,7 +34377,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC152</f>
-        <v>9.209149157839903</v>
+        <v>8.2559602361521094</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34377,7 +34406,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC155</f>
-        <v>4.2499396777522023</v>
+        <v>3.8142372410508774</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34406,7 +34435,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC156</f>
-        <v>11.781075907590759</v>
+        <v>10.57328382838284</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35179,7 +35208,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC162</f>
-        <v>6.558853326329217E-2</v>
+        <v>7.3161033797216682E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35208,7 +35237,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC161</f>
-        <v>7.7108743597919055E-2</v>
+        <v>8.6011305875406105E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35266,7 +35295,7 @@
       </c>
       <c r="I54" s="177">
         <f ca="1">Statement!AC164</f>
-        <v>8.5980161586137888E-2</v>
+        <v>9.5906970238868294E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35295,7 +35324,7 @@
       </c>
       <c r="I55" s="177">
         <f ca="1">Statement!AC165</f>
-        <v>8.5980161586137888E-2</v>
+        <v>9.5906970238868294E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35531,7 +35560,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC176</f>
-        <v>-9.6067746333634331E-3</v>
+        <v>-1.0715921345768289E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36017,14 +36046,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>319</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>320</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36091,19 +36120,19 @@
       <c r="B7" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="241">
         <f>Statement!AA89</f>
         <v>3.4385745545482967E-2</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="242"/>
+      <c r="F7" s="241">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1268516941937681</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -36130,19 +36159,19 @@
       <c r="B9" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="241">
         <f>Statement!AA90</f>
         <v>7.6807228915662648E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="242"/>
+      <c r="F9" s="241">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1206896551724138</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="242"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -36169,19 +36198,19 @@
       <c r="B11" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="241">
         <f>Statement!AA91</f>
         <v>2.9473317056156263E-2</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="242"/>
+      <c r="F11" s="241">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12760267430754538</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="242"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -36208,19 +36237,19 @@
       <c r="B13" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="241">
         <f>Statement!AA95</f>
         <v>0.10524728588661038</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="242"/>
+      <c r="F13" s="241">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.172424824056302</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="242"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -36247,19 +36276,19 @@
       <c r="B15" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="241">
         <f>Statement!AA96</f>
         <v>-7.4441687344913146E-2</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="242"/>
+      <c r="F15" s="241">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.1166429587482217E-2</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -36286,19 +36315,19 @@
       <c r="B17" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="241">
         <f>Statement!AA98</f>
         <v>-9.3700370566437263E-2</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="242"/>
+      <c r="F17" s="241">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2418687167356593E-2</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="242"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -36325,22 +36354,22 @@
       <c r="B19" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="241">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.1897810218978103E-2</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="242"/>
+      <c r="F19" s="241">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.2937062937062943E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="242"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -36367,22 +36396,22 @@
       <c r="B21" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="241">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-7.6086956521739066E-2</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="242"/>
+      <c r="F21" s="241">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>7.8680203045685293E-2</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="242"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36430,22 +36459,22 @@
       <c r="B25" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="241">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5172636334301385E-2</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="242"/>
+      <c r="F25" s="241">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13738698812267328</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="242"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36472,22 +36501,22 @@
       <c r="B27" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="241">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-1.1111111111111112E-2</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="242"/>
+      <c r="F27" s="241">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="242"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36514,49 +36543,49 @@
       <c r="B29" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="241">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="242"/>
+      <c r="F29" s="241">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.21527777777777779</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC355E1F-C84E-CC40-A2BD-2B3BB0215D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1004C7-F8DA-EB43-9C62-09864B1797E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2340,19 +2310,9 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2364,6 +2324,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2373,16 +2339,22 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2394,8 +2366,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12760,7 +12730,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12800,8 +12770,10 @@
     <v>363.7</v>
     <v>190.12</v>
     <v>1.4074</v>
-    <v>-3.8149999999999999</v>
-    <v>-1.5966999999999999E-2</v>
+    <v>-3.46</v>
+    <v>-1.4480999999999999E-2</v>
+    <v>0.1835</v>
+    <v>7.7930000000000002E-4</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12813,46 +12785,32 @@
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.814752082813</v>
+    <v>46290.841048911716</v>
     <v>4</v>
     <v>234.96</v>
-    <v>91506758000</v>
+    <v>91644924000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
     <v>238.85</v>
-    <v>13.12</v>
+    <v>13.139799999999999</v>
     <v>238.93</v>
-    <v>235.11500000000001</v>
+    <v>235.47</v>
+    <v>235.65350000000001</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>2041129</v>
+    <v>3092658</v>
     <v>5303349</v>
     <v>1997</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12871,7 +12829,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>10</v>
+    <v>7</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -12881,13 +12839,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12921,6 +12879,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12942,6 +12902,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12951,11 +12912,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12991,7 +12947,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13002,13 +12958,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13109,13 +13068,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13196,6 +13161,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13203,6 +13171,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13694,18 +13665,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="238" t="s">
+      <c r="B2" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="239"/>
-      <c r="E2" s="238" t="s">
+      <c r="C2" s="237"/>
+      <c r="E2" s="236" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="H2" s="238" t="s">
+      <c r="F2" s="237"/>
+      <c r="H2" s="236" t="s">
         <v>326</v>
       </c>
-      <c r="I2" s="239"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="183" t="s">
@@ -13720,7 +13691,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>93575.77</v>
+        <v>93717.06</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13728,7 +13699,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>300.04579130718093</v>
+        <v>300.02121860664784</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13744,7 +13715,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>94594.77</v>
+        <v>94736.06</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13752,7 +13723,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>394.32937668981884</v>
+        <v>393.35077635092063</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13761,7 +13732,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>235.11500000000001</v>
+        <v>235.47</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13783,16 +13754,16 @@
       <c r="B6" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="206" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="206" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>235.65350000000001</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>13.450514874141879</v>
+        <v>13.470823798627004</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13800,7 +13771,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>368.87515213250623</v>
+        <v>367.89735085887645</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13809,14 +13780,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.8149999999999999</v>
+        <v>-3.46</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>3.8582448011746964</v>
+        <v>3.8640703627272006</v>
       </c>
       <c r="H7" s="182" t="str">
         <f>'AVG target price'!B9</f>
@@ -13824,23 +13795,23 @@
       </c>
       <c r="I7" s="210">
         <f ca="1">'AVG target price'!C9</f>
-        <v>346.66049206145931</v>
+        <v>346.16524848319403</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.1835</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>8.7405104975358472E-2</v>
+        <v>8.7273331024255357E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B11</f>
@@ -13848,7 +13819,7 @@
       </c>
       <c r="I8" s="211">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.47442950071862405</v>
+        <v>0.47010340375926463</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13857,30 +13828,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.5966999999999999E-2</v>
+        <v>-1.4480999999999999E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>7.434659634646873E-2</v>
+        <v>7.4234509703996254E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>7.7930000000000002E-4</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>9.7461126956262287E-2</v>
+        <v>9.7314192314611664E-2</v>
       </c>
       <c r="H10" s="182" t="s">
         <v>399</v>
@@ -13960,7 +13931,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0889571093029744E-2</v>
+        <v>-1.0873153724626019E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13973,10 +13944,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="240" t="s">
+      <c r="B17" s="238" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="240"/>
+      <c r="C17" s="238"/>
       <c r="E17" s="182" t="s">
         <v>297</v>
       </c>
@@ -14049,14 +14020,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="240" t="s">
+      <c r="B25" s="238" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="240"/>
-      <c r="E25" s="238" t="s">
+      <c r="C25" s="238"/>
+      <c r="E25" s="236" t="s">
         <v>344</v>
       </c>
-      <c r="F25" s="239"/>
+      <c r="F25" s="237"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="182" t="s">
@@ -14065,7 +14036,7 @@
       <c r="C26" s="168">
         <v>0.21</v>
       </c>
-      <c r="E26" s="183" t="e" vm="5">
+      <c r="E26" s="183" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="217" cm="1">
@@ -14217,18 +14188,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14304,8 +14275,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>115</v>
       </c>
       <c r="I2" s="235"/>
@@ -14338,32 +14309,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="246" t="s">
+      <c r="S4" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
-      <c r="AA4" s="247"/>
-      <c r="AB4" s="247"/>
-      <c r="AC4" s="247"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14853,33 +14824,33 @@
       <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="234" t="s">
+      <c r="C11" s="244" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="234"/>
-      <c r="E11" s="234"/>
-      <c r="F11" s="234"/>
-      <c r="G11" s="234"/>
-      <c r="H11" s="234"/>
-      <c r="I11" s="234"/>
-      <c r="J11" s="234"/>
-      <c r="K11" s="234"/>
-      <c r="L11" s="234"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="246" t="s">
+      <c r="S11" s="245" t="s">
         <v>123</v>
       </c>
-      <c r="T11" s="247"/>
-      <c r="U11" s="247"/>
-      <c r="V11" s="247"/>
-      <c r="W11" s="247"/>
-      <c r="X11" s="247"/>
-      <c r="Y11" s="247"/>
-      <c r="Z11" s="247"/>
-      <c r="AA11" s="247"/>
-      <c r="AB11" s="247"/>
-      <c r="AC11" s="247"/>
+      <c r="T11" s="246"/>
+      <c r="U11" s="246"/>
+      <c r="V11" s="246"/>
+      <c r="W11" s="246"/>
+      <c r="X11" s="246"/>
+      <c r="Y11" s="246"/>
+      <c r="Z11" s="246"/>
+      <c r="AA11" s="246"/>
+      <c r="AB11" s="246"/>
+      <c r="AC11" s="246"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15353,8 +15324,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>115</v>
       </c>
       <c r="I2" s="235"/>
@@ -15384,31 +15355,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
-      <c r="P4" s="247" t="s">
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="P4" s="246" t="s">
         <v>117</v>
       </c>
-      <c r="Q4" s="247"/>
-      <c r="R4" s="247"/>
-      <c r="S4" s="247"/>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15603,32 +15574,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="234" t="s">
+      <c r="C9" s="244" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="234"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="247" t="s">
+      <c r="P9" s="246" t="s">
         <v>127</v>
       </c>
-      <c r="Q9" s="247"/>
-      <c r="R9" s="247"/>
-      <c r="S9" s="247"/>
-      <c r="T9" s="247"/>
-      <c r="U9" s="247"/>
-      <c r="V9" s="247"/>
-      <c r="W9" s="247"/>
-      <c r="X9" s="247"/>
-      <c r="Y9" s="247"/>
-      <c r="Z9" s="247"/>
+      <c r="Q9" s="246"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
+      <c r="W9" s="246"/>
+      <c r="X9" s="246"/>
+      <c r="Y9" s="246"/>
+      <c r="Z9" s="246"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16477,31 +16448,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="234" t="s">
+      <c r="C21" s="244" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="234"/>
-      <c r="E21" s="234"/>
-      <c r="F21" s="234"/>
-      <c r="G21" s="234"/>
-      <c r="H21" s="234"/>
-      <c r="I21" s="234"/>
-      <c r="J21" s="234"/>
-      <c r="K21" s="234"/>
-      <c r="L21" s="234"/>
-      <c r="P21" s="247" t="s">
+      <c r="D21" s="244"/>
+      <c r="E21" s="244"/>
+      <c r="F21" s="244"/>
+      <c r="G21" s="244"/>
+      <c r="H21" s="244"/>
+      <c r="I21" s="244"/>
+      <c r="J21" s="244"/>
+      <c r="K21" s="244"/>
+      <c r="L21" s="244"/>
+      <c r="P21" s="246" t="s">
         <v>129</v>
       </c>
-      <c r="Q21" s="247"/>
-      <c r="R21" s="247"/>
-      <c r="S21" s="247"/>
-      <c r="T21" s="247"/>
-      <c r="U21" s="247"/>
-      <c r="V21" s="247"/>
-      <c r="W21" s="247"/>
-      <c r="X21" s="247"/>
-      <c r="Y21" s="247"/>
-      <c r="Z21" s="247"/>
+      <c r="Q21" s="246"/>
+      <c r="R21" s="246"/>
+      <c r="S21" s="246"/>
+      <c r="T21" s="246"/>
+      <c r="U21" s="246"/>
+      <c r="V21" s="246"/>
+      <c r="W21" s="246"/>
+      <c r="X21" s="246"/>
+      <c r="Y21" s="246"/>
+      <c r="Z21" s="246"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -17322,54 +17293,54 @@
       <c r="D3" s="235"/>
       <c r="E3" s="235"/>
       <c r="F3" s="235"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>115</v>
       </c>
       <c r="I3" s="235"/>
       <c r="J3" s="235"/>
       <c r="K3" s="235"/>
       <c r="L3" s="235"/>
-      <c r="P3" s="233"/>
-      <c r="Q3" s="233"/>
-      <c r="R3" s="233"/>
-      <c r="S3" s="233"/>
-      <c r="T3" s="233"/>
-      <c r="U3" s="233"/>
-      <c r="V3" s="233"/>
-      <c r="W3" s="233"/>
-      <c r="X3" s="233"/>
-      <c r="Y3" s="233"/>
-      <c r="Z3" s="233"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="234" t="s">
+      <c r="C5" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="234"/>
-      <c r="J5" s="234"/>
-      <c r="K5" s="234"/>
-      <c r="L5" s="234"/>
-      <c r="P5" s="233"/>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="233"/>
-      <c r="S5" s="233"/>
-      <c r="T5" s="233"/>
-      <c r="U5" s="233"/>
-      <c r="V5" s="233"/>
-      <c r="W5" s="233"/>
-      <c r="X5" s="233"/>
-      <c r="Y5" s="233"/>
-      <c r="Z5" s="233"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17555,30 +17526,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="234" t="s">
+      <c r="C11" s="244" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="234"/>
-      <c r="E11" s="234"/>
-      <c r="F11" s="234"/>
-      <c r="G11" s="234"/>
-      <c r="H11" s="234"/>
-      <c r="I11" s="234"/>
-      <c r="J11" s="234"/>
-      <c r="K11" s="234"/>
-      <c r="L11" s="234"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="233"/>
-      <c r="Q11" s="233"/>
-      <c r="R11" s="233"/>
-      <c r="S11" s="233"/>
-      <c r="T11" s="233"/>
-      <c r="U11" s="233"/>
-      <c r="V11" s="233"/>
-      <c r="W11" s="233"/>
-      <c r="X11" s="233"/>
-      <c r="Y11" s="233"/>
-      <c r="Z11" s="233"/>
+      <c r="P11" s="249"/>
+      <c r="Q11" s="249"/>
+      <c r="R11" s="249"/>
+      <c r="S11" s="249"/>
+      <c r="T11" s="249"/>
+      <c r="U11" s="249"/>
+      <c r="V11" s="249"/>
+      <c r="W11" s="249"/>
+      <c r="X11" s="249"/>
+      <c r="Y11" s="249"/>
+      <c r="Z11" s="249"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17820,18 +17791,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="234" t="s">
+      <c r="C18" s="244" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="234"/>
-      <c r="E18" s="234"/>
-      <c r="F18" s="234"/>
-      <c r="G18" s="234"/>
-      <c r="H18" s="234"/>
-      <c r="I18" s="234"/>
-      <c r="J18" s="234"/>
-      <c r="K18" s="234"/>
-      <c r="L18" s="234"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18044,23 +18015,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="233"/>
-      <c r="C25" s="233"/>
+      <c r="B25" s="249"/>
+      <c r="C25" s="249"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="234" t="s">
+      <c r="C26" s="244" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="234"/>
-      <c r="E26" s="234"/>
-      <c r="F26" s="234"/>
-      <c r="G26" s="234"/>
-      <c r="H26" s="234"/>
-      <c r="I26" s="234"/>
-      <c r="J26" s="234"/>
-      <c r="K26" s="234"/>
-      <c r="L26" s="234"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="244"/>
+      <c r="H26" s="244"/>
+      <c r="I26" s="244"/>
+      <c r="J26" s="244"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="244"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18252,18 +18223,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="234" t="s">
+      <c r="C33" s="244" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="234"/>
-      <c r="G33" s="234"/>
-      <c r="H33" s="234"/>
-      <c r="I33" s="234"/>
-      <c r="J33" s="234"/>
-      <c r="K33" s="234"/>
-      <c r="L33" s="234"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="244"/>
+      <c r="J33" s="244"/>
+      <c r="K33" s="244"/>
+      <c r="L33" s="244"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18447,18 +18418,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="234" t="s">
+      <c r="C40" s="244" t="s">
         <v>151</v>
       </c>
-      <c r="D40" s="234"/>
-      <c r="E40" s="234"/>
-      <c r="F40" s="234"/>
-      <c r="G40" s="234"/>
-      <c r="H40" s="234"/>
-      <c r="I40" s="234"/>
-      <c r="J40" s="234"/>
-      <c r="K40" s="234"/>
-      <c r="L40" s="234"/>
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18722,6 +18693,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18729,12 +18706,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18778,54 +18749,54 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>115</v>
       </c>
       <c r="I2" s="235"/>
       <c r="J2" s="235"/>
       <c r="K2" s="235"/>
       <c r="L2" s="235"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233"/>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="244" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
-      <c r="S4" s="233"/>
-      <c r="T4" s="233"/>
-      <c r="U4" s="233"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="233"/>
-      <c r="X4" s="233"/>
-      <c r="Y4" s="233"/>
-      <c r="Z4" s="233"/>
-      <c r="AA4" s="233"/>
-      <c r="AB4" s="233"/>
-      <c r="AC4" s="233"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="S4" s="249"/>
+      <c r="T4" s="249"/>
+      <c r="U4" s="249"/>
+      <c r="V4" s="249"/>
+      <c r="W4" s="249"/>
+      <c r="X4" s="249"/>
+      <c r="Y4" s="249"/>
+      <c r="Z4" s="249"/>
+      <c r="AA4" s="249"/>
+      <c r="AB4" s="249"/>
+      <c r="AC4" s="249"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19188,18 +19159,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="234" t="s">
+      <c r="C13" s="244" t="s">
         <v>159</v>
       </c>
-      <c r="D13" s="234"/>
-      <c r="E13" s="234"/>
-      <c r="F13" s="234"/>
-      <c r="G13" s="234"/>
-      <c r="H13" s="234"/>
-      <c r="I13" s="234"/>
-      <c r="J13" s="234"/>
-      <c r="K13" s="234"/>
-      <c r="L13" s="234"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="244"/>
+      <c r="H13" s="244"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="244"/>
+      <c r="L13" s="244"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19292,18 +19263,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="234" t="s">
+      <c r="C18" s="244" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="234"/>
-      <c r="E18" s="234"/>
-      <c r="F18" s="234"/>
-      <c r="G18" s="234"/>
-      <c r="H18" s="234"/>
-      <c r="I18" s="234"/>
-      <c r="J18" s="234"/>
-      <c r="K18" s="234"/>
-      <c r="L18" s="234"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19495,18 +19466,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="234" t="s">
+      <c r="C25" s="244" t="s">
         <v>263</v>
       </c>
-      <c r="D25" s="234"/>
-      <c r="E25" s="234"/>
-      <c r="F25" s="234"/>
-      <c r="G25" s="234"/>
-      <c r="H25" s="234"/>
-      <c r="I25" s="234"/>
-      <c r="J25" s="234"/>
-      <c r="K25" s="234"/>
-      <c r="L25" s="234"/>
+      <c r="D25" s="244"/>
+      <c r="E25" s="244"/>
+      <c r="F25" s="244"/>
+      <c r="G25" s="244"/>
+      <c r="H25" s="244"/>
+      <c r="I25" s="244"/>
+      <c r="J25" s="244"/>
+      <c r="K25" s="244"/>
+      <c r="L25" s="244"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19644,18 +19615,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="234" t="s">
+      <c r="C31" s="244" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="234"/>
-      <c r="E31" s="234"/>
-      <c r="F31" s="234"/>
-      <c r="G31" s="234"/>
-      <c r="H31" s="234"/>
-      <c r="I31" s="234"/>
-      <c r="J31" s="234"/>
-      <c r="K31" s="234"/>
-      <c r="L31" s="234"/>
+      <c r="D31" s="244"/>
+      <c r="E31" s="244"/>
+      <c r="F31" s="244"/>
+      <c r="G31" s="244"/>
+      <c r="H31" s="244"/>
+      <c r="I31" s="244"/>
+      <c r="J31" s="244"/>
+      <c r="K31" s="244"/>
+      <c r="L31" s="244"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19794,16 +19765,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19886,7 +19857,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>235.11500000000001</v>
+        <v>235.47</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19895,7 +19866,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>93575.77</v>
+        <v>93717.06</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19965,7 +19936,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.6303621494825868E-2</v>
+        <v>6.6210279063622257E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19974,7 +19945,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93369637850517417</v>
+        <v>0.9337897209363778</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20001,7 +19972,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11000257270833182</v>
+        <v>0.11000954193427279</v>
       </c>
     </row>
   </sheetData>
@@ -20052,54 +20023,54 @@
       <c r="D3" s="235"/>
       <c r="E3" s="235"/>
       <c r="F3" s="235"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>115</v>
       </c>
       <c r="I3" s="235"/>
       <c r="J3" s="235"/>
       <c r="K3" s="235"/>
       <c r="L3" s="235"/>
-      <c r="P3" s="233"/>
-      <c r="Q3" s="233"/>
-      <c r="R3" s="233"/>
-      <c r="S3" s="233"/>
-      <c r="T3" s="233"/>
-      <c r="U3" s="233"/>
-      <c r="V3" s="233"/>
-      <c r="W3" s="233"/>
-      <c r="X3" s="233"/>
-      <c r="Y3" s="233"/>
-      <c r="Z3" s="233"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="234" t="s">
+      <c r="C5" s="244" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="234"/>
-      <c r="J5" s="234"/>
-      <c r="K5" s="234"/>
-      <c r="L5" s="234"/>
-      <c r="P5" s="233"/>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="233"/>
-      <c r="S5" s="233"/>
-      <c r="T5" s="233"/>
-      <c r="U5" s="233"/>
-      <c r="V5" s="233"/>
-      <c r="W5" s="233"/>
-      <c r="X5" s="233"/>
-      <c r="Y5" s="233"/>
-      <c r="Z5" s="233"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20252,7 +20223,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>140658.2650101904</v>
+        <v>140647.37417341626</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20306,23 +20277,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7309.5281154838513</v>
+        <v>7309.4822224072295</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7445.4704151823898</v>
+        <v>7445.3769222875871</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7448.0397036832001</v>
+        <v>7447.8994163874986</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7395.8563908388614</v>
+        <v>7395.6706522236691</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7365.463495221823</v>
+        <v>7365.2322767829273</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20341,7 +20312,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>83472.866819847899</v>
+        <v>83463.783515356932</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20364,7 +20335,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11000257270833182</v>
+        <v>0.11000954193427279</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20379,7 +20350,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>36964.358120410128</v>
+        <v>36963.661490088911</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20388,7 +20359,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>83472.866819847899</v>
+        <v>83463.783515356932</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20397,7 +20368,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>120437.22494025802</v>
+        <v>120427.44500544584</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20424,7 +20395,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119418.22494025802</v>
+        <v>119408.44500544584</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20437,12 +20408,12 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="251" t="s">
+      <c r="B26" s="233" t="s">
         <v>193</v>
       </c>
-      <c r="C26" s="252">
+      <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>300.04579130718093</v>
+        <v>300.02121860664784</v>
       </c>
     </row>
   </sheetData>
@@ -20491,8 +20462,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>115</v>
       </c>
       <c r="I2" s="235"/>
@@ -20504,18 +20475,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="244" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20711,23 +20682,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7309.5281154838513</v>
+        <v>7309.4822224072295</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7445.4704151823898</v>
+        <v>7445.3769222875871</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7448.0397036832001</v>
+        <v>7447.8994163874986</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7395.8563908388614</v>
+        <v>7395.6706522236691</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7365.463495221823</v>
+        <v>7365.2322767829273</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20735,18 +20706,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="234" t="s">
+      <c r="C11" s="244" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="234"/>
-      <c r="E11" s="234"/>
-      <c r="F11" s="234"/>
-      <c r="G11" s="234"/>
-      <c r="H11" s="234"/>
-      <c r="I11" s="234"/>
-      <c r="J11" s="234"/>
-      <c r="K11" s="234"/>
-      <c r="L11" s="234"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20940,18 +20911,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="234" t="s">
+      <c r="C17" s="244" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
-      <c r="F17" s="234"/>
-      <c r="G17" s="234"/>
-      <c r="H17" s="234"/>
-      <c r="I17" s="234"/>
-      <c r="J17" s="234"/>
-      <c r="K17" s="234"/>
-      <c r="L17" s="234"/>
+      <c r="D17" s="244"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="244"/>
+      <c r="K17" s="244"/>
+      <c r="L17" s="244"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -21085,18 +21056,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="234" t="s">
+      <c r="C22" s="244" t="s">
         <v>200</v>
       </c>
-      <c r="D22" s="234"/>
-      <c r="E22" s="234"/>
-      <c r="F22" s="234"/>
-      <c r="G22" s="234"/>
-      <c r="H22" s="234"/>
-      <c r="I22" s="234"/>
-      <c r="J22" s="234"/>
-      <c r="K22" s="234"/>
-      <c r="L22" s="234"/>
+      <c r="D22" s="244"/>
+      <c r="E22" s="244"/>
+      <c r="F22" s="244"/>
+      <c r="G22" s="244"/>
+      <c r="H22" s="244"/>
+      <c r="I22" s="244"/>
+      <c r="J22" s="244"/>
+      <c r="K22" s="244"/>
+      <c r="L22" s="244"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21180,18 +21151,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="234" t="s">
+      <c r="C27" s="244" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="234"/>
-      <c r="E27" s="234"/>
-      <c r="F27" s="234"/>
-      <c r="G27" s="234"/>
-      <c r="H27" s="234"/>
-      <c r="I27" s="234"/>
-      <c r="J27" s="234"/>
-      <c r="K27" s="234"/>
-      <c r="L27" s="234"/>
+      <c r="D27" s="244"/>
+      <c r="E27" s="244"/>
+      <c r="F27" s="244"/>
+      <c r="G27" s="244"/>
+      <c r="H27" s="244"/>
+      <c r="I27" s="244"/>
+      <c r="J27" s="244"/>
+      <c r="K27" s="244"/>
+      <c r="L27" s="244"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21482,7 +21453,7 @@
       </c>
       <c r="C40" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11000257270833182</v>
+        <v>0.11000954193427279</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -21507,8 +21478,8 @@
         <v>410</v>
       </c>
       <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5-G31+G32</f>
-        <v>128363.19729735961</v>
+        <f ca="1">C42/(1+C40)^5</f>
+        <v>127974.17977436041</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21517,7 +21488,7 @@
       </c>
       <c r="C44" s="108">
         <f ca="1">SUM(H9:K9)+C43</f>
-        <v>157962.0919225479</v>
+        <v>157572.6089876664</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21544,7 +21515,7 @@
       </c>
       <c r="C47" s="108">
         <f ca="1">C44+C45-C46</f>
-        <v>156943.0919225479</v>
+        <v>156553.6089876664</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -21557,12 +21528,12 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="251" t="s">
+      <c r="B49" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="252">
+      <c r="C49" s="234">
         <f ca="1">C47/C48</f>
-        <v>394.32937668981884</v>
+        <v>393.35077635092063</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
@@ -21616,10 +21587,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="251" t="s">
+      <c r="B57" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="252">
+      <c r="C57" s="234">
         <f>C56/(1+C53)^5</f>
         <v>323.39164811633128</v>
       </c>
@@ -21645,7 +21616,7 @@
       </c>
       <c r="C61" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11000257270833182</v>
+        <v>0.11000954193427279</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -21670,8 +21641,8 @@
         <v>410</v>
       </c>
       <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5-G31+G32</f>
-        <v>118232.41592354917</v>
+        <f ca="1">C63/(1+C61)^5</f>
+        <v>117843.71642852684</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -21680,7 +21651,7 @@
       </c>
       <c r="C65" s="108">
         <f ca="1">SUM(H9:K9)+C64</f>
-        <v>147831.31054873747</v>
+        <v>147442.14564183282</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21707,7 +21678,7 @@
       </c>
       <c r="C68" s="108">
         <f ca="1">C65+C66-C67</f>
-        <v>146812.31054873747</v>
+        <v>146423.14564183282</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -21720,12 +21691,12 @@
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="251" t="s">
+      <c r="B70" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="252">
+      <c r="C70" s="234">
         <f ca="1">C68/C69</f>
-        <v>368.87515213250623</v>
+        <v>367.89735085887645</v>
       </c>
     </row>
   </sheetData>
@@ -21789,7 +21760,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>300.04579130718093</v>
+        <v>300.02121860664784</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21798,7 +21769,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C49</f>
-        <v>394.32937668981884</v>
+        <v>393.35077635092063</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21816,16 +21787,16 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C70</f>
-        <v>368.87515213250623</v>
+        <v>367.89735085887645</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="251" t="s">
+      <c r="B9" s="233" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="252">
+      <c r="C9" s="234">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>346.66049206145931</v>
+        <v>346.16524848319403</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21834,7 +21805,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C5</f>
-        <v>235.11500000000001</v>
+        <v>235.47</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21843,7 +21814,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.47442950071862405</v>
+        <v>0.47010340375926463</v>
       </c>
     </row>
   </sheetData>
@@ -21905,8 +21876,8 @@
       <c r="D2" s="235"/>
       <c r="E2" s="235"/>
       <c r="F2" s="235"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>115</v>
       </c>
       <c r="I2" s="235"/>
@@ -21918,18 +21889,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="234" t="s">
+      <c r="C4" s="244" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22042,18 +22013,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="234" t="s">
+      <c r="C9" s="244" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="234"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22174,18 +22145,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="234" t="s">
+      <c r="C14" s="244" t="s">
         <v>402</v>
       </c>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
-      <c r="F14" s="234"/>
-      <c r="G14" s="234"/>
-      <c r="H14" s="234"/>
-      <c r="I14" s="234"/>
-      <c r="J14" s="234"/>
-      <c r="K14" s="234"/>
-      <c r="L14" s="234"/>
+      <c r="D14" s="244"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="244"/>
+      <c r="G14" s="244"/>
+      <c r="H14" s="244"/>
+      <c r="I14" s="244"/>
+      <c r="J14" s="244"/>
+      <c r="K14" s="244"/>
+      <c r="L14" s="244"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22325,10 +22296,10 @@
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B26" s="251" t="s">
+      <c r="B26" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C26" s="252">
+      <c r="C26" s="234">
         <f>C23/(C24-C25)</f>
         <v>0</v>
       </c>
@@ -22385,54 +22356,54 @@
       <c r="D3" s="235"/>
       <c r="E3" s="235"/>
       <c r="F3" s="235"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>115</v>
       </c>
       <c r="I3" s="235"/>
       <c r="J3" s="235"/>
       <c r="K3" s="235"/>
       <c r="L3" s="235"/>
-      <c r="P3" s="233"/>
-      <c r="Q3" s="233"/>
-      <c r="R3" s="233"/>
-      <c r="S3" s="233"/>
-      <c r="T3" s="233"/>
-      <c r="U3" s="233"/>
-      <c r="V3" s="233"/>
-      <c r="W3" s="233"/>
-      <c r="X3" s="233"/>
-      <c r="Y3" s="233"/>
-      <c r="Z3" s="233"/>
+      <c r="P3" s="249"/>
+      <c r="Q3" s="249"/>
+      <c r="R3" s="249"/>
+      <c r="S3" s="249"/>
+      <c r="T3" s="249"/>
+      <c r="U3" s="249"/>
+      <c r="V3" s="249"/>
+      <c r="W3" s="249"/>
+      <c r="X3" s="249"/>
+      <c r="Y3" s="249"/>
+      <c r="Z3" s="249"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="234" t="s">
+      <c r="C5" s="244" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="234"/>
-      <c r="J5" s="234"/>
-      <c r="K5" s="234"/>
-      <c r="L5" s="234"/>
-      <c r="P5" s="233"/>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="233"/>
-      <c r="S5" s="233"/>
-      <c r="T5" s="233"/>
-      <c r="U5" s="233"/>
-      <c r="V5" s="233"/>
-      <c r="W5" s="233"/>
-      <c r="X5" s="233"/>
-      <c r="Y5" s="233"/>
-      <c r="Z5" s="233"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="249"/>
+      <c r="Y5" s="249"/>
+      <c r="Z5" s="249"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22567,7 +22538,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>104494.15193159635</v>
+        <v>104486.06119656235</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22621,23 +22592,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7674.0047783486025</v>
+        <v>7673.9565968950637</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7051.7718304175069</v>
+        <v>7051.6832812023267</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6479.991527835733</v>
+        <v>6479.8694741781574</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5954.5730081196907</v>
+        <v>5954.4234657156558</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5471.7571090513338</v>
+        <v>5471.5853383083804</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22656,15 +22627,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>62011.474597722168</v>
+        <v>62004.726667200972</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="248" t="s">
+      <c r="B14" s="250" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="249"/>
+      <c r="C14" s="251"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -22672,7 +22643,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>235.11500000000001</v>
+        <v>235.47</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22681,7 +22652,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>235.237620229887</v>
+        <v>235.21920809924762</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22691,20 +22662,20 @@
       <c r="C17" s="158">
         <v>0.02</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="252" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="248" t="s">
+      <c r="B19" s="250" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="249"/>
+      <c r="C19" s="251"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -22720,7 +22691,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11000257270833182</v>
+        <v>0.11000954193427279</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22738,7 +22709,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>93575.77</v>
+        <v>93717.06</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22765,15 +22736,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>94594.77</v>
+        <v>94736.06</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="248" t="s">
+      <c r="B28" s="250" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="249"/>
+      <c r="C28" s="251"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -22781,7 +22752,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>32632.098253772867</v>
+        <v>32631.518156299586</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22790,7 +22761,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>62011.474597722168</v>
+        <v>62004.726667200972</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22799,7 +22770,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>94643.572851495032</v>
+        <v>94636.244823500558</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22826,7 +22797,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>93624.572851495032</v>
+        <v>93617.244823500558</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22844,21 +22815,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>235.237620229887</v>
+        <v>235.21920809924762</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29372,7 +29343,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>235.11500000000001</v>
+        <v>235.47</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29443,7 +29414,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>235.11500000000001</v>
+        <v>235.47</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30749,7 +30720,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>13.450514874141879</v>
+        <v>13.470823798627004</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30786,7 +30757,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.8582448011746964</v>
+        <v>3.8640703627272006</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30847,7 +30818,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.1243071713839203</v>
+        <v>8.1365740579961798</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30908,7 +30879,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>93575.77</v>
+        <v>93717.06</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30969,7 +30940,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>94594.77</v>
+        <v>94736.06</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31006,7 +30977,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.7540586554488451</v>
+        <v>3.7596658464957535</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31043,7 +31014,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>10.406465346534654</v>
+        <v>10.422008800880088</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31178,7 +31149,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="94">AC153/AC157</f>
-        <v>11.440979337327303</v>
+        <v>11.458254065289156</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31215,7 +31186,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="94"/>
-        <v>11.654858624891773</v>
+        <v>11.672266722349072</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31252,7 +31223,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="97">AC157/AC153</f>
-        <v>8.7405104975358472E-2</v>
+        <v>8.7273331024255357E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31289,7 +31260,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.434659634646873E-2</v>
+        <v>7.4234509703996254E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31363,7 +31334,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>9.7461126956262287E-2</v>
+        <v>9.7314192314611664E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31400,7 +31371,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.7461126956262287E-2</v>
+        <v>9.7314192314611664E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31903,7 +31874,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.0889571093029744E-2</v>
+        <v>-1.0873153724626019E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33180,7 +33151,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>235.11500000000001</v>
+        <v>235.47</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33196,7 +33167,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>93575.77</v>
+        <v>93717.06</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33216,7 +33187,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>94594.77</v>
+        <v>94736.06</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33236,7 +33207,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.450514874141879</v>
+        <v>13.470823798627004</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33256,7 +33227,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.8582448011746964</v>
+        <v>3.8640703627272006</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33276,7 +33247,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.1243071713839203</v>
+        <v>8.1365740579961798</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33296,7 +33267,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.7540586554488451</v>
+        <v>3.7596658464957535</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33305,7 +33276,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.406465346534654</v>
+        <v>10.422008800880088</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33541,7 +33512,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.434659634646873E-2</v>
+        <v>7.4234509703996254E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -33557,7 +33528,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>8.7405104975358472E-2</v>
+        <v>8.7273331024255357E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -33589,7 +33560,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.7461126956262287E-2</v>
+        <v>9.7314192314611664E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33598,7 +33569,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.7461126956262287E-2</v>
+        <v>9.7314192314611664E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33642,7 +33613,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0889571093029744E-2</v>
+        <v>-1.0873153724626019E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33821,7 +33792,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>235.11500000000001</v>
+        <v>235.47</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33850,7 +33821,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>93575.77</v>
+        <v>93717.06</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33879,7 +33850,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>94594.77</v>
+        <v>94736.06</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33908,7 +33879,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.450514874141879</v>
+        <v>13.470823798627004</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33937,7 +33908,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.8582448011746964</v>
+        <v>3.8640703627272006</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33966,7 +33937,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.1243071713839203</v>
+        <v>8.1365740579961798</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33995,7 +33966,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.7540586554488451</v>
+        <v>3.7596658464957535</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34024,7 +33995,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.406465346534654</v>
+        <v>10.422008800880088</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34797,7 +34768,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.434659634646873E-2</v>
+        <v>7.4234509703996254E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34826,7 +34797,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>8.7405104975358472E-2</v>
+        <v>8.7273331024255357E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34884,7 +34855,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.7461126956262287E-2</v>
+        <v>9.7314192314611664E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34913,7 +34884,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.7461126956262287E-2</v>
+        <v>9.7314192314611664E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35149,7 +35120,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-1.0889571093029744E-2</v>
+        <v>-1.0873153724626019E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35709,19 +35680,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="239">
         <f>Statement!AA89</f>
         <v>3.4385745545482967E-2</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1268516941937681</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -35748,19 +35719,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="239">
         <f>Statement!AA90</f>
         <v>7.6807228915662648E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1206896551724138</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -35787,19 +35758,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="239">
         <f>Statement!AA91</f>
         <v>2.9473317056156263E-2</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12760267430754538</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -35826,19 +35797,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="239">
         <f>Statement!AA95</f>
         <v>0.10524728588661038</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.172424824056302</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -35865,19 +35836,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="239">
         <f>Statement!AA96</f>
         <v>-7.4441687344913146E-2</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>6.1166429587482217E-2</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -35904,19 +35875,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="239">
         <f>Statement!AA98</f>
         <v>-9.3700370566437263E-2</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.2418687167356593E-2</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -35943,22 +35914,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.1897810218978103E-2</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.2937062937062943E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -35985,22 +35956,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-7.6086956521739066E-2</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>7.8680203045685293E-2</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36048,22 +36019,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>3.5172636334301385E-2</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13738698812267328</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36090,22 +36061,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-1.1111111111111112E-2</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36132,49 +36103,49 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.21527777777777779</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1004C7-F8DA-EB43-9C62-09864B1797E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C803504-3E88-1F49-BE87-FEDB69355E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="418">
   <si>
     <t>Ticker</t>
   </si>
@@ -1391,6 +1391,21 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>EV/Sales price</t>
   </si>
 </sst>
 </file>
@@ -2357,14 +2372,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12769,11 +12784,11 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.4074</v>
+    <v>1.401</v>
     <v>-3.46</v>
     <v>-1.4480999999999999E-2</v>
-    <v>0.1835</v>
-    <v>7.7930000000000002E-4</v>
+    <v>0.22</v>
+    <v>9.343E-4</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12785,21 +12800,21 @@
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46290.841048911716</v>
+    <v>46290.99926767344</v>
     <v>4</v>
     <v>234.96</v>
     <v>91644924000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
     <v>238.85</v>
-    <v>13.139799999999999</v>
+    <v>13.3329</v>
     <v>238.93</v>
     <v>235.47</v>
-    <v>235.65350000000001</v>
+    <v>235.69</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>3092658</v>
+    <v>3115375</v>
     <v>5303349</v>
     <v>1997</v>
   </rv>
@@ -12822,19 +12837,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>7</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13076,9 +13091,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13699,7 +13714,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>300.02121860664784</v>
+        <v>300.24524605053278</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13723,7 +13738,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>393.35077635092063</v>
+        <v>393.45341640559127</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13756,7 +13771,7 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>235.65350000000001</v>
+        <v>235.69</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
@@ -13771,7 +13786,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>367.89735085887645</v>
+        <v>367.99270939322611</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13790,12 +13805,12 @@
         <v>3.8640703627272006</v>
       </c>
       <c r="H7" s="182" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="210">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>346.16524848319403</v>
+        <f ca="1">'AVG target price'!C10</f>
+        <v>350.12640339541497</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13804,7 +13819,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.1835</v>
+        <v>0.22</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
@@ -13814,12 +13829,12 @@
         <v>8.7273331024255357E-2</v>
       </c>
       <c r="H8" s="182" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="211">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>0.47010340375926463</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>0.48692573744177592</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13844,7 +13859,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>7.7930000000000002E-4</v>
+        <v>9.343E-4</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
@@ -13899,7 +13914,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4074</v>
+        <v>1.401</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -14041,7 +14056,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14056,7 +14071,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19884,7 +19899,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19893,7 +19908,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4074</v>
+        <v>1.401</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19963,7 +19978,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.114953</v>
+        <v>0.11488500000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19972,7 +19987,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11000954193427279</v>
+        <v>0.10994604423324912</v>
       </c>
     </row>
   </sheetData>
@@ -20223,7 +20238,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>140647.37417341626</v>
+        <v>140746.66464239862</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20277,23 +20292,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7309.4822224072295</v>
+        <v>7309.9003826585385</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7445.3769222875871</v>
+        <v>7446.2288156624181</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7447.8994163874986</v>
+        <v>7449.1777259460423</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7395.6706522236691</v>
+        <v>7397.3631611014553</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7365.2322767829273</v>
+        <v>7367.3392658209714</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20312,7 +20327,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>83463.783515356932</v>
+        <v>83546.598576922624</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20335,7 +20350,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11000954193427279</v>
+        <v>0.10994604423324912</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20350,7 +20365,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>36963.661490088911</v>
+        <v>36970.009351189423</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20359,7 +20374,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>83463.783515356932</v>
+        <v>83546.598576922624</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20368,7 +20383,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>120427.44500544584</v>
+        <v>120516.60792811205</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20395,7 +20410,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119408.44500544584</v>
+        <v>119497.60792811205</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20413,7 +20428,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>300.02121860664784</v>
+        <v>300.24524605053278</v>
       </c>
     </row>
   </sheetData>
@@ -20434,7 +20449,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -20682,23 +20697,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7309.4822224072295</v>
+        <v>7309.9003826585385</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7445.3769222875871</v>
+        <v>7446.2288156624181</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7447.8994163874986</v>
+        <v>7449.1777259460423</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7395.6706522236691</v>
+        <v>7397.3631611014553</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7365.2322767829273</v>
+        <v>7367.3392658209714</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21426,291 +21441,427 @@
       <c r="N35" s="91"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="C36" s="149">
+        <f>C33/C6</f>
+        <v>20.367391827684507</v>
+      </c>
+      <c r="D36" s="149">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>9.0939912529819384</v>
+      </c>
+      <c r="E36" s="149">
+        <f t="shared" si="14"/>
+        <v>14.232860528620741</v>
+      </c>
+      <c r="F36" s="149">
+        <f t="shared" si="14"/>
+        <v>10.64812834224599</v>
+      </c>
+      <c r="G36" s="150">
+        <f t="shared" si="14"/>
+        <v>5.6879145104968645</v>
+      </c>
+      <c r="H36" s="139"/>
+      <c r="I36" s="139"/>
+      <c r="J36" s="139"/>
+      <c r="K36" s="139"/>
+      <c r="L36" s="139"/>
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="235" t="s">
+      <c r="N38" s="91"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="235" t="s">
         <v>206</v>
       </c>
-      <c r="C38" s="235"/>
-      <c r="N38" s="91"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="235"/>
+      <c r="N39" s="91"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>14376.880278018019</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C40" s="137">
+      <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11000954193427279</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+        <v>0.10994604423324912</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="C41" s="105">
+      <c r="C42" s="105">
         <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>215653.2041702703</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>215653.2041702703</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5</f>
-        <v>127974.17977436041</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="24">
+        <f ca="1">C43/(1+C41)^5</f>
+        <v>128010.78964405687</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="C44" s="108">
-        <f ca="1">SUM(H9:K9)+C43</f>
-        <v>157572.6089876664</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="108">
+        <f ca="1">SUM(H9:K9)+C44</f>
+        <v>157613.45972942532</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C45" s="88">
+      <c r="C46" s="88">
         <f>Statement!AC107</f>
         <v>5626</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C46" s="88">
+      <c r="C47" s="88">
         <f>Statement!AC108</f>
         <v>6645</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="C47" s="108">
-        <f ca="1">C44+C45-C46</f>
-        <v>156553.6089876664</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="108">
+        <f ca="1">C45+C46-C47</f>
+        <v>156594.45972942532</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C49" s="88">
         <f>Statement!AC78</f>
         <v>398</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="233" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="234">
-        <f ca="1">C47/C48</f>
-        <v>393.35077635092063</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="C50" s="234">
+        <f ca="1">C48/C49</f>
+        <v>393.45341640559127</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="235" t="s">
         <v>211</v>
       </c>
-      <c r="C51" s="235"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="235"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>39388.713090460325</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C53" s="137">
+      <c r="C54" s="137">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="C54" s="105">
+      <c r="C55" s="105">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>378.13734504559994</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
         <v>520.82548320783292</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="233" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="234">
-        <f>C56/(1+C53)^5</f>
+      <c r="C58" s="234">
+        <f>C57/(1+C54)^5</f>
         <v>323.39164811633128</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="235" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="235" t="s">
         <v>323</v>
       </c>
-      <c r="C59" s="235"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="235"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>12411.378160399478</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C61" s="137">
+      <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11000954193427279</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+        <v>0.10994604423324912</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>351</v>
       </c>
-      <c r="C62" s="105">
+      <c r="C63" s="105">
         <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>198582.05056639164</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>198582.05056639164</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5</f>
-        <v>117843.71642852684</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+      <c r="C65" s="24">
+        <f ca="1">C64/(1+C62)^5</f>
+        <v>117877.42825313554</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="C65" s="108">
-        <f ca="1">SUM(H9:K9)+C64</f>
-        <v>147442.14564183282</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="108">
+        <f ca="1">SUM(H9:K9)+C65</f>
+        <v>147480.098338504</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C66" s="88">
+      <c r="C67" s="88">
         <f>Statement!AC107</f>
         <v>5626</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C67" s="88">
+      <c r="C68" s="88">
         <f>Statement!AC108</f>
         <v>6645</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="C68" s="108">
-        <f ca="1">C65+C66-C67</f>
-        <v>146423.14564183282</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="108">
+        <f ca="1">C66+C67-C68</f>
+        <v>146461.098338504</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="88">
+      <c r="C70" s="88">
         <f>Statement!AC78</f>
         <v>398</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="233" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="234">
-        <f ca="1">C68/C69</f>
-        <v>367.89735085887645</v>
+      <c r="C71" s="234">
+        <f ca="1">C69/C70</f>
+        <v>367.99270939322611</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="235" t="s">
+        <v>414</v>
+      </c>
+      <c r="C73" s="235"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>39388.713090460325</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C75" s="137">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.10994604423324912</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="C76" s="105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>196943.56545230164</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C78" s="24">
+        <f ca="1">C77/(1+C75)^5</f>
+        <v>116904.8307251661</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="C79" s="108">
+        <f ca="1">SUM(H9:K9)+C78</f>
+        <v>146507.50081053455</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C80" s="88">
+        <f>Statement!AC107</f>
+        <v>5626</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C81" s="88">
+        <f>Statement!AC108</f>
+        <v>6645</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C82" s="108">
+        <f ca="1">C79+C80-C81</f>
+        <v>145488.50081053455</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C83" s="88">
+        <f>Statement!AC78</f>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="233" t="s">
+        <v>210</v>
+      </c>
+      <c r="C84" s="234">
+        <f ca="1">C82/C83</f>
+        <v>365.54899701139334</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+  <mergeCells count="11">
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21721,7 +21872,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -21760,7 +21911,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>300.02121860664784</v>
+        <v>300.24524605053278</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21768,8 +21919,8 @@
         <v>217</v>
       </c>
       <c r="C6" s="135">
-        <f ca="1">Multiples!C49</f>
-        <v>393.35077635092063</v>
+        <f ca="1">Multiples!C50</f>
+        <v>393.45341640559127</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21777,7 +21928,7 @@
         <v>218</v>
       </c>
       <c r="C7" s="135">
-        <f>Multiples!C57</f>
+        <f>Multiples!C58</f>
         <v>323.39164811633128</v>
       </c>
     </row>
@@ -21786,35 +21937,44 @@
         <v>324</v>
       </c>
       <c r="C8" s="135">
-        <f ca="1">Multiples!C70</f>
-        <v>367.89735085887645</v>
+        <f ca="1">Multiples!C71</f>
+        <v>367.99270939322611</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="233" t="s">
+      <c r="B9" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9" s="135">
+        <f ca="1">Multiples!C84</f>
+        <v>365.54899701139334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="233" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="234">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>346.16524848319403</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="234">
+        <f ca="1">AVERAGE(C5:C9)</f>
+        <v>350.12640339541497</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="135">
+      <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
         <v>235.47</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="154">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>0.47010340375926463</v>
+      <c r="C12" s="154">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>0.48692573744177592</v>
       </c>
     </row>
   </sheetData>
@@ -22538,7 +22698,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>104486.06119656235</v>
+        <v>104559.82346961791</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22592,23 +22752,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7673.9565968950637</v>
+        <v>7674.3956079660884</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7051.6832812023267</v>
+        <v>7052.4901285025189</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6479.8694741781574</v>
+        <v>6480.9816373028007</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5954.4234657156558</v>
+        <v>5955.7861432944346</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5471.5853383083804</v>
+        <v>5473.1506073854844</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22627,15 +22787,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>62004.726667200972</v>
+        <v>62066.249462358748</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="250" t="s">
+      <c r="B14" s="251" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="251"/>
+      <c r="C14" s="252"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -22652,7 +22812,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>235.21920809924762</v>
+        <v>235.38706931359314</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22662,20 +22822,20 @@
       <c r="C17" s="158">
         <v>0.02</v>
       </c>
-      <c r="E17" s="252" t="s">
+      <c r="E17" s="250" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="250" t="s">
+      <c r="B19" s="251" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="251"/>
+      <c r="C19" s="252"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -22691,7 +22851,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11000954193427279</v>
+        <v>0.10994604423324912</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22741,10 +22901,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="250" t="s">
+      <c r="B28" s="251" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="251"/>
+      <c r="C28" s="252"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -22752,7 +22912,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>32631.518156299586</v>
+        <v>32636.804124451326</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22761,7 +22921,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>62004.726667200972</v>
+        <v>62066.249462358748</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22770,7 +22930,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>94636.244823500558</v>
+        <v>94703.053586810071</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22797,7 +22957,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>93617.244823500558</v>
+        <v>93684.053586810071</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22815,7 +22975,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>235.21920809924762</v>
+        <v>235.38706931359314</v>
       </c>
     </row>
   </sheetData>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A244D6-8A97-9047-922A-B596EC87DCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4109C6DD-128E-3448-ABF3-E0F3E14A9E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2339,6 +2339,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2346,12 +2352,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2372,14 +2372,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12784,11 +12784,11 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.4132</v>
-    <v>2.16</v>
-    <v>9.3500000000000007E-3</v>
-    <v>-0.17</v>
-    <v>-7.291E-4</v>
+    <v>1.4151</v>
+    <v>1.34</v>
+    <v>5.5849999999999997E-3</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12796,26 +12796,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>233.33</v>
+    <v>248.3</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46294.967140474218</v>
+    <v>46296.853922048438</v>
     <v>4</v>
-    <v>228.68</v>
-    <v>90749764000</v>
+    <v>237.785</v>
+    <v>93906176000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>230.99</v>
-    <v>13.0115</v>
-    <v>231.01</v>
-    <v>233.17</v>
-    <v>233</v>
+    <v>245.93</v>
+    <v>13.4641</v>
+    <v>239.94</v>
+    <v>241.28</v>
+    <v>241.28</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>4106077</v>
-    <v>5357999</v>
+    <v>4493895</v>
+    <v>5433492</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12837,19 +12837,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.93</v>
+    <v>53.06</v>
     <v>39.47</v>
-    <v>0.15</v>
-    <v>2.8630000000000001E-3</v>
+    <v>0.38</v>
+    <v>7.2309999999999996E-3</v>
     <v>US</v>
-    <v>52.93</v>
+    <v>53.06</v>
     <v>Index</v>
     <v>7</v>
-    <v>52.13</v>
+    <v>52.05</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.13</v>
-    <v>52.4</v>
+    <v>52.43</v>
     <v>52.55</v>
+    <v>52.93</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>90936.299999999988</v>
+        <v>94099.199999999997</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>302.16779774520745</v>
+        <v>300.15494694544896</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>91660.299999999988</v>
+        <v>94823.2</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>400.31012162357183</v>
+        <v>399.35929119576576</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>233.17</v>
+        <v>241.28</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>301.30218246299063</v>
+        <v>300.6746610567622</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13771,14 +13771,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>233</v>
+        <v>241.28</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>13.011718749999998</v>
+        <v>13.464285714285714</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>374.74495488717514</v>
+        <v>373.86081166709221</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13795,14 +13795,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>2.16</v>
+        <v>1.34</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>3.6474898921832883</v>
+        <v>3.7743550250288798</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>371.97816383726149</v>
+        <v>371.10123784252954</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13819,14 +13819,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>9.2911191680330088E-2</v>
+        <v>8.9788223491804403E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>350.10064411124131</v>
+        <v>349.03018974151979</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13843,14 +13843,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>9.3500000000000007E-3</v>
+        <v>5.5849999999999997E-3</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>7.6853797658360867E-2</v>
+        <v>7.4270557029177731E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.50148236956401482</v>
+        <v>0.44657737790749252</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13867,14 +13867,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-7.291E-4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>0.10221440722791669</v>
+        <v>9.8778735632183909E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4132</v>
+        <v>1.4151</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5357999</v>
+        <v>5433492</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.9616170880055601E-3</v>
+        <v>-7.6940080255730129E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.55</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2929999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18722,6 +18722,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18729,12 +18735,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19794,16 +19794,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19886,7 +19886,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>233.17</v>
+        <v>241.28</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>90936.299999999988</v>
+        <v>94099.199999999997</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19913,7 +19913,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2929999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4132</v>
+        <v>1.4151</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.5396153929164966E-2</v>
+        <v>6.333725520643585E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93460384607083502</v>
+        <v>0.93666274479356415</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19992,7 +19992,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.116144</v>
+        <v>0.1166095</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1115450808710854</v>
+        <v>0.11212588737256401</v>
       </c>
     </row>
   </sheetData>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>138710.29371196657</v>
+        <v>137835.79640499235</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20306,23 +20306,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7212.3476804721704</v>
+        <v>7208.5810399584425</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7452.4629246393633</v>
+        <v>7444.6808763899699</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7441.9708516312994</v>
+        <v>7430.3172569530725</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7378.5599486205601</v>
+        <v>7363.1582404203027</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7336.8244375396816</v>
+        <v>7317.6861960277602</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20341,7 +20341,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>81747.275277727851</v>
+        <v>81020.005698975554</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1115450808710854</v>
+        <v>0.11212588737256401</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>36822.165842903072</v>
+        <v>36764.423609749545</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>81747.275277727851</v>
+        <v>81020.005698975554</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>118569.44112063092</v>
+        <v>117784.4293087251</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>117845.44112063092</v>
+        <v>117060.4293087251</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>302.16779774520745</v>
+        <v>300.15494694544896</v>
       </c>
     </row>
   </sheetData>
@@ -20711,23 +20711,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7212.3476804721704</v>
+        <v>7208.5810399584425</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7452.4629246393633</v>
+        <v>7444.6808763899699</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7441.9708516312994</v>
+        <v>7430.3172569530725</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7378.5599486205601</v>
+        <v>7363.1582404203027</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7336.8244375396816</v>
+        <v>7317.6861960277602</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1115450808710854</v>
+        <v>0.11212588737256401</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>127359.60602782961</v>
+        <v>127027.38615262687</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>156844.94743319301</v>
+        <v>156474.12356634866</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>156120.94743319301</v>
+        <v>155750.12356634866</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>400.31012162357183</v>
+        <v>399.35929119576576</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.116144</v>
+        <v>0.1166095</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>301.30218246299063</v>
+        <v>300.6746610567622</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1115450808710854</v>
+        <v>0.11212588737256401</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>117389.19100063491</v>
+        <v>117082.97913644416</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>146874.5324059983</v>
+        <v>146529.71655016596</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>146150.5324059983</v>
+        <v>145805.71655016596</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>374.74495488717514</v>
+        <v>373.86081166709221</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1115450808710854</v>
+        <v>0.11212588737256401</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>116310.14249116858</v>
+        <v>116006.74534486473</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>145795.48389653198</v>
+        <v>145453.48275858653</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>145071.48389653198</v>
+        <v>144729.48275858653</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21860,22 +21860,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>371.97816383726149</v>
+        <v>371.10123784252954</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>302.16779774520745</v>
+        <v>300.15494694544896</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>400.31012162357183</v>
+        <v>399.35929119576576</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21943,7 +21943,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>301.30218246299063</v>
+        <v>300.6746610567622</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>374.74495488717514</v>
+        <v>373.86081166709221</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>371.97816383726149</v>
+        <v>371.10123784252954</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>350.10064411124131</v>
+        <v>349.03018974151979</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>233.17</v>
+        <v>241.28</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.50148236956401482</v>
+        <v>0.44657737790749252</v>
       </c>
     </row>
   </sheetData>
@@ -22458,7 +22458,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.116144</v>
+        <v>0.1166095</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22712,7 +22712,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>102733.45566282053</v>
+        <v>102085.77388009828</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22766,23 +22766,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7663.3554441782453</v>
+        <v>7659.3532653640859</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7032.2137064707731</v>
+        <v>7024.8704929697878</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6453.051796135007</v>
+        <v>6442.9467780465147</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5921.5887374531831</v>
+        <v>5909.2282521482912</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5433.8961290430607</v>
+        <v>5419.7217110297006</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22801,15 +22801,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>60544.750180831936</v>
+        <v>60006.110148976659</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="250" t="s">
+      <c r="B14" s="251" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="251"/>
+      <c r="C14" s="252"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>233.17</v>
+        <v>241.28</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22826,7 +22826,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>237.33896142445298</v>
+        <v>235.83092711705666</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22836,20 +22836,20 @@
       <c r="C17" s="158">
         <v>0.02</v>
       </c>
-      <c r="E17" s="252" t="s">
+      <c r="E17" s="250" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="250" t="s">
+      <c r="B19" s="251" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="251"/>
+      <c r="C19" s="252"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1115450808710854</v>
+        <v>0.11212588737256401</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>90703.12999999999</v>
+        <v>93857.919999999998</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22910,15 +22910,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>91427.12999999999</v>
+        <v>94581.92</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="250" t="s">
+      <c r="B28" s="251" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="251"/>
+      <c r="C28" s="252"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>32504.105813280265</v>
+        <v>32456.120499558383</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>60544.750180831936</v>
+        <v>60006.110148976659</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>93048.855994112208</v>
+        <v>92462.230648535042</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>92324.855994112208</v>
+        <v>91738.230648535042</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22989,21 +22989,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>237.33896142445298</v>
+        <v>235.83092711705666</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29608,7 +29608,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>233.17</v>
+        <v>241.28</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>233.17</v>
+        <v>241.28</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30985,7 +30985,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>13.011718749999998</v>
+        <v>13.464285714285714</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31022,7 +31022,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.6474898921832883</v>
+        <v>3.7743550250288798</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31083,7 +31083,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.710228663719823</v>
+        <v>7.9784019041142473</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31144,7 +31144,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>90936.299999999988</v>
+        <v>94099.199999999997</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31205,7 +31205,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>91660.299999999988</v>
+        <v>94823.2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31242,7 +31242,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.5294686176357333</v>
+        <v>3.6512591451675007</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31279,7 +31279,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>9.8867759680724827</v>
+        <v>10.227936576421097</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31414,7 +31414,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>10.762966031483014</v>
+        <v>11.13731802580187</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31451,7 +31451,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>11.146614249274601</v>
+        <v>11.531247795193943</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31488,7 +31488,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>9.2911191680330088E-2</v>
+        <v>8.9788223491804403E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31525,7 +31525,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.6853797658360867E-2</v>
+        <v>7.4270557029177731E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31599,7 +31599,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>0.10221440722791669</v>
+        <v>9.8778735632183909E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31636,7 +31636,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>0.10221440722791669</v>
+        <v>9.8778735632183909E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32139,7 +32139,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.9616170880055601E-3</v>
+        <v>-7.6940080255730129E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33437,7 +33437,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>233.17</v>
+        <v>241.28</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33453,7 +33453,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>90936.299999999988</v>
+        <v>94099.199999999997</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33473,7 +33473,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>91660.299999999988</v>
+        <v>94823.2</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33493,7 +33493,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.011718749999998</v>
+        <v>13.464285714285714</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33513,7 +33513,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.6474898921832883</v>
+        <v>3.7743550250288798</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33533,7 +33533,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>7.710228663719823</v>
+        <v>7.9784019041142473</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33553,7 +33553,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.5294686176357333</v>
+        <v>3.6512591451675007</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>9.8867759680724827</v>
+        <v>10.227936576421097</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.6853797658360867E-2</v>
+        <v>7.4270557029177731E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -33814,7 +33814,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>9.2911191680330088E-2</v>
+        <v>8.9788223491804403E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -33846,7 +33846,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>0.10221440722791669</v>
+        <v>9.8778735632183909E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>0.10221440722791669</v>
+        <v>9.8778735632183909E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.9616170880055601E-3</v>
+        <v>-7.6940080255730129E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34078,7 +34078,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>233.17</v>
+        <v>241.28</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>90936.299999999988</v>
+        <v>94099.199999999997</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>91660.299999999988</v>
+        <v>94823.2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34165,7 +34165,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.011718749999998</v>
+        <v>13.464285714285714</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34194,7 +34194,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.6474898921832883</v>
+        <v>3.7743550250288798</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34223,7 +34223,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>7.710228663719823</v>
+        <v>7.9784019041142473</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.5294686176357333</v>
+        <v>3.6512591451675007</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>9.8867759680724827</v>
+        <v>10.227936576421097</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35054,7 +35054,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.6853797658360867E-2</v>
+        <v>7.4270557029177731E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>9.2911191680330088E-2</v>
+        <v>8.9788223491804403E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35141,7 +35141,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>0.10221440722791669</v>
+        <v>9.8778735632183909E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35170,7 +35170,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>0.10221440722791669</v>
+        <v>9.8778735632183909E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35406,7 +35406,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.9616170880055601E-3</v>
+        <v>-7.6940080255730129E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35892,14 +35892,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="241" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35966,19 +35966,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="242">
+      <c r="C7" s="239">
         <f>Statement!AA89</f>
         <v>2.1456633423995165E-2</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="F7" s="242">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12892451569806279</v>
       </c>
-      <c r="G7" s="243"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -36005,19 +36005,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="242">
+      <c r="C9" s="239">
         <f>Statement!AA90</f>
         <v>6.7132867132867133E-2</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="F9" s="242">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18847352024922118</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -36044,19 +36044,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="242">
+      <c r="C11" s="239">
         <f>Statement!AA91</f>
         <v>1.5924106386583092E-2</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="F11" s="242">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12177328843995511</v>
       </c>
-      <c r="G11" s="243"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -36083,19 +36083,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="239">
         <f>Statement!AA95</f>
         <v>-6.0027285129604369E-3</v>
       </c>
-      <c r="D13" s="243"/>
-      <c r="F13" s="242">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.14812480302552788</v>
       </c>
-      <c r="G13" s="243"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -36122,19 +36122,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="242">
+      <c r="C15" s="239">
         <f>Statement!AA96</f>
         <v>5.1831992850759609E-2</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="F15" s="242">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>8.3294983893235156E-2</v>
       </c>
-      <c r="G15" s="243"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -36161,19 +36161,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="242">
+      <c r="C17" s="239">
         <f>Statement!AA98</f>
         <v>6.7172897196261683E-2</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="F17" s="242">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>3.1038374717832957E-2</v>
       </c>
-      <c r="G17" s="243"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -36200,22 +36200,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="242">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.7412935323383085E-2</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="F19" s="242">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.8396226415094338E-2</v>
       </c>
-      <c r="G19" s="243"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -36242,22 +36242,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="242">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>8.7058823529411786E-2</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="F21" s="242">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.10526315789473695</v>
       </c>
-      <c r="G21" s="243"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36305,22 +36305,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="242">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.5872817955112218E-2</v>
       </c>
-      <c r="D25" s="243"/>
-      <c r="F25" s="242">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13659126230357452</v>
       </c>
-      <c r="G25" s="243"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36347,22 +36347,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="242">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.24719101123595505</v>
       </c>
-      <c r="D27" s="243"/>
-      <c r="F27" s="242">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-1.4705882352941176E-2</v>
       </c>
-      <c r="G27" s="243"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36389,49 +36389,49 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="242">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.7699115044247787E-2</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="F29" s="242">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.13953488372093023</v>
       </c>
-      <c r="G29" s="243"/>
+      <c r="G29" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4109C6DD-128E-3448-ABF3-E0F3E14A9E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF9CFF1-0569-4F4C-A57C-D226DB6BEFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2339,12 +2339,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2352,6 +2346,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2372,14 +2372,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12784,11 +12784,11 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.4151</v>
-    <v>1.34</v>
-    <v>5.5849999999999997E-3</v>
-    <v>0</v>
-    <v>0</v>
+    <v>1.387</v>
+    <v>1.095</v>
+    <v>4.607E-3</v>
+    <v>-0.33500000000000002</v>
+    <v>-1.4030000000000002E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12796,26 +12796,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>248.3</v>
+    <v>241</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46296.853922048438</v>
+    <v>46300.890774189065</v>
     <v>4</v>
-    <v>237.785</v>
-    <v>93906176000</v>
+    <v>235.51</v>
+    <v>92935122000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>245.93</v>
-    <v>13.4641</v>
-    <v>239.94</v>
-    <v>241.28</v>
-    <v>241.28</v>
+    <v>238.68</v>
+    <v>13.3248</v>
+    <v>237.69</v>
+    <v>238.785</v>
+    <v>238.45</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>4493895</v>
-    <v>5433492</v>
+    <v>3288539</v>
+    <v>5342234</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12837,19 +12837,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.06</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.2309999999999996E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>53.06</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>7</v>
-    <v>52.05</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.43</v>
-    <v>52.55</v>
-    <v>52.93</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>94099.199999999997</v>
+        <v>93126.15</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>300.15494694544896</v>
+        <v>304.97016020039513</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>94823.2</v>
+        <v>93850.15</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>399.35929119576576</v>
+        <v>401.61864881029658</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>241.28</v>
+        <v>238.785</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>300.6746610567622</v>
+        <v>302.59993208221965</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13771,14 +13771,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>241.28</v>
+        <v>238.45</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>13.464285714285714</v>
+        <v>13.325055803571427</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>373.86081166709221</v>
+        <v>375.96169571522699</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13795,14 +13795,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.34</v>
+        <v>1.095</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>3.7743550250288798</v>
+        <v>3.7353256160954946</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>371.10123784252954</v>
+        <v>373.18497108348703</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13819,14 +13819,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-0.33500000000000002</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>8.9788223491804403E-2</v>
+        <v>9.0726396398863263E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>349.03018974151979</v>
+        <v>351.66708157832505</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13843,14 +13843,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>5.5849999999999997E-3</v>
+        <v>4.607E-3</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>7.4270557029177731E-2</v>
+        <v>7.5046590028686896E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.44657737790749252</v>
+        <v>0.47273522867150392</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13867,14 +13867,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>-1.4030000000000002E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>9.8778735632183909E-2</v>
+        <v>9.9810847973421005E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.4151</v>
+        <v>1.387</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5433492</v>
+        <v>5342234</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.6940080255730129E-3</v>
+        <v>-7.7744006382739978E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.93</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.2929999999999998E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18722,12 +18722,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18735,6 +18729,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19794,16 +19794,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19886,7 +19886,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>241.28</v>
+        <v>238.785</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>94099.199999999997</v>
+        <v>93126.15</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19913,7 +19913,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2929999999999998E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.4151</v>
+        <v>1.387</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.333725520643585E-2</v>
+        <v>6.3956722919031872E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93666274479356415</v>
+        <v>0.93604327708096813</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19992,7 +19992,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1166095</v>
+        <v>0.11518500000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11212588737256401</v>
+        <v>0.11074864191472136</v>
       </c>
     </row>
   </sheetData>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>137835.79640499235</v>
+        <v>139927.65938521514</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20306,23 +20306,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7208.5810399584425</v>
+        <v>7217.5191427119689</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7444.6808763899699</v>
+        <v>7463.1540198309513</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7430.3172569530725</v>
+        <v>7457.9906589265456</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7363.1582404203027</v>
+        <v>7399.7452857671169</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7317.6861960277602</v>
+        <v>7363.165763856372</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20341,7 +20341,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>81020.005698975554</v>
+        <v>82760.787607061138</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11212588737256401</v>
+        <v>0.11074864191472136</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>36764.423609749545</v>
+        <v>36901.574871092955</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>81020.005698975554</v>
+        <v>82760.787607061138</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>117784.4293087251</v>
+        <v>119662.3624781541</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>117060.4293087251</v>
+        <v>118938.3624781541</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>300.15494694544896</v>
+        <v>304.97016020039513</v>
       </c>
     </row>
   </sheetData>
@@ -20711,23 +20711,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7208.5810399584425</v>
+        <v>7217.5191427119689</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7444.6808763899699</v>
+        <v>7463.1540198309513</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7430.3172569530725</v>
+        <v>7457.9906589265456</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7363.1582404203027</v>
+        <v>7399.7452857671169</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7317.6861960277602</v>
+        <v>7363.165763856372</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11212588737256401</v>
+        <v>0.11074864191472136</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>127027.38615262687</v>
+        <v>127816.86392877909</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>156474.12356634866</v>
+        <v>157355.27303601566</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>155750.12356634866</v>
+        <v>156631.27303601566</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>399.35929119576576</v>
+        <v>401.61864881029658</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1166095</v>
+        <v>0.11518500000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>300.6746610567622</v>
+        <v>302.59993208221965</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11212588737256401</v>
+        <v>0.11074864191472136</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>117082.97913644416</v>
+        <v>117810.65222170195</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>146529.71655016596</v>
+        <v>147349.06132893852</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>145805.71655016596</v>
+        <v>146625.06132893852</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>373.86081166709221</v>
+        <v>375.96169571522699</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11212588737256401</v>
+        <v>0.11074864191472136</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>116006.74534486473</v>
+        <v>116727.72961532336</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>145453.48275858653</v>
+        <v>146266.13872255993</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>144729.48275858653</v>
+        <v>145542.13872255993</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21860,22 +21860,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>371.10123784252954</v>
+        <v>373.18497108348703</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>300.15494694544896</v>
+        <v>304.97016020039513</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>399.35929119576576</v>
+        <v>401.61864881029658</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21943,7 +21943,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>300.6746610567622</v>
+        <v>302.59993208221965</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>373.86081166709221</v>
+        <v>375.96169571522699</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>371.10123784252954</v>
+        <v>373.18497108348703</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>349.03018974151979</v>
+        <v>351.66708157832505</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>241.28</v>
+        <v>238.785</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.44657737790749252</v>
+        <v>0.47273522867150392</v>
       </c>
     </row>
   </sheetData>
@@ -22458,7 +22458,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1166095</v>
+        <v>0.11518500000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22712,7 +22712,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>102085.77388009828</v>
+        <v>103635.07715803427</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22766,23 +22766,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7659.3532653640859</v>
+        <v>7668.8502920510155</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7024.8704929697878</v>
+        <v>7042.3019238700035</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6442.9467780465147</v>
+        <v>6466.9428269252803</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5909.2282521482912</v>
+        <v>5938.5908157340064</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5419.7217110297006</v>
+        <v>5453.4053911665687</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22801,15 +22801,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>60006.110148976659</v>
+        <v>61295.39111138531</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="251" t="s">
+      <c r="B14" s="250" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="252"/>
+      <c r="C14" s="251"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>241.28</v>
+        <v>238.785</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22826,7 +22826,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>235.83092711705666</v>
+        <v>239.43825799776909</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22836,20 +22836,20 @@
       <c r="C17" s="158">
         <v>0.02</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="252" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="251" t="s">
+      <c r="B19" s="250" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="252"/>
+      <c r="C19" s="251"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11212588737256401</v>
+        <v>0.11074864191472136</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>93857.919999999998</v>
+        <v>92887.365000000005</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22910,15 +22910,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>94581.92</v>
+        <v>93611.365000000005</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="251" t="s">
+      <c r="B28" s="250" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="251"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>32456.120499558383</v>
+        <v>32570.091249746871</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>60006.110148976659</v>
+        <v>61295.39111138531</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>92462.230648535042</v>
+        <v>93865.482361132177</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>91738.230648535042</v>
+        <v>93141.482361132177</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22989,21 +22989,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>235.83092711705666</v>
+        <v>239.43825799776909</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29608,7 +29608,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>241.28</v>
+        <v>238.785</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>241.28</v>
+        <v>238.785</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30985,7 +30985,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>13.464285714285714</v>
+        <v>13.325055803571427</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31022,7 +31022,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7743550250288798</v>
+        <v>3.7353256160954946</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31083,7 +31083,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.9784019041142473</v>
+        <v>7.8958997789867391</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31144,7 +31144,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>94099.199999999997</v>
+        <v>93126.15</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31205,7 +31205,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>94823.2</v>
+        <v>93850.15</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31242,7 +31242,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.6512591451675007</v>
+        <v>3.6137909125914516</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31279,7 +31279,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>10.227936576421097</v>
+        <v>10.122980261029015</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31376,7 +31376,7 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="64">
-        <f>AC109+AC53+AC110+AC55+AC57+AC58</f>
+        <f>AC109+AC53+AC110+AC55+AC57+AC58+AC56</f>
         <v>8223.151707790108</v>
       </c>
     </row>
@@ -31414,7 +31414,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>11.13731802580187</v>
+        <v>11.022150550360989</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31451,7 +31451,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>11.531247795193943</v>
+        <v>11.412917253015305</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31488,7 +31488,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>8.9788223491804403E-2</v>
+        <v>9.0726396398863263E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31525,7 +31525,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.4270557029177731E-2</v>
+        <v>7.5046590028686896E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31599,7 +31599,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>9.8778735632183909E-2</v>
+        <v>9.9810847973421005E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31636,7 +31636,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.8778735632183909E-2</v>
+        <v>9.9810847973421005E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32139,7 +32139,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.6940080255730129E-3</v>
+        <v>-7.7744006382739978E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33437,7 +33437,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>241.28</v>
+        <v>238.785</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33453,7 +33453,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>94099.199999999997</v>
+        <v>93126.15</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33473,7 +33473,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>94823.2</v>
+        <v>93850.15</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33493,7 +33493,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.464285714285714</v>
+        <v>13.325055803571427</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33513,7 +33513,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.7743550250288798</v>
+        <v>3.7353256160954946</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33533,7 +33533,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>7.9784019041142473</v>
+        <v>7.8958997789867391</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33553,7 +33553,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.6512591451675007</v>
+        <v>3.6137909125914516</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.227936576421097</v>
+        <v>10.122980261029015</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.4270557029177731E-2</v>
+        <v>7.5046590028686896E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -33814,7 +33814,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>8.9788223491804403E-2</v>
+        <v>9.0726396398863263E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -33846,7 +33846,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.8778735632183909E-2</v>
+        <v>9.9810847973421005E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.8778735632183909E-2</v>
+        <v>9.9810847973421005E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.6940080255730129E-3</v>
+        <v>-7.7744006382739978E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34078,7 +34078,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>241.28</v>
+        <v>238.785</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>94099.199999999997</v>
+        <v>93126.15</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>94823.2</v>
+        <v>93850.15</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34165,7 +34165,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.464285714285714</v>
+        <v>13.325055803571427</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34194,7 +34194,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.7743550250288798</v>
+        <v>3.7353256160954946</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34223,7 +34223,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>7.9784019041142473</v>
+        <v>7.8958997789867391</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.6512591451675007</v>
+        <v>3.6137909125914516</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.227936576421097</v>
+        <v>10.122980261029015</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35054,7 +35054,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.4270557029177731E-2</v>
+        <v>7.5046590028686896E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>8.9788223491804403E-2</v>
+        <v>9.0726396398863263E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35141,7 +35141,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.8778735632183909E-2</v>
+        <v>9.9810847973421005E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35170,7 +35170,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.8778735632183909E-2</v>
+        <v>9.9810847973421005E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35406,7 +35406,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.6940080255730129E-3</v>
+        <v>-7.7744006382739978E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35892,14 +35892,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="239" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35966,19 +35966,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="242">
         <f>Statement!AA89</f>
         <v>2.1456633423995165E-2</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="243"/>
+      <c r="F7" s="242">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12892451569806279</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="243"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -36005,19 +36005,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="242">
         <f>Statement!AA90</f>
         <v>6.7132867132867133E-2</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="243"/>
+      <c r="F9" s="242">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18847352024922118</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="243"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -36044,19 +36044,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="242">
         <f>Statement!AA91</f>
         <v>1.5924106386583092E-2</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="243"/>
+      <c r="F11" s="242">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12177328843995511</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="243"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -36083,19 +36083,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="242">
         <f>Statement!AA95</f>
         <v>-6.0027285129604369E-3</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="243"/>
+      <c r="F13" s="242">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.14812480302552788</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="243"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -36122,19 +36122,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="242">
         <f>Statement!AA96</f>
         <v>5.1831992850759609E-2</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="243"/>
+      <c r="F15" s="242">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>8.3294983893235156E-2</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -36161,19 +36161,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="242">
         <f>Statement!AA98</f>
         <v>6.7172897196261683E-2</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="243"/>
+      <c r="F17" s="242">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>3.1038374717832957E-2</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="243"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -36200,22 +36200,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="242">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.7412935323383085E-2</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="243"/>
+      <c r="F19" s="242">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.8396226415094338E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="243"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -36242,22 +36242,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="242">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>8.7058823529411786E-2</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="243"/>
+      <c r="F21" s="242">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.10526315789473695</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="243"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36305,22 +36305,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="242">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.5872817955112218E-2</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="243"/>
+      <c r="F25" s="242">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13659126230357452</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="243"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36347,22 +36347,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="242">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.24719101123595505</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="243"/>
+      <c r="F27" s="242">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-1.4705882352941176E-2</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="243"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36389,49 +36389,49 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="242">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.7699115044247787E-2</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="243"/>
+      <c r="F29" s="242">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.13953488372093023</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF9CFF1-0569-4F4C-A57C-D226DB6BEFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F64DDD-682C-304A-B5C9-0951F37EEAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2339,6 +2339,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2346,12 +2352,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2372,14 +2372,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12784,11 +12784,11 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.387</v>
-    <v>1.095</v>
-    <v>4.607E-3</v>
-    <v>-0.33500000000000002</v>
-    <v>-1.4030000000000002E-3</v>
+    <v>1.3875</v>
+    <v>1.22</v>
+    <v>5.0609999999999995E-3</v>
+    <v>-0.02</v>
+    <v>-8.2550000000000001E-5</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12796,26 +12796,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>241</v>
+    <v>245.16</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46300.890774189065</v>
+    <v>46304.999797476565</v>
     <v>4</v>
-    <v>235.51</v>
-    <v>92935122000</v>
+    <v>240</v>
+    <v>94291484000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>238.68</v>
-    <v>13.3248</v>
-    <v>237.69</v>
-    <v>238.785</v>
-    <v>238.45</v>
+    <v>240</v>
+    <v>13.4512</v>
+    <v>241.05</v>
+    <v>242.27</v>
+    <v>242.25</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>3288539</v>
-    <v>5342234</v>
+    <v>3892791</v>
+    <v>5387828</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12837,19 +12837,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>7</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13091,9 +13091,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>93126.15</v>
+        <v>94485.3</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>304.97016020039513</v>
+        <v>305.7826546342402</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>93850.15</v>
+        <v>95209.3</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>401.61864881029658</v>
+        <v>401.99475703331012</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>238.785</v>
+        <v>242.27</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>302.59993208221965</v>
+        <v>303.01747043136169</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13771,14 +13771,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>238.45</v>
+        <v>242.25</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>13.325055803571427</v>
+        <v>13.51953125</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>375.96169571522699</v>
+        <v>376.31141938292967</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13795,14 +13795,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.095</v>
+        <v>1.22</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>3.7353256160954946</v>
+        <v>3.7898416442048521</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>373.18497108348703</v>
+        <v>373.53183928178305</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13819,14 +13819,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.33500000000000002</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>9.0726396398863263E-2</v>
+        <v>8.942131739011254E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>351.66708157832505</v>
+        <v>352.12762815272492</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13843,14 +13843,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.607E-3</v>
+        <v>5.0609999999999995E-3</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>7.5046590028686896E-2</v>
+        <v>7.3967061542906679E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.47273522867150392</v>
+        <v>0.45345122447156028</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13867,14 +13867,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.4030000000000002E-3</v>
+        <v>-8.2550000000000001E-5</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>9.9810847973421005E-2</v>
+        <v>9.8375091151745295E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.387</v>
+        <v>1.3875</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5342234</v>
+        <v>5387828</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.7744006382739978E-3</v>
+        <v>-7.662567616338203E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18722,6 +18722,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18729,12 +18735,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19794,16 +19794,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19886,7 +19886,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>238.785</v>
+        <v>242.27</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>93126.15</v>
+        <v>94485.3</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19913,7 +19913,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.387</v>
+        <v>1.3875</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.3956722919031872E-2</v>
+        <v>6.3094767090768999E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93604327708096813</v>
+        <v>0.936905232909231</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19992,7 +19992,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11518500000000001</v>
+        <v>0.11487749999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11074864191472136</v>
+        <v>0.11052033312162921</v>
       </c>
     </row>
   </sheetData>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>139927.65938521514</v>
+        <v>140280.58246815964</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20306,23 +20306,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7217.5191427119689</v>
+        <v>7219.0029724406522</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7463.1540198309513</v>
+        <v>7466.2229935120622</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7457.9906589265456</v>
+        <v>7462.5914074528982</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7399.7452857671169</v>
+        <v>7405.8323349575758</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7363.165763856372</v>
+        <v>7370.7377406862106</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20341,7 +20341,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>82760.787607061138</v>
+        <v>83054.847858304274</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11074864191472136</v>
+        <v>0.11052033312162921</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>36901.574871092955</v>
+        <v>36924.387449049405</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>82760.787607061138</v>
+        <v>83054.847858304274</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>119662.3624781541</v>
+        <v>119979.23530735368</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>118938.3624781541</v>
+        <v>119255.23530735368</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>304.97016020039513</v>
+        <v>305.7826546342402</v>
       </c>
     </row>
   </sheetData>
@@ -20711,23 +20711,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7217.5191427119689</v>
+        <v>7219.0029724406522</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7463.1540198309513</v>
+        <v>7466.2229935120622</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7457.9906589265456</v>
+        <v>7462.5914074528982</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7399.7452857671169</v>
+        <v>7405.8323349575758</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7363.165763856372</v>
+        <v>7370.7377406862106</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11074864191472136</v>
+        <v>0.11052033312162921</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>127816.86392877909</v>
+        <v>127948.30553462775</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>157355.27303601566</v>
+        <v>157501.95524299095</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>156631.27303601566</v>
+        <v>156777.95524299095</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>401.61864881029658</v>
+        <v>401.99475703331012</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11518500000000001</v>
+        <v>0.11487749999999999</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>302.59993208221965</v>
+        <v>303.01747043136169</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11074864191472136</v>
+        <v>0.11052033312162921</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>117810.65222170195</v>
+        <v>117931.80385097937</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>147349.06132893852</v>
+        <v>147485.45355934257</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>146625.06132893852</v>
+        <v>146761.45355934257</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>375.96169571522699</v>
+        <v>376.31141938292967</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11074864191472136</v>
+        <v>0.11052033312162921</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>116727.72961532336</v>
+        <v>116847.7676115322</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>146266.13872255993</v>
+        <v>146401.41731989538</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>145542.13872255993</v>
+        <v>145677.41731989538</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21860,22 +21860,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>373.18497108348703</v>
+        <v>373.53183928178305</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>304.97016020039513</v>
+        <v>305.7826546342402</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>401.61864881029658</v>
+        <v>401.99475703331012</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21943,7 +21943,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>302.59993208221965</v>
+        <v>303.01747043136169</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>375.96169571522699</v>
+        <v>376.31141938292967</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>373.18497108348703</v>
+        <v>373.53183928178305</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>351.66708157832505</v>
+        <v>352.12762815272492</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>238.785</v>
+        <v>242.27</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.47273522867150392</v>
+        <v>0.45345122447156028</v>
       </c>
     </row>
   </sheetData>
@@ -22458,7 +22458,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11518500000000001</v>
+        <v>0.11487749999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22712,7 +22712,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>103635.07715803427</v>
+        <v>103896.46372801266</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22766,23 +22766,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7668.8502920510155</v>
+        <v>7670.4269096980443</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7042.3019238700035</v>
+        <v>7045.1978361346264</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6466.9428269252803</v>
+        <v>6470.9322094602885</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5938.5908157340064</v>
+        <v>5943.475915561281</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5453.4053911665687</v>
+        <v>5459.0134489762031</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22801,15 +22801,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>61295.39111138531</v>
+        <v>61513.181911006985</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="250" t="s">
+      <c r="B14" s="251" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="251"/>
+      <c r="C14" s="252"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>238.785</v>
+        <v>242.27</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22826,7 +22826,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>239.43825799776909</v>
+        <v>240.04685920523761</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22836,20 +22836,20 @@
       <c r="C17" s="158">
         <v>0.02</v>
       </c>
-      <c r="E17" s="252" t="s">
+      <c r="E17" s="250" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="250" t="s">
+      <c r="B19" s="251" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="251"/>
+      <c r="C19" s="252"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11074864191472136</v>
+        <v>0.11052033312162921</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>92887.365000000005</v>
+        <v>94243.03</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22910,15 +22910,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>93611.365000000005</v>
+        <v>94967.03</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="250" t="s">
+      <c r="B28" s="251" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="251"/>
+      <c r="C28" s="252"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>32570.091249746871</v>
+        <v>32589.046319830442</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>61295.39111138531</v>
+        <v>61513.181911006985</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>93865.482361132177</v>
+        <v>94102.228230837427</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>93141.482361132177</v>
+        <v>93378.228230837427</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22989,21 +22989,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>239.43825799776909</v>
+        <v>240.04685920523761</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29608,7 +29608,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>238.785</v>
+        <v>242.27</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>238.785</v>
+        <v>242.27</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30985,7 +30985,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>13.325055803571427</v>
+        <v>13.51953125</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31022,7 +31022,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7353256160954946</v>
+        <v>3.7898416442048521</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31083,7 +31083,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.8958997789867391</v>
+        <v>8.0111382182930981</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31144,7 +31144,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>93126.15</v>
+        <v>94485.3</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31205,7 +31205,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>93850.15</v>
+        <v>95209.3</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31242,7 +31242,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.6137909125914516</v>
+        <v>3.6661262995764345</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31279,7 +31279,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>10.122980261029015</v>
+        <v>10.269582569302125</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31414,7 +31414,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>11.022150550360989</v>
+        <v>11.183015741507871</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31451,7 +31451,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>11.412917253015305</v>
+        <v>11.578200595497291</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31488,7 +31488,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>9.0726396398863263E-2</v>
+        <v>8.942131739011254E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31525,7 +31525,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.5046590028686896E-2</v>
+        <v>7.3967061542906679E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31599,7 +31599,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>9.9810847973421005E-2</v>
+        <v>9.8375091151745295E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31636,7 +31636,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.9810847973421005E-2</v>
+        <v>9.8375091151745295E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32139,7 +32139,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.7744006382739978E-3</v>
+        <v>-7.662567616338203E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33437,7 +33437,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>238.785</v>
+        <v>242.27</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33453,7 +33453,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>93126.15</v>
+        <v>94485.3</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33473,7 +33473,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>93850.15</v>
+        <v>95209.3</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33493,7 +33493,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.325055803571427</v>
+        <v>13.51953125</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33513,7 +33513,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.7353256160954946</v>
+        <v>3.7898416442048521</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33533,7 +33533,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>7.8958997789867391</v>
+        <v>8.0111382182930981</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33553,7 +33553,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.6137909125914516</v>
+        <v>3.6661262995764345</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.122980261029015</v>
+        <v>10.269582569302125</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.5046590028686896E-2</v>
+        <v>7.3967061542906679E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -33814,7 +33814,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>9.0726396398863263E-2</v>
+        <v>8.942131739011254E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -33846,7 +33846,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.9810847973421005E-2</v>
+        <v>9.8375091151745295E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.9810847973421005E-2</v>
+        <v>9.8375091151745295E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.7744006382739978E-3</v>
+        <v>-7.662567616338203E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34078,7 +34078,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>238.785</v>
+        <v>242.27</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>93126.15</v>
+        <v>94485.3</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>93850.15</v>
+        <v>95209.3</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34165,7 +34165,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.325055803571427</v>
+        <v>13.51953125</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34194,7 +34194,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.7353256160954946</v>
+        <v>3.7898416442048521</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34223,7 +34223,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>7.8958997789867391</v>
+        <v>8.0111382182930981</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.6137909125914516</v>
+        <v>3.6661262995764345</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.122980261029015</v>
+        <v>10.269582569302125</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35054,7 +35054,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.5046590028686896E-2</v>
+        <v>7.3967061542906679E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>9.0726396398863263E-2</v>
+        <v>8.942131739011254E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35141,7 +35141,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.9810847973421005E-2</v>
+        <v>9.8375091151745295E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35170,7 +35170,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.9810847973421005E-2</v>
+        <v>9.8375091151745295E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35406,7 +35406,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.7744006382739978E-3</v>
+        <v>-7.662567616338203E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35892,14 +35892,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="241" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35966,19 +35966,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="242">
+      <c r="C7" s="239">
         <f>Statement!AA89</f>
         <v>2.1456633423995165E-2</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="F7" s="242">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12892451569806279</v>
       </c>
-      <c r="G7" s="243"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -36005,19 +36005,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="242">
+      <c r="C9" s="239">
         <f>Statement!AA90</f>
         <v>6.7132867132867133E-2</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="F9" s="242">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18847352024922118</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -36044,19 +36044,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="242">
+      <c r="C11" s="239">
         <f>Statement!AA91</f>
         <v>1.5924106386583092E-2</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="F11" s="242">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12177328843995511</v>
       </c>
-      <c r="G11" s="243"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -36083,19 +36083,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="239">
         <f>Statement!AA95</f>
         <v>-6.0027285129604369E-3</v>
       </c>
-      <c r="D13" s="243"/>
-      <c r="F13" s="242">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.14812480302552788</v>
       </c>
-      <c r="G13" s="243"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -36122,19 +36122,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="242">
+      <c r="C15" s="239">
         <f>Statement!AA96</f>
         <v>5.1831992850759609E-2</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="F15" s="242">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>8.3294983893235156E-2</v>
       </c>
-      <c r="G15" s="243"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -36161,19 +36161,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="242">
+      <c r="C17" s="239">
         <f>Statement!AA98</f>
         <v>6.7172897196261683E-2</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="F17" s="242">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>3.1038374717832957E-2</v>
       </c>
-      <c r="G17" s="243"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -36200,22 +36200,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="242">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.7412935323383085E-2</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="F19" s="242">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.8396226415094338E-2</v>
       </c>
-      <c r="G19" s="243"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -36242,22 +36242,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="242">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>8.7058823529411786E-2</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="F21" s="242">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.10526315789473695</v>
       </c>
-      <c r="G21" s="243"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36305,22 +36305,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="242">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.5872817955112218E-2</v>
       </c>
-      <c r="D25" s="243"/>
-      <c r="F25" s="242">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13659126230357452</v>
       </c>
-      <c r="G25" s="243"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36347,22 +36347,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="242">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.24719101123595505</v>
       </c>
-      <c r="D27" s="243"/>
-      <c r="F27" s="242">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-1.4705882352941176E-2</v>
       </c>
-      <c r="G27" s="243"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36389,49 +36389,49 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="242">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.7699115044247787E-2</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="F29" s="242">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.13953488372093023</v>
       </c>
-      <c r="G29" s="243"/>
+      <c r="G29" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F64DDD-682C-304A-B5C9-0951F37EEAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB69D71A-AC8B-AA4E-979E-4296009EAB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="426">
   <si>
     <t>Ticker</t>
   </si>
@@ -1406,6 +1406,30 @@
   </si>
   <si>
     <t>18.09.2026</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1446,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1594,6 +1618,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2011,11 +2043,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2327,6 +2360,14 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2339,12 +2380,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2352,6 +2387,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2372,17 +2413,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -12785,10 +12827,10 @@
     <v>363.7</v>
     <v>190.12</v>
     <v>1.3875</v>
-    <v>1.22</v>
-    <v>5.0609999999999995E-3</v>
-    <v>-0.02</v>
-    <v>-8.2550000000000001E-5</v>
+    <v>-4.13</v>
+    <v>-1.7047E-2</v>
+    <v>-0.20250000000000001</v>
+    <v>-8.5029999999999991E-4</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12796,26 +12838,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>245.16</v>
+    <v>242.46</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46304.999797476565</v>
+    <v>46307.857740057814</v>
     <v>4</v>
-    <v>240</v>
-    <v>94291484000</v>
+    <v>232.85</v>
+    <v>92684088000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>240</v>
-    <v>13.4512</v>
-    <v>241.05</v>
+    <v>234.625</v>
+    <v>13.2888</v>
     <v>242.27</v>
-    <v>242.25</v>
+    <v>238.14</v>
+    <v>237.9375</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>3892791</v>
-    <v>5387828</v>
+    <v>4514737</v>
+    <v>5401609</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -13091,9 +13133,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13663,7 +13705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I59"/>
+  <dimension ref="B1:K59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13675,25 +13717,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="235" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="235" t="s">
+      <c r="C2" s="240"/>
+      <c r="E2" s="239" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="H2" s="235" t="s">
+      <c r="F2" s="240"/>
+      <c r="H2" s="239" t="s">
         <v>326</v>
       </c>
-      <c r="I2" s="236"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="240"/>
+      <c r="K2" s="134" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="183" t="s">
         <v>11</v>
       </c>
@@ -13706,7 +13753,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>94485.3</v>
+        <v>92874.599999999991</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13714,10 +13761,13 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>305.7826546342402</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+        <v>306.03516812553221</v>
+      </c>
+      <c r="K3" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="183" t="s">
         <v>0</v>
       </c>
@@ -13730,7 +13780,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>95209.3</v>
+        <v>93598.599999999991</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13738,16 +13788,19 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>401.99475703331012</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+        <v>402.11134975713304</v>
+      </c>
+      <c r="K4" s="237" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="183" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>242.27</v>
+        <v>238.14</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13764,21 +13817,24 @@
         <f ca="1">'AVG target price'!C7</f>
         <v>303.01747043136169</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="183" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>242.25</v>
+        <v>237.9375</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>13.51953125</v>
+        <v>13.289062499999998</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13786,23 +13842,26 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>376.31141938292967</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+        <v>376.41983272411642</v>
+      </c>
+      <c r="K6" s="238" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="183" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.22</v>
+        <v>-4.13</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>3.7898416442048521</v>
+        <v>3.7252358490566038</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13810,23 +13869,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>373.53183928178305</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+        <v>373.63936740900249</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="183" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.02</v>
+        <v>-0.20250000000000001</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>8.942131739011254E-2</v>
+        <v>9.0972128009165057E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13834,23 +13893,23 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>352.12762815272492</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+        <v>352.24463768942917</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="183" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>5.0609999999999995E-3</v>
+        <v>-1.7047E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>7.3967061542906679E-2</v>
+        <v>7.524985302763082E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13858,26 +13917,26 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.45345122447156028</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.47914939820873936</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="183" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-8.2550000000000001E-5</v>
+        <v>-8.5029999999999991E-4</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>9.8375091151745295E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.1000811847372694</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="183" t="s">
         <v>7</v>
       </c>
@@ -13900,7 +13959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="183" t="s">
         <v>8</v>
       </c>
@@ -13916,7 +13975,7 @@
         <v>0.24295387078483044</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="183" t="s">
         <v>9</v>
       </c>
@@ -13939,13 +13998,13 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="184" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5387828</v>
+        <v>5401609</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -13955,16 +14014,16 @@
         <v>0.58265148204597283</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="183" t="s">
         <v>291</v>
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.662567616338203E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-7.7954575309072674E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="184" t="s">
         <v>296</v>
       </c>
@@ -13972,12 +14031,16 @@
         <f>Statement!AC175</f>
         <v>-1.8611825192802056</v>
       </c>
+      <c r="H16" s="239" t="s">
+        <v>418</v>
+      </c>
+      <c r="I16" s="240"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="241" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="237"/>
+      <c r="C17" s="241"/>
       <c r="E17" s="182" t="s">
         <v>297</v>
       </c>
@@ -13985,6 +14048,13 @@
         <f>Statement!AC171</f>
         <v>2.5641025641025641E-3</v>
       </c>
+      <c r="H17" s="183" t="s">
+        <v>166</v>
+      </c>
+      <c r="I17" s="235">
+        <f ca="1">DCF!C15</f>
+        <v>0.1104496130650076</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="182" t="s">
@@ -14000,6 +14070,13 @@
         <f>Statement!AC144</f>
         <v>-39.933511119339947</v>
       </c>
+      <c r="H18" s="184" t="s">
+        <v>419</v>
+      </c>
+      <c r="I18" s="236">
+        <f ca="1">Multiples!C54</f>
+        <v>0.11487749999999999</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="182" t="s">
@@ -14050,14 +14127,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="241" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="237"/>
-      <c r="E25" s="235" t="s">
+      <c r="C25" s="241"/>
+      <c r="E25" s="239" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="236"/>
+      <c r="F25" s="240"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="182" t="s">
@@ -14222,13 +14299,14 @@
       <c r="H59" s="134"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14241,6 +14319,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{1621CF88-B889-2143-A07D-41075A1E40C7}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{6C1FB1EB-07D1-684F-8B75-01548820DC66}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{A6DD7074-1F30-274A-939E-C3124387BF4E}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{13526B62-5DF8-464A-9BB0-76685653979C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14250,18 +14334,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18.1640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>112</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{0C7F0F1F-F339-B848-9C11-B9DEBD77927D}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{4DDFAC57-39D4-3345-8DDC-127F349724B3}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{057BE4E1-006C-1146-8D88-DA0B50E42D63}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{E36163F3-014E-C54F-9203-D28EA0B6F5D0}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{13B55C9E-2A66-CD4A-8132-953862B3BEB7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14298,36 +14421,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="238" t="s">
+      <c r="S2" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -14338,32 +14461,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="245" t="s">
+      <c r="S4" s="249" t="s">
         <v>117</v>
       </c>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
+      <c r="AA4" s="250"/>
+      <c r="AB4" s="250"/>
+      <c r="AC4" s="250"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14853,33 +14976,33 @@
       <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="248" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="245" t="s">
+      <c r="S11" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="T11" s="246"/>
-      <c r="U11" s="246"/>
-      <c r="V11" s="246"/>
-      <c r="W11" s="246"/>
-      <c r="X11" s="246"/>
-      <c r="Y11" s="246"/>
-      <c r="Z11" s="246"/>
-      <c r="AA11" s="246"/>
-      <c r="AB11" s="246"/>
-      <c r="AC11" s="246"/>
+      <c r="T11" s="250"/>
+      <c r="U11" s="250"/>
+      <c r="V11" s="250"/>
+      <c r="W11" s="250"/>
+      <c r="X11" s="250"/>
+      <c r="Y11" s="250"/>
+      <c r="Z11" s="250"/>
+      <c r="AA11" s="250"/>
+      <c r="AB11" s="250"/>
+      <c r="AC11" s="250"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15347,35 +15470,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="P2" s="238" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15384,31 +15507,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="P4" s="246" t="s">
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="P4" s="250" t="s">
         <v>117</v>
       </c>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
+      <c r="Q4" s="250"/>
+      <c r="R4" s="250"/>
+      <c r="S4" s="250"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15603,32 +15726,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="248" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="246" t="s">
+      <c r="P9" s="250" t="s">
         <v>127</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="246"/>
-      <c r="S9" s="246"/>
-      <c r="T9" s="246"/>
-      <c r="U9" s="246"/>
-      <c r="V9" s="246"/>
-      <c r="W9" s="246"/>
-      <c r="X9" s="246"/>
-      <c r="Y9" s="246"/>
-      <c r="Z9" s="246"/>
+      <c r="Q9" s="250"/>
+      <c r="R9" s="250"/>
+      <c r="S9" s="250"/>
+      <c r="T9" s="250"/>
+      <c r="U9" s="250"/>
+      <c r="V9" s="250"/>
+      <c r="W9" s="250"/>
+      <c r="X9" s="250"/>
+      <c r="Y9" s="250"/>
+      <c r="Z9" s="250"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16477,31 +16600,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="244" t="s">
+      <c r="C21" s="248" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-      <c r="G21" s="244"/>
-      <c r="H21" s="244"/>
-      <c r="I21" s="244"/>
-      <c r="J21" s="244"/>
-      <c r="K21" s="244"/>
-      <c r="L21" s="244"/>
-      <c r="P21" s="246" t="s">
+      <c r="D21" s="248"/>
+      <c r="E21" s="248"/>
+      <c r="F21" s="248"/>
+      <c r="G21" s="248"/>
+      <c r="H21" s="248"/>
+      <c r="I21" s="248"/>
+      <c r="J21" s="248"/>
+      <c r="K21" s="248"/>
+      <c r="L21" s="248"/>
+      <c r="P21" s="250" t="s">
         <v>129</v>
       </c>
-      <c r="Q21" s="246"/>
-      <c r="R21" s="246"/>
-      <c r="S21" s="246"/>
-      <c r="T21" s="246"/>
-      <c r="U21" s="246"/>
-      <c r="V21" s="246"/>
-      <c r="W21" s="246"/>
-      <c r="X21" s="246"/>
-      <c r="Y21" s="246"/>
-      <c r="Z21" s="246"/>
+      <c r="Q21" s="250"/>
+      <c r="R21" s="250"/>
+      <c r="S21" s="250"/>
+      <c r="T21" s="250"/>
+      <c r="U21" s="250"/>
+      <c r="V21" s="250"/>
+      <c r="W21" s="250"/>
+      <c r="X21" s="250"/>
+      <c r="Y21" s="250"/>
+      <c r="Z21" s="250"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -17316,60 +17439,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17555,30 +17678,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="248" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="249"/>
-      <c r="Q11" s="249"/>
-      <c r="R11" s="249"/>
-      <c r="S11" s="249"/>
-      <c r="T11" s="249"/>
-      <c r="U11" s="249"/>
-      <c r="V11" s="249"/>
-      <c r="W11" s="249"/>
-      <c r="X11" s="249"/>
-      <c r="Y11" s="249"/>
-      <c r="Z11" s="249"/>
+      <c r="P11" s="253"/>
+      <c r="Q11" s="253"/>
+      <c r="R11" s="253"/>
+      <c r="S11" s="253"/>
+      <c r="T11" s="253"/>
+      <c r="U11" s="253"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="253"/>
+      <c r="X11" s="253"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17820,18 +17943,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="248" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18044,23 +18167,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="249"/>
-      <c r="C25" s="249"/>
+      <c r="B25" s="253"/>
+      <c r="C25" s="253"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="244" t="s">
+      <c r="C26" s="248" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="248"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="248"/>
+      <c r="I26" s="248"/>
+      <c r="J26" s="248"/>
+      <c r="K26" s="248"/>
+      <c r="L26" s="248"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18252,18 +18375,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="244" t="s">
+      <c r="C33" s="248" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="244"/>
-      <c r="I33" s="244"/>
-      <c r="J33" s="244"/>
-      <c r="K33" s="244"/>
-      <c r="L33" s="244"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="248"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="248"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18447,18 +18570,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="244" t="s">
+      <c r="C40" s="248" t="s">
         <v>151</v>
       </c>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
+      <c r="D40" s="248"/>
+      <c r="E40" s="248"/>
+      <c r="F40" s="248"/>
+      <c r="G40" s="248"/>
+      <c r="H40" s="248"/>
+      <c r="I40" s="248"/>
+      <c r="J40" s="248"/>
+      <c r="K40" s="248"/>
+      <c r="L40" s="248"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18722,12 +18845,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18735,6 +18852,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18772,60 +18895,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249"/>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
+      <c r="AA2" s="253"/>
+      <c r="AB2" s="253"/>
+      <c r="AC2" s="253"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="S4" s="249"/>
-      <c r="T4" s="249"/>
-      <c r="U4" s="249"/>
-      <c r="V4" s="249"/>
-      <c r="W4" s="249"/>
-      <c r="X4" s="249"/>
-      <c r="Y4" s="249"/>
-      <c r="Z4" s="249"/>
-      <c r="AA4" s="249"/>
-      <c r="AB4" s="249"/>
-      <c r="AC4" s="249"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19188,18 +19311,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="248" t="s">
         <v>159</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
-      <c r="L13" s="244"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="248"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="248"/>
+      <c r="I13" s="248"/>
+      <c r="J13" s="248"/>
+      <c r="K13" s="248"/>
+      <c r="L13" s="248"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19292,18 +19415,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="248" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19495,18 +19618,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="244" t="s">
+      <c r="C25" s="248" t="s">
         <v>263</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
-      <c r="K25" s="244"/>
-      <c r="L25" s="244"/>
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="248"/>
+      <c r="I25" s="248"/>
+      <c r="J25" s="248"/>
+      <c r="K25" s="248"/>
+      <c r="L25" s="248"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19644,18 +19767,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="244" t="s">
+      <c r="C31" s="248" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19794,16 +19917,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19817,18 +19940,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>165</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{E9D325EF-2B97-8C40-B8E7-7BB9014A74A8}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{A7A03757-8751-5F43-AE38-CD5D7C93F606}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{983558CB-5894-4B42-A739-EDDC57596255}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{682C8372-6400-A944-9F4C-C4B13CF132CD}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{2C21B7D5-75A9-474B-AB0D-5863115B2EFE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19866,10 +20028,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19886,7 +20048,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>242.27</v>
+        <v>238.14</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19895,7 +20057,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>94485.3</v>
+        <v>92874.599999999991</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19954,10 +20116,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="242" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="238"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19965,7 +20127,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.3094767090768999E-2</v>
+        <v>6.4118842051802946E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19974,7 +20136,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.936905232909231</v>
+        <v>0.93588115794819704</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20001,7 +20163,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11052033312162921</v>
+        <v>0.1104496130650076</v>
       </c>
     </row>
   </sheetData>
@@ -20046,60 +20208,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20252,7 +20414,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>140280.58246815964</v>
+        <v>140390.26398473981</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20306,23 +20468,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7219.0029724406522</v>
+        <v>7219.4627216205836</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7466.2229935120622</v>
+        <v>7467.1740110460505</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7462.5914074528982</v>
+        <v>7464.0172852918231</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7405.8323349575758</v>
+        <v>7407.7191055428775</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7370.7377406862106</v>
+        <v>7373.0851024315034</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20341,14 +20503,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>83054.847858304274</v>
+        <v>83146.257343024728</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="238" t="s">
+      <c r="B13" s="242" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="238"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20364,14 +20526,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11052033312162921</v>
+        <v>0.1104496130650076</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="238" t="s">
+      <c r="B18" s="242" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="238"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20379,7 +20541,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>36924.387449049405</v>
+        <v>36931.458225932838</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20388,7 +20550,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>83054.847858304274</v>
+        <v>83146.257343024728</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20397,7 +20559,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>119979.23530735368</v>
+        <v>120077.71556895756</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20424,7 +20586,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119255.23530735368</v>
+        <v>119353.71556895756</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20442,7 +20604,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>305.7826546342402</v>
+        <v>306.03516812553221</v>
       </c>
     </row>
   </sheetData>
@@ -20485,37 +20647,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20711,23 +20873,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7219.0029724406522</v>
+        <v>7219.4627216205836</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7466.2229935120622</v>
+        <v>7467.1740110460505</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7462.5914074528982</v>
+        <v>7464.0172852918231</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7405.8323349575758</v>
+        <v>7407.7191055428775</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7370.7377406862106</v>
+        <v>7373.0851024315034</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20735,18 +20897,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="248" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20940,18 +21102,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="248" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="244"/>
-      <c r="L17" s="244"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -21085,18 +21247,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="248" t="s">
         <v>200</v>
       </c>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
-      <c r="F22" s="244"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="244"/>
-      <c r="I22" s="244"/>
-      <c r="J22" s="244"/>
-      <c r="K22" s="244"/>
-      <c r="L22" s="244"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="248"/>
+      <c r="G22" s="248"/>
+      <c r="H22" s="248"/>
+      <c r="I22" s="248"/>
+      <c r="J22" s="248"/>
+      <c r="K22" s="248"/>
+      <c r="L22" s="248"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21180,18 +21342,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="244" t="s">
+      <c r="C27" s="248" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="E27" s="244"/>
-      <c r="F27" s="244"/>
-      <c r="G27" s="244"/>
-      <c r="H27" s="244"/>
-      <c r="I27" s="244"/>
-      <c r="J27" s="244"/>
-      <c r="K27" s="244"/>
-      <c r="L27" s="244"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="248"/>
+      <c r="I27" s="248"/>
+      <c r="J27" s="248"/>
+      <c r="K27" s="248"/>
+      <c r="L27" s="248"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21492,10 +21654,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="238" t="s">
+      <c r="B39" s="242" t="s">
         <v>206</v>
       </c>
-      <c r="C39" s="238"/>
+      <c r="C39" s="242"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21513,7 +21675,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11052033312162921</v>
+        <v>0.1104496130650076</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21539,7 +21701,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>127948.30553462775</v>
+        <v>127989.05328178055</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21548,7 +21710,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>157501.95524299095</v>
+        <v>157547.42640528188</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21575,7 +21737,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>156777.95524299095</v>
+        <v>156823.42640528188</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21593,14 +21755,14 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>401.99475703331012</v>
+        <v>402.11134975713304</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="238" t="s">
+      <c r="B52" s="242" t="s">
         <v>211</v>
       </c>
-      <c r="C52" s="238"/>
+      <c r="C52" s="242"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21656,10 +21818,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="238" t="s">
+      <c r="B60" s="242" t="s">
         <v>323</v>
       </c>
-      <c r="C60" s="238"/>
+      <c r="C60" s="242"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21676,7 +21838,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11052033312162921</v>
+        <v>0.1104496130650076</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21702,7 +21864,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>117931.80385097937</v>
+        <v>117969.36163890405</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21711,7 +21873,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>147485.45355934257</v>
+        <v>147527.73476240539</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21738,7 +21900,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>146761.45355934257</v>
+        <v>146803.73476240539</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21756,14 +21918,14 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>376.31141938292967</v>
+        <v>376.41983272411642</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="238" t="s">
+      <c r="B73" s="242" t="s">
         <v>410</v>
       </c>
-      <c r="C73" s="238"/>
+      <c r="C73" s="242"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21780,7 +21942,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11052033312162921</v>
+        <v>0.1104496130650076</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21806,7 +21968,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>116847.7676115322</v>
+        <v>116884.98016600963</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21815,7 +21977,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>146401.41731989538</v>
+        <v>146443.35328951097</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21842,7 +22004,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>145677.41731989538</v>
+        <v>145719.35328951097</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21860,22 +22022,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>373.53183928178305</v>
+        <v>373.63936740900249</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21913,10 +22075,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21925,7 +22087,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>305.7826546342402</v>
+        <v>306.03516812553221</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21934,7 +22096,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>401.99475703331012</v>
+        <v>402.11134975713304</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21952,7 +22114,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>376.31141938292967</v>
+        <v>376.41983272411642</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21961,7 +22123,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>373.53183928178305</v>
+        <v>373.63936740900249</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21970,7 +22132,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>352.12762815272492</v>
+        <v>352.24463768942917</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21979,7 +22141,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>242.27</v>
+        <v>238.14</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21988,7 +22150,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.45345122447156028</v>
+        <v>0.47914939820873936</v>
       </c>
     </row>
   </sheetData>
@@ -22004,18 +22166,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{143F4B9F-EC26-484D-AFDC-A9CE3E6FFC1F}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{0B5BD635-45CB-754B-80E1-B7F9DC321CC9}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{C5BB6F3D-0578-BA4D-B491-2F4294D08695}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{248DC901-D83B-7349-B21F-846BB64E20CC}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{8EB181CF-4C75-584E-AD71-1E2F7A9E8085}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -22044,37 +22245,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22187,18 +22388,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="248" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22319,18 +22520,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="248" t="s">
         <v>398</v>
       </c>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="244"/>
-      <c r="K14" s="244"/>
-      <c r="L14" s="244"/>
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="248"/>
+      <c r="G14" s="248"/>
+      <c r="H14" s="248"/>
+      <c r="I14" s="248"/>
+      <c r="J14" s="248"/>
+      <c r="K14" s="248"/>
+      <c r="L14" s="248"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22420,10 +22621,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="238" t="s">
+      <c r="B20" s="242" t="s">
         <v>400</v>
       </c>
-      <c r="C20" s="238"/>
+      <c r="C20" s="242"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22524,60 +22725,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22712,7 +22913,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>103896.46372801266</v>
+        <v>103977.69750612014</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22766,23 +22967,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7670.4269096980443</v>
+        <v>7670.9154082476252</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7045.1978361346264</v>
+        <v>7046.0952251730196</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6470.9322094602885</v>
+        <v>6472.1686109099837</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5943.475915561281</v>
+        <v>5944.9901242315209</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5459.0134489762031</v>
+        <v>5460.7519831349255</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22801,15 +23002,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>61513.181911006985</v>
+        <v>61580.882814771125</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="251" t="s">
+      <c r="B14" s="254" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="252"/>
+      <c r="C14" s="255"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -22817,7 +23018,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>242.27</v>
+        <v>238.14</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22826,7 +23027,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>240.04685920523761</v>
+        <v>240.23600042793885</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22836,20 +23037,20 @@
       <c r="C17" s="158">
         <v>0.02</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="256" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="256"/>
+      <c r="G17" s="256"/>
+      <c r="H17" s="256"/>
+      <c r="I17" s="256"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="251" t="s">
+      <c r="B19" s="254" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="252"/>
+      <c r="C19" s="255"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -22865,7 +23066,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11052033312162921</v>
+        <v>0.1104496130650076</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22883,7 +23084,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>94243.03</v>
+        <v>92636.459999999992</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22910,15 +23111,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>94967.03</v>
+        <v>93360.459999999992</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="251" t="s">
+      <c r="B28" s="254" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="255"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -22926,7 +23127,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>32589.046319830442</v>
+        <v>32594.921351697078</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22935,7 +23136,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>61513.181911006985</v>
+        <v>61580.882814771125</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22944,7 +23145,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>94102.228230837427</v>
+        <v>94175.80416646821</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22971,7 +23172,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>93378.228230837427</v>
+        <v>93451.80416646821</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22989,21 +23190,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>240.04685920523761</v>
+        <v>240.23600042793885</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29608,7 +29809,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>242.27</v>
+        <v>238.14</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29679,7 +29880,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>242.27</v>
+        <v>238.14</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30985,7 +31186,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>13.51953125</v>
+        <v>13.289062499999998</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31022,7 +31223,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7898416442048521</v>
+        <v>3.7252358490566038</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31083,7 +31284,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.0111382182930981</v>
+        <v>7.8745715742944569</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31144,7 +31345,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>94485.3</v>
+        <v>92874.599999999991</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31205,7 +31406,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>95209.3</v>
+        <v>93598.599999999991</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31242,7 +31443,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.6661262995764345</v>
+        <v>3.6041047362341159</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31279,7 +31480,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>10.269582569302125</v>
+        <v>10.095847265667134</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31414,7 +31615,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>11.183015741507871</v>
+        <v>10.992377796188897</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31451,7 +31652,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>11.578200595497291</v>
+        <v>11.382326792211609</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31488,7 +31689,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>8.942131739011254E-2</v>
+        <v>9.0972128009165057E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31525,7 +31726,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.3967061542906679E-2</v>
+        <v>7.524985302763082E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31599,7 +31800,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>9.8375091151745295E-2</v>
+        <v>0.1000811847372694</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31636,7 +31837,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.8375091151745295E-2</v>
+        <v>0.1000811847372694</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32139,7 +32340,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.662567616338203E-3</v>
+        <v>-7.7954575309072674E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33386,18 +33587,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>233</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{20744307-6899-E14E-A89E-5997BE08FB99}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{453D1AC9-C5D9-6241-AA24-1E2D8C8B273F}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{B0D18EE8-BE4D-D941-9CDD-CC1AF0E90E7B}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{73679ABD-615E-804F-BFBC-FA733B2672C8}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{8EA60BF0-8D9B-3941-BA1C-F39576F09E36}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -33421,15 +33661,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>234</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="E4" s="238" t="s">
+      <c r="C4" s="242"/>
+      <c r="E4" s="242" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33437,7 +33677,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>242.27</v>
+        <v>238.14</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33453,7 +33693,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>94485.3</v>
+        <v>92874.599999999991</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33473,7 +33713,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>95209.3</v>
+        <v>93598.599999999991</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33493,7 +33733,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.51953125</v>
+        <v>13.289062499999998</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33513,7 +33753,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.7898416442048521</v>
+        <v>3.7252358490566038</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33533,7 +33773,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.0111382182930981</v>
+        <v>7.8745715742944569</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33553,7 +33793,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.6661262995764345</v>
+        <v>3.6041047362341159</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33562,18 +33802,18 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.269582569302125</v>
+        <v>10.095847265667134</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="242" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="238"/>
-      <c r="E15" s="238" t="s">
+      <c r="C15" s="242"/>
+      <c r="E15" s="242" t="s">
         <v>247</v>
       </c>
-      <c r="F15" s="238"/>
+      <c r="F15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33624,14 +33864,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="238" t="s">
+      <c r="B21" s="242" t="s">
         <v>246</v>
       </c>
-      <c r="C21" s="238"/>
-      <c r="E21" s="238" t="s">
+      <c r="C21" s="242"/>
+      <c r="E21" s="242" t="s">
         <v>250</v>
       </c>
-      <c r="F21" s="238"/>
+      <c r="F21" s="242"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33700,14 +33940,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="242" t="s">
         <v>251</v>
       </c>
-      <c r="C29" s="238"/>
-      <c r="E29" s="238" t="s">
+      <c r="C29" s="242"/>
+      <c r="E29" s="242" t="s">
         <v>257</v>
       </c>
-      <c r="F29" s="238"/>
+      <c r="F29" s="242"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33783,14 +34023,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="242" t="s">
         <v>269</v>
       </c>
-      <c r="C37" s="238"/>
-      <c r="E37" s="238" t="s">
+      <c r="C37" s="242"/>
+      <c r="E37" s="242" t="s">
         <v>272</v>
       </c>
-      <c r="F37" s="238"/>
+      <c r="F37" s="242"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33798,7 +34038,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.3967061542906679E-2</v>
+        <v>7.524985302763082E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -33814,7 +34054,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>8.942131739011254E-2</v>
+        <v>9.0972128009165057E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -33846,7 +34086,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.8375091151745295E-2</v>
+        <v>0.1000811847372694</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33855,18 +34095,18 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.8375091151745295E-2</v>
+        <v>0.1000811847372694</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="238" t="s">
+      <c r="B45" s="242" t="s">
         <v>280</v>
       </c>
-      <c r="C45" s="238"/>
-      <c r="E45" s="238" t="s">
+      <c r="C45" s="242"/>
+      <c r="E45" s="242" t="s">
         <v>286</v>
       </c>
-      <c r="F45" s="238"/>
+      <c r="F45" s="242"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33899,18 +34139,18 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.662567616338203E-3</v>
+        <v>-7.7954575309072674E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="238" t="s">
+      <c r="B51" s="242" t="s">
         <v>283</v>
       </c>
-      <c r="C51" s="238"/>
-      <c r="E51" s="238" t="s">
+      <c r="C51" s="242"/>
+      <c r="E51" s="242" t="s">
         <v>304</v>
       </c>
-      <c r="F51" s="238"/>
+      <c r="F51" s="242"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34078,7 +34318,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>242.27</v>
+        <v>238.14</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34107,7 +34347,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>94485.3</v>
+        <v>92874.599999999991</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34136,7 +34376,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>95209.3</v>
+        <v>93598.599999999991</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34165,7 +34405,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.51953125</v>
+        <v>13.289062499999998</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34194,7 +34434,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.7898416442048521</v>
+        <v>3.7252358490566038</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34223,7 +34463,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.0111382182930981</v>
+        <v>7.8745715742944569</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34252,7 +34492,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.6661262995764345</v>
+        <v>3.6041047362341159</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34281,7 +34521,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.269582569302125</v>
+        <v>10.095847265667134</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35054,7 +35294,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.3967061542906679E-2</v>
+        <v>7.524985302763082E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35083,7 +35323,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>8.942131739011254E-2</v>
+        <v>9.0972128009165057E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35141,7 +35381,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.8375091151745295E-2</v>
+        <v>0.1000811847372694</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35170,7 +35410,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.8375091151745295E-2</v>
+        <v>0.1000811847372694</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35406,7 +35646,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.662567616338203E-3</v>
+        <v>-7.7954575309072674E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35892,14 +36132,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35966,19 +36206,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="246">
         <f>Statement!AA89</f>
         <v>2.1456633423995165E-2</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12892451569806279</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -36005,19 +36245,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="246">
         <f>Statement!AA90</f>
         <v>6.7132867132867133E-2</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18847352024922118</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -36044,19 +36284,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="246">
         <f>Statement!AA91</f>
         <v>1.5924106386583092E-2</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12177328843995511</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -36083,19 +36323,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="246">
         <f>Statement!AA95</f>
         <v>-6.0027285129604369E-3</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.14812480302552788</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -36122,19 +36362,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="246">
         <f>Statement!AA96</f>
         <v>5.1831992850759609E-2</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>8.3294983893235156E-2</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -36161,19 +36401,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="246">
         <f>Statement!AA98</f>
         <v>6.7172897196261683E-2</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>3.1038374717832957E-2</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -36200,22 +36440,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.7412935323383085E-2</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.8396226415094338E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -36242,22 +36482,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>8.7058823529411786E-2</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.10526315789473695</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36305,22 +36545,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.5872817955112218E-2</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13659126230357452</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36347,22 +36587,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.24719101123595505</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-1.4705882352941176E-2</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36389,49 +36629,49 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.7699115044247787E-2</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.13953488372093023</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB69D71A-AC8B-AA4E-979E-4296009EAB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE395F7-4CEA-374B-931C-3FB859B24026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -12826,11 +12826,11 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.3875</v>
-    <v>-4.13</v>
-    <v>-1.7047E-2</v>
-    <v>-0.20250000000000001</v>
-    <v>-8.5029999999999991E-4</v>
+    <v>1.3869</v>
+    <v>10.99</v>
+    <v>4.5662000000000001E-2</v>
+    <v>-0.67</v>
+    <v>-2.6619999999999999E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12838,26 +12838,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>242.46</v>
+    <v>254.32</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46307.857740057814</v>
+    <v>46310.902512291403</v>
     <v>4</v>
-    <v>232.85</v>
-    <v>92684088000</v>
+    <v>243.435</v>
+    <v>97949964000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>234.625</v>
-    <v>13.2888</v>
-    <v>242.27</v>
-    <v>238.14</v>
-    <v>237.9375</v>
+    <v>243.74</v>
+    <v>14.043799999999999</v>
+    <v>240.68</v>
+    <v>251.67</v>
+    <v>251</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>4514737</v>
-    <v>5401609</v>
+    <v>6607337</v>
+    <v>5218596</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12881,17 +12881,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-5.1749999999999999E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>53.29</v>
     <v>Index</v>
     <v>7</v>
-    <v>52.34</v>
+    <v>51.77</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.96</v>
+    <v>52.17</v>
+    <v>51.9</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>92874.599999999991</v>
+        <v>98151.299999999988</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13761,7 +13761,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>306.03516812553221</v>
+        <v>307.14290106008809</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>421</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>93598.599999999991</v>
+        <v>98875.299999999988</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>402.11134975713304</v>
+        <v>402.62116526730949</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>422</v>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>238.14</v>
+        <v>251.67</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>303.01747043136169</v>
+        <v>303.78918460561232</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>423</v>
@@ -13827,14 +13827,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>237.9375</v>
+        <v>251</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>13.289062499999998</v>
+        <v>14.044084821428569</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>376.41983272411642</v>
+        <v>376.8938816457607</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>424</v>
@@ -13854,14 +13854,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.13</v>
+        <v>10.99</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>3.7252358490566038</v>
+        <v>3.9368863111282248</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>373.63936740900249</v>
+        <v>374.10954549037194</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13878,14 +13878,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.20250000000000001</v>
+        <v>-0.67</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>9.0972128009165057E-2</v>
+        <v>8.6081386593962597E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13893,7 +13893,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>352.24463768942917</v>
+        <v>352.9113356138285</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13902,14 +13902,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.7047E-2</v>
+        <v>4.5662000000000001E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>7.524985302763082E-2</v>
+        <v>7.1204354909206513E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.47914939820873936</v>
+        <v>0.40227812458309897</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13926,14 +13926,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-8.5029999999999991E-4</v>
+        <v>-2.6619999999999999E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>0.1000811847372694</v>
+        <v>9.4700732440629931E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3875</v>
+        <v>1.3869</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5401609</v>
+        <v>5218596</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.7954575309072674E-3</v>
+        <v>-7.3763668947838699E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14053,7 +14053,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.1104496130650076</v>
+        <v>0.11014068733800064</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.11487749999999999</v>
+        <v>0.11431050000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>238.14</v>
+        <v>251.67</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20057,7 +20057,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>92874.599999999991</v>
+        <v>98151.299999999988</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20084,7 +20084,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3875</v>
+        <v>1.3869</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.4118842051802946E-2</v>
+        <v>6.0881620983922781E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93588115794819704</v>
+        <v>0.9391183790160772</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11487749999999999</v>
+        <v>0.11431050000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1104496130650076</v>
+        <v>0.11014068733800064</v>
       </c>
     </row>
   </sheetData>
@@ -20414,7 +20414,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>140390.26398473981</v>
+        <v>140871.4025875947</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20468,23 +20468,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7219.4627216205836</v>
+        <v>7221.4717262407321</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7467.1740110460505</v>
+        <v>7471.3304628371243</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7464.0172852918231</v>
+        <v>7470.250194441539</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7407.7191055428775</v>
+        <v>7415.9681155610187</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7373.0851024315034</v>
+        <v>7383.3495839228917</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20503,7 +20503,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>83146.257343024728</v>
+        <v>83547.361330431042</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1104496130650076</v>
+        <v>0.11014068733800064</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>36931.458225932838</v>
+        <v>36962.370083003305</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>83146.257343024728</v>
+        <v>83547.361330431042</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20559,7 +20559,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>120077.71556895756</v>
+        <v>120509.73141343435</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119353.71556895756</v>
+        <v>119785.73141343435</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20604,7 +20604,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>306.03516812553221</v>
+        <v>307.14290106008809</v>
       </c>
     </row>
   </sheetData>
@@ -20873,23 +20873,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7219.4627216205836</v>
+        <v>7221.4717262407321</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7467.1740110460505</v>
+        <v>7471.3304628371243</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7464.0172852918231</v>
+        <v>7470.250194441539</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7407.7191055428775</v>
+        <v>7415.9681155610187</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7373.0851024315034</v>
+        <v>7383.3495839228917</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1104496130650076</v>
+        <v>0.11014068733800064</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>127989.05328178055</v>
+        <v>128167.2339551703</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21710,7 +21710,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>157547.42640528188</v>
+        <v>157746.25445425071</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21737,7 +21737,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>156823.42640528188</v>
+        <v>157022.25445425071</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>402.11134975713304</v>
+        <v>402.62116526730949</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21779,7 +21779,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11487749999999999</v>
+        <v>0.11431050000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>303.01747043136169</v>
+        <v>303.78918460561232</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1104496130650076</v>
+        <v>0.11014068733800064</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21864,7 +21864,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>117969.36163890405</v>
+        <v>118133.59334276627</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21873,7 +21873,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>147527.73476240539</v>
+        <v>147712.61384184667</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>146803.73476240539</v>
+        <v>146988.61384184667</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>376.41983272411642</v>
+        <v>376.8938816457607</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1104496130650076</v>
+        <v>0.11014068733800064</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>116884.98016600963</v>
+        <v>117047.70224216465</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21977,7 +21977,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>146443.35328951097</v>
+        <v>146626.72274124506</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -22004,7 +22004,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>145719.35328951097</v>
+        <v>145902.72274124506</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>373.63936740900249</v>
+        <v>374.10954549037194</v>
       </c>
     </row>
   </sheetData>
@@ -22087,7 +22087,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>306.03516812553221</v>
+        <v>307.14290106008809</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>402.11134975713304</v>
+        <v>402.62116526730949</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22105,7 +22105,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>303.01747043136169</v>
+        <v>303.78918460561232</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>376.41983272411642</v>
+        <v>376.8938816457607</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>373.63936740900249</v>
+        <v>374.10954549037194</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>352.24463768942917</v>
+        <v>352.9113356138285</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22141,7 +22141,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>238.14</v>
+        <v>251.67</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.47914939820873936</v>
+        <v>0.40227812458309897</v>
       </c>
     </row>
   </sheetData>
@@ -22659,7 +22659,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11487749999999999</v>
+        <v>0.11431050000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22913,7 +22913,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>103977.69750612014</v>
+        <v>104334.04475333095</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22967,23 +22967,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7670.9154082476252</v>
+        <v>7673.0500414038825</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7046.0952251730196</v>
+        <v>7050.017291951619</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6472.1686109099837</v>
+        <v>6477.5732659920313</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5944.9901242315209</v>
+        <v>5951.6102838776715</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5460.7519831349255</v>
+        <v>5468.3541994231209</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23002,7 +23002,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>61580.882814771125</v>
+        <v>61877.953764616803</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23018,7 +23018,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>238.14</v>
+        <v>251.67</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>240.23600042793885</v>
+        <v>241.06570397754533</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1104496130650076</v>
+        <v>0.11014068733800064</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23084,7 +23084,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>92636.459999999992</v>
+        <v>97899.62999999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>93360.459999999992</v>
+        <v>98623.62999999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23127,7 +23127,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>32594.921351697078</v>
+        <v>32620.605082648326</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>61580.882814771125</v>
+        <v>61877.953764616803</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23145,7 +23145,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>94175.80416646821</v>
+        <v>94498.558847265129</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23172,7 +23172,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>93451.80416646821</v>
+        <v>93774.558847265129</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>240.23600042793885</v>
+        <v>241.06570397754533</v>
       </c>
     </row>
   </sheetData>
@@ -29809,7 +29809,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>238.14</v>
+        <v>251.67</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29880,7 +29880,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>238.14</v>
+        <v>251.67</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31186,7 +31186,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>13.289062499999998</v>
+        <v>14.044084821428569</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31223,7 +31223,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7252358490566038</v>
+        <v>3.9368863111282248</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31284,7 +31284,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.8745715742944569</v>
+        <v>8.3219678680720843</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31345,7 +31345,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>92874.599999999991</v>
+        <v>98151.299999999988</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>93598.599999999991</v>
+        <v>98875.299999999988</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31443,7 +31443,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.6041047362341159</v>
+        <v>3.8072891798228721</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31480,7 +31480,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>10.095847265667134</v>
+        <v>10.6650091683745</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31615,7 +31615,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>10.992377796188897</v>
+        <v>11.616913244170906</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31652,7 +31652,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>11.382326792211609</v>
+        <v>12.024015063024024</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31689,7 +31689,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>9.0972128009165057E-2</v>
+        <v>8.6081386593962597E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31726,7 +31726,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.524985302763082E-2</v>
+        <v>7.1204354909206513E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31800,7 +31800,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>0.1000811847372694</v>
+        <v>9.4700732440629931E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31837,7 +31837,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>0.1000811847372694</v>
+        <v>9.4700732440629931E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32340,7 +32340,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.7954575309072674E-3</v>
+        <v>-7.3763668947838699E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33677,7 +33677,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>238.14</v>
+        <v>251.67</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33693,7 +33693,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>92874.599999999991</v>
+        <v>98151.299999999988</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33713,7 +33713,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>93598.599999999991</v>
+        <v>98875.299999999988</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33733,7 +33733,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.289062499999998</v>
+        <v>14.044084821428569</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33753,7 +33753,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.7252358490566038</v>
+        <v>3.9368863111282248</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33773,7 +33773,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>7.8745715742944569</v>
+        <v>8.3219678680720843</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33793,7 +33793,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.6041047362341159</v>
+        <v>3.8072891798228721</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33802,7 +33802,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.095847265667134</v>
+        <v>10.6650091683745</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.524985302763082E-2</v>
+        <v>7.1204354909206513E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>9.0972128009165057E-2</v>
+        <v>8.6081386593962597E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -34086,7 +34086,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>0.1000811847372694</v>
+        <v>9.4700732440629931E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34095,7 +34095,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>0.1000811847372694</v>
+        <v>9.4700732440629931E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34139,7 +34139,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.7954575309072674E-3</v>
+        <v>-7.3763668947838699E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34318,7 +34318,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>238.14</v>
+        <v>251.67</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34347,7 +34347,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>92874.599999999991</v>
+        <v>98151.299999999988</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>93598.599999999991</v>
+        <v>98875.299999999988</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34405,7 +34405,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>13.289062499999998</v>
+        <v>14.044084821428569</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34434,7 +34434,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.7252358490566038</v>
+        <v>3.9368863111282248</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34463,7 +34463,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>7.8745715742944569</v>
+        <v>8.3219678680720843</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.6041047362341159</v>
+        <v>3.8072891798228721</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34521,7 +34521,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.095847265667134</v>
+        <v>10.6650091683745</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.524985302763082E-2</v>
+        <v>7.1204354909206513E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35323,7 +35323,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>9.0972128009165057E-2</v>
+        <v>8.6081386593962597E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35381,7 +35381,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>0.1000811847372694</v>
+        <v>9.4700732440629931E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35410,7 +35410,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>0.1000811847372694</v>
+        <v>9.4700732440629931E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35646,7 +35646,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.7954575309072674E-3</v>
+        <v>-7.3763668947838699E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE395F7-4CEA-374B-931C-3FB859B24026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CC2F26-687D-FC40-9CD3-8C6D36491105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -140,19 +161,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="427">
   <si>
     <t>Ticker</t>
   </si>
@@ -1430,6 +1460,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2048,7 +2081,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2368,6 +2401,9 @@
     <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -12787,7 +12823,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12826,11 +12862,9 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.3869</v>
-    <v>10.99</v>
-    <v>4.5662000000000001E-2</v>
-    <v>-0.67</v>
-    <v>-2.6619999999999999E-3</v>
+    <v>1.3853</v>
+    <v>8.0399999999999991</v>
+    <v>3.2538999999999998E-2</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12838,36 +12872,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>254.32</v>
+    <v>256.39</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46310.902512291403</v>
+    <v>46315.716707950778</v>
     <v>4</v>
-    <v>243.435</v>
-    <v>97949964000</v>
+    <v>248.5</v>
+    <v>99296596000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>243.74</v>
-    <v>14.043799999999999</v>
-    <v>240.68</v>
-    <v>251.67</v>
-    <v>251</v>
+    <v>249.58</v>
+    <v>14.2369</v>
+    <v>247.09</v>
+    <v>255.13</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>6607337</v>
-    <v>5218596</v>
+    <v>2277515</v>
+    <v>4680929</v>
     <v>1997</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12881,28 +12929,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-0.27</v>
-    <v>-5.1749999999999999E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>53.29</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>7</v>
-    <v>51.77</v>
+    <v>10</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.96</v>
-    <v>52.17</v>
-    <v>51.9</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12936,8 +12984,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12959,7 +13005,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12969,6 +13014,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13004,7 +13054,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13015,16 +13065,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13125,19 +13172,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13218,9 +13259,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13228,9 +13266,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13715,7 +13750,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -13724,18 +13759,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="239" t="s">
+      <c r="B2" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="240"/>
-      <c r="E2" s="239" t="s">
+      <c r="C2" s="243"/>
+      <c r="E2" s="242" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="240"/>
-      <c r="H2" s="239" t="s">
+      <c r="F2" s="243"/>
+      <c r="H2" s="242" t="s">
         <v>326</v>
       </c>
-      <c r="I2" s="240"/>
+      <c r="I2" s="243"/>
       <c r="K2" s="134" t="s">
         <v>420</v>
       </c>
@@ -13753,7 +13788,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>98151.299999999988</v>
+        <v>99500.7</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13761,7 +13796,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>307.14290106008809</v>
+        <v>309.03238676514036</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>421</v>
@@ -13780,7 +13815,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>98875.299999999988</v>
+        <v>100224.7</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13788,7 +13823,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>402.62116526730949</v>
+        <v>403.48459080423686</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>422</v>
@@ -13800,7 +13835,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>251.67</v>
+        <v>255.13</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13815,7 +13850,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>303.78918460561232</v>
+        <v>304.62479417958991</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>423</v>
@@ -13825,16 +13860,16 @@
       <c r="B6" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="206" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>251</v>
+      <c r="C6" s="206" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>14.044084821428569</v>
+        <v>14.237165178571427</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13842,7 +13877,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>376.8938816457607</v>
+        <v>377.6967280495</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>424</v>
@@ -13854,14 +13889,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>10.99</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>3.9368863111282248</v>
+        <v>3.9910112629957641</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13869,23 +13904,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>374.10954549037194</v>
+        <v>374.90583571533699</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.67</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>8.6081386593962597E-2</v>
+        <v>8.4913975479569498E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13893,7 +13928,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>352.9113356138285</v>
+        <v>353.9488671027608</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13902,14 +13937,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.5662000000000001E-2</v>
+        <v>3.2538999999999998E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>7.1204354909206513E-2</v>
+        <v>7.0238701838278531E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13917,23 +13952,23 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.40227812458309897</v>
+        <v>0.38732750794795129</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.6619999999999999E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>9.4700732440629931E-2</v>
+        <v>9.341642822613308E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13981,7 +14016,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3869</v>
+        <v>1.3853</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -13990,12 +14025,12 @@
         <f>Statement!AC125</f>
         <v>0.61917715062903789</v>
       </c>
-      <c r="H13" s="182" t="s">
+      <c r="H13" s="241" t="s">
         <v>414</v>
       </c>
-      <c r="I13" s="211">
+      <c r="I13" s="239">
         <f>'Reverse DCF'!C17</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -14004,7 +14039,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>5218596</v>
+        <v>4680929</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -14013,6 +14048,13 @@
         <f>Statement!AC140</f>
         <v>0.58265148204597283</v>
       </c>
+      <c r="H14" s="184" t="s">
+        <v>426</v>
+      </c>
+      <c r="I14" s="240">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>252.85851957947744</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="183" t="s">
@@ -14020,7 +14062,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.3763668947838699E-3</v>
+        <v>-7.2763307192813724E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14031,16 +14073,16 @@
         <f>Statement!AC175</f>
         <v>-1.8611825192802056</v>
       </c>
-      <c r="H16" s="239" t="s">
+      <c r="H16" s="242" t="s">
         <v>418</v>
       </c>
-      <c r="I16" s="240"/>
+      <c r="I16" s="243"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="241" t="s">
+      <c r="B17" s="244" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="241"/>
+      <c r="C17" s="244"/>
       <c r="E17" s="182" t="s">
         <v>297</v>
       </c>
@@ -14053,7 +14095,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.11014068733800064</v>
+        <v>0.10961862280413401</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14075,7 +14117,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.11431050000000001</v>
+        <v>0.11369850000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14127,14 +14169,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="241" t="s">
+      <c r="B25" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="241"/>
-      <c r="E25" s="239" t="s">
+      <c r="C25" s="244"/>
+      <c r="E25" s="242" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="240"/>
+      <c r="F25" s="243"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="182" t="s">
@@ -14143,12 +14185,12 @@
       <c r="C26" s="168">
         <v>0.21</v>
       </c>
-      <c r="E26" s="183" t="e" vm="2">
+      <c r="E26" s="183" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.9</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14163,7 +14205,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14421,36 +14463,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
+      <c r="AA2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="245"/>
+      <c r="AC2" s="245"/>
       <c r="AE2" s="85" t="s">
         <v>116</v>
       </c>
@@ -14461,32 +14503,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="249" t="s">
+      <c r="S4" s="252" t="s">
         <v>117</v>
       </c>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
-      <c r="AA4" s="250"/>
-      <c r="AB4" s="250"/>
-      <c r="AC4" s="250"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14976,33 +15018,33 @@
       <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="251" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="249" t="s">
+      <c r="S11" s="252" t="s">
         <v>123</v>
       </c>
-      <c r="T11" s="250"/>
-      <c r="U11" s="250"/>
-      <c r="V11" s="250"/>
-      <c r="W11" s="250"/>
-      <c r="X11" s="250"/>
-      <c r="Y11" s="250"/>
-      <c r="Z11" s="250"/>
-      <c r="AA11" s="250"/>
-      <c r="AB11" s="250"/>
-      <c r="AC11" s="250"/>
+      <c r="T11" s="253"/>
+      <c r="U11" s="253"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="253"/>
+      <c r="X11" s="253"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
+      <c r="AA11" s="253"/>
+      <c r="AB11" s="253"/>
+      <c r="AC11" s="253"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15470,35 +15512,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="P2" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="245"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
       <c r="AB2" s="85" t="s">
         <v>116</v>
       </c>
@@ -15507,31 +15549,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="P4" s="250" t="s">
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="P4" s="253" t="s">
         <v>117</v>
       </c>
-      <c r="Q4" s="250"/>
-      <c r="R4" s="250"/>
-      <c r="S4" s="250"/>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
+      <c r="Q4" s="253"/>
+      <c r="R4" s="253"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15726,32 +15768,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="251" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="250" t="s">
+      <c r="P9" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="Q9" s="250"/>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
+      <c r="T9" s="253"/>
+      <c r="U9" s="253"/>
+      <c r="V9" s="253"/>
+      <c r="W9" s="253"/>
+      <c r="X9" s="253"/>
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16600,31 +16642,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="248" t="s">
+      <c r="C21" s="251" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="248"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
-      <c r="I21" s="248"/>
-      <c r="J21" s="248"/>
-      <c r="K21" s="248"/>
-      <c r="L21" s="248"/>
-      <c r="P21" s="250" t="s">
+      <c r="D21" s="251"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
+      <c r="I21" s="251"/>
+      <c r="J21" s="251"/>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
+      <c r="P21" s="253" t="s">
         <v>129</v>
       </c>
-      <c r="Q21" s="250"/>
-      <c r="R21" s="250"/>
-      <c r="S21" s="250"/>
-      <c r="T21" s="250"/>
-      <c r="U21" s="250"/>
-      <c r="V21" s="250"/>
-      <c r="W21" s="250"/>
-      <c r="X21" s="250"/>
-      <c r="Y21" s="250"/>
-      <c r="Z21" s="250"/>
+      <c r="Q21" s="253"/>
+      <c r="R21" s="253"/>
+      <c r="S21" s="253"/>
+      <c r="T21" s="253"/>
+      <c r="U21" s="253"/>
+      <c r="V21" s="253"/>
+      <c r="W21" s="253"/>
+      <c r="X21" s="253"/>
+      <c r="Y21" s="253"/>
+      <c r="Z21" s="253"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -17439,60 +17481,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17678,30 +17720,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="251" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="253"/>
-      <c r="Q11" s="253"/>
-      <c r="R11" s="253"/>
-      <c r="S11" s="253"/>
-      <c r="T11" s="253"/>
-      <c r="U11" s="253"/>
-      <c r="V11" s="253"/>
-      <c r="W11" s="253"/>
-      <c r="X11" s="253"/>
-      <c r="Y11" s="253"/>
-      <c r="Z11" s="253"/>
+      <c r="P11" s="256"/>
+      <c r="Q11" s="256"/>
+      <c r="R11" s="256"/>
+      <c r="S11" s="256"/>
+      <c r="T11" s="256"/>
+      <c r="U11" s="256"/>
+      <c r="V11" s="256"/>
+      <c r="W11" s="256"/>
+      <c r="X11" s="256"/>
+      <c r="Y11" s="256"/>
+      <c r="Z11" s="256"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17943,18 +17985,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="251" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18167,23 +18209,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="253"/>
-      <c r="C25" s="253"/>
+      <c r="B25" s="256"/>
+      <c r="C25" s="256"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="248" t="s">
+      <c r="C26" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="248"/>
-      <c r="G26" s="248"/>
-      <c r="H26" s="248"/>
-      <c r="I26" s="248"/>
-      <c r="J26" s="248"/>
-      <c r="K26" s="248"/>
-      <c r="L26" s="248"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18375,18 +18417,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="248" t="s">
+      <c r="C33" s="251" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="248"/>
-      <c r="H33" s="248"/>
-      <c r="I33" s="248"/>
-      <c r="J33" s="248"/>
-      <c r="K33" s="248"/>
-      <c r="L33" s="248"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
+      <c r="I33" s="251"/>
+      <c r="J33" s="251"/>
+      <c r="K33" s="251"/>
+      <c r="L33" s="251"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18570,18 +18612,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="248" t="s">
+      <c r="C40" s="251" t="s">
         <v>151</v>
       </c>
-      <c r="D40" s="248"/>
-      <c r="E40" s="248"/>
-      <c r="F40" s="248"/>
-      <c r="G40" s="248"/>
-      <c r="H40" s="248"/>
-      <c r="I40" s="248"/>
-      <c r="J40" s="248"/>
-      <c r="K40" s="248"/>
-      <c r="L40" s="248"/>
+      <c r="D40" s="251"/>
+      <c r="E40" s="251"/>
+      <c r="F40" s="251"/>
+      <c r="G40" s="251"/>
+      <c r="H40" s="251"/>
+      <c r="I40" s="251"/>
+      <c r="J40" s="251"/>
+      <c r="K40" s="251"/>
+      <c r="L40" s="251"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18895,60 +18937,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
-      <c r="AA2" s="253"/>
-      <c r="AB2" s="253"/>
-      <c r="AC2" s="253"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256"/>
+      <c r="AB2" s="256"/>
+      <c r="AC2" s="256"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="S4" s="256"/>
+      <c r="T4" s="256"/>
+      <c r="U4" s="256"/>
+      <c r="V4" s="256"/>
+      <c r="W4" s="256"/>
+      <c r="X4" s="256"/>
+      <c r="Y4" s="256"/>
+      <c r="Z4" s="256"/>
+      <c r="AA4" s="256"/>
+      <c r="AB4" s="256"/>
+      <c r="AC4" s="256"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19311,18 +19353,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="248" t="s">
+      <c r="C13" s="251" t="s">
         <v>159</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="248"/>
-      <c r="J13" s="248"/>
-      <c r="K13" s="248"/>
-      <c r="L13" s="248"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="251"/>
+      <c r="K13" s="251"/>
+      <c r="L13" s="251"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19415,18 +19457,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="251" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19618,18 +19660,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="248" t="s">
+      <c r="C25" s="251" t="s">
         <v>263</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="248"/>
-      <c r="I25" s="248"/>
-      <c r="J25" s="248"/>
-      <c r="K25" s="248"/>
-      <c r="L25" s="248"/>
+      <c r="D25" s="251"/>
+      <c r="E25" s="251"/>
+      <c r="F25" s="251"/>
+      <c r="G25" s="251"/>
+      <c r="H25" s="251"/>
+      <c r="I25" s="251"/>
+      <c r="J25" s="251"/>
+      <c r="K25" s="251"/>
+      <c r="L25" s="251"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19767,18 +19809,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="248" t="s">
+      <c r="C31" s="251" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="251"/>
+      <c r="G31" s="251"/>
+      <c r="H31" s="251"/>
+      <c r="I31" s="251"/>
+      <c r="J31" s="251"/>
+      <c r="K31" s="251"/>
+      <c r="L31" s="251"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -20028,10 +20070,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="245"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20048,7 +20090,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>251.67</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20057,7 +20099,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>98151.299999999988</v>
+        <v>99500.7</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20075,7 +20117,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20084,7 +20126,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3869</v>
+        <v>1.3853</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20116,10 +20158,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="245" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="245"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -20127,7 +20169,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.0881620983922781E-2</v>
+        <v>6.010558860119191E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20136,7 +20178,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9391183790160772</v>
+        <v>0.93989441139880814</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20154,7 +20196,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11431050000000001</v>
+        <v>0.11369850000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20163,7 +20205,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11014068733800064</v>
+        <v>0.10961862280413401</v>
       </c>
     </row>
   </sheetData>
@@ -20208,60 +20250,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20414,7 +20456,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>140871.4025875947</v>
+        <v>141692.0351841005</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20468,23 +20510,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7221.4717262407321</v>
+        <v>7224.8693569159122</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7471.3304628371243</v>
+        <v>7478.3624901525</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7470.250194441539</v>
+        <v>7480.7991914992263</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7415.9681155610187</v>
+        <v>7429.9345254562386</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7383.3495839228917</v>
+        <v>7400.734898455069</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20503,14 +20545,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>83547.361330431042</v>
+        <v>84231.930375925789</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="245" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="245"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20526,14 +20568,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11014068733800064</v>
+        <v>0.10961862280413401</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="245" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="245"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20541,7 +20583,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>36962.370083003305</v>
+        <v>37014.700462478948</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20550,7 +20592,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>83547.361330431042</v>
+        <v>84231.930375925789</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20559,7 +20601,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>120509.73141343435</v>
+        <v>121246.63083840473</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20586,7 +20628,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119785.73141343435</v>
+        <v>120522.63083840473</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20604,7 +20646,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>307.14290106008809</v>
+        <v>309.03238676514036</v>
       </c>
     </row>
   </sheetData>
@@ -20647,37 +20689,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20873,23 +20915,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7221.4717262407321</v>
+        <v>7224.8693569159122</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7471.3304628371243</v>
+        <v>7478.3624901525</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7470.250194441539</v>
+        <v>7480.7991914992263</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7415.9681155610187</v>
+        <v>7429.9345254562386</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7383.3495839228917</v>
+        <v>7400.734898455069</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20897,18 +20939,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="251" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21102,18 +21144,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="248" t="s">
+      <c r="C17" s="251" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -21247,18 +21289,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="248" t="s">
+      <c r="C22" s="251" t="s">
         <v>200</v>
       </c>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
-      <c r="J22" s="248"/>
-      <c r="K22" s="248"/>
-      <c r="L22" s="248"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="251"/>
+      <c r="F22" s="251"/>
+      <c r="G22" s="251"/>
+      <c r="H22" s="251"/>
+      <c r="I22" s="251"/>
+      <c r="J22" s="251"/>
+      <c r="K22" s="251"/>
+      <c r="L22" s="251"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21342,18 +21384,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="248" t="s">
+      <c r="C27" s="251" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="E27" s="248"/>
-      <c r="F27" s="248"/>
-      <c r="G27" s="248"/>
-      <c r="H27" s="248"/>
-      <c r="I27" s="248"/>
-      <c r="J27" s="248"/>
-      <c r="K27" s="248"/>
-      <c r="L27" s="248"/>
+      <c r="D27" s="251"/>
+      <c r="E27" s="251"/>
+      <c r="F27" s="251"/>
+      <c r="G27" s="251"/>
+      <c r="H27" s="251"/>
+      <c r="I27" s="251"/>
+      <c r="J27" s="251"/>
+      <c r="K27" s="251"/>
+      <c r="L27" s="251"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21654,10 +21696,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="242" t="s">
+      <c r="B39" s="245" t="s">
         <v>206</v>
       </c>
-      <c r="C39" s="242"/>
+      <c r="C39" s="245"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21675,7 +21717,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11014068733800064</v>
+        <v>0.10961862280413401</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21701,7 +21743,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>128167.2339551703</v>
+        <v>128469.02484962852</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21710,7 +21752,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>157746.25445425071</v>
+        <v>158082.99041365238</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21737,7 +21779,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>157022.25445425071</v>
+        <v>157358.99041365238</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21755,14 +21797,14 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>402.62116526730949</v>
+        <v>403.48459080423686</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="245" t="s">
         <v>211</v>
       </c>
-      <c r="C52" s="242"/>
+      <c r="C52" s="245"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21779,7 +21821,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11431050000000001</v>
+        <v>0.11369850000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21814,14 +21856,14 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>303.78918460561232</v>
+        <v>304.62479417958991</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="242" t="s">
+      <c r="B60" s="245" t="s">
         <v>323</v>
       </c>
-      <c r="C60" s="242"/>
+      <c r="C60" s="245"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21838,7 +21880,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11014068733800064</v>
+        <v>0.10961862280413401</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21864,7 +21906,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>118133.59334276627</v>
+        <v>118411.7583752811</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21873,7 +21915,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>147712.61384184667</v>
+        <v>148025.723939305</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21900,7 +21942,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>146988.61384184667</v>
+        <v>147301.723939305</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21918,14 +21960,14 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>376.8938816457607</v>
+        <v>377.6967280495</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="242" t="s">
+      <c r="B73" s="245" t="s">
         <v>410</v>
       </c>
-      <c r="C73" s="242"/>
+      <c r="C73" s="245"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21942,7 +21984,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11014068733800064</v>
+        <v>0.10961862280413401</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21968,7 +22010,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>117047.70224216465</v>
+        <v>117323.31036495755</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21977,7 +22019,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>146626.72274124506</v>
+        <v>146937.27592898143</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -22004,7 +22046,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>145902.72274124506</v>
+        <v>146213.27592898143</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -22022,7 +22064,7 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>374.10954549037194</v>
+        <v>374.90583571533699</v>
       </c>
     </row>
   </sheetData>
@@ -22075,10 +22117,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="245"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22087,7 +22129,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>307.14290106008809</v>
+        <v>309.03238676514036</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22096,7 +22138,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>402.62116526730949</v>
+        <v>403.48459080423686</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22105,7 +22147,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>303.78918460561232</v>
+        <v>304.62479417958991</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22114,7 +22156,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>376.8938816457607</v>
+        <v>377.6967280495</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22123,7 +22165,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>374.10954549037194</v>
+        <v>374.90583571533699</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22132,7 +22174,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>352.9113356138285</v>
+        <v>353.9488671027608</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22141,7 +22183,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>251.67</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22150,7 +22192,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.40227812458309897</v>
+        <v>0.38732750794795129</v>
       </c>
     </row>
   </sheetData>
@@ -22245,37 +22287,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22388,18 +22430,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="251" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22520,18 +22562,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="248" t="s">
+      <c r="C14" s="251" t="s">
         <v>398</v>
       </c>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="248"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="248"/>
-      <c r="I14" s="248"/>
-      <c r="J14" s="248"/>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="251"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="251"/>
+      <c r="J14" s="251"/>
+      <c r="K14" s="251"/>
+      <c r="L14" s="251"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22621,10 +22663,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="242" t="s">
+      <c r="B20" s="245" t="s">
         <v>400</v>
       </c>
-      <c r="C20" s="242"/>
+      <c r="C20" s="245"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22659,7 +22701,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11431050000000001</v>
+        <v>0.11369850000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22725,60 +22767,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22865,23 +22907,23 @@
       </c>
       <c r="H7" s="128">
         <f>G7*(1+$C$17)</f>
-        <v>8518.1650469429806</v>
+        <v>8601.6764689718348</v>
       </c>
       <c r="I7" s="128">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>8688.5283478818401</v>
+        <v>8859.7267630409897</v>
       </c>
       <c r="J7" s="128">
         <f t="shared" si="0"/>
-        <v>8862.2989148394772</v>
+        <v>9125.5185659322196</v>
       </c>
       <c r="K7" s="128">
         <f t="shared" si="0"/>
-        <v>9039.5448931362662</v>
+        <v>9399.2841229101869</v>
       </c>
       <c r="L7" s="128">
         <f t="shared" si="0"/>
-        <v>9220.3357909989918</v>
+        <v>9681.2626465974936</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22913,7 +22955,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>104334.04475333095</v>
+        <v>110187.90057856063</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22967,23 +23009,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7673.0500414038825</v>
+        <v>7751.9215090626431</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7050.017291951619</v>
+        <v>7195.6967828791694</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6477.5732659920313</v>
+        <v>6679.382928555814</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5951.6102838776715</v>
+        <v>6200.1162156295932</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5468.3541994231209</v>
+        <v>5755.2383952965938</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23002,15 +23044,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>61877.953764616803</v>
+        <v>65503.608284992908</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="254" t="s">
+      <c r="B14" s="257" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="255"/>
+      <c r="C14" s="258"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -23018,7 +23060,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>251.67</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23027,7 +23069,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>241.06570397754533</v>
+        <v>252.85851957947744</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23035,22 +23077,22 @@
         <v>325</v>
       </c>
       <c r="C17" s="158">
-        <v>0.02</v>
-      </c>
-      <c r="E17" s="256" t="s">
+        <v>0.03</v>
+      </c>
+      <c r="E17" s="259" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="256"/>
-      <c r="G17" s="256"/>
-      <c r="H17" s="256"/>
-      <c r="I17" s="256"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="254" t="s">
+      <c r="B19" s="257" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="255"/>
+      <c r="C19" s="258"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -23066,7 +23108,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11014068733800064</v>
+        <v>0.10961862280413401</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23084,7 +23126,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>97899.62999999999</v>
+        <v>99245.569999999992</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23111,15 +23153,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>98623.62999999999</v>
+        <v>99969.569999999992</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="257" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="255"/>
+      <c r="C28" s="258"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -23127,7 +23169,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>32620.605082648326</v>
+        <v>33582.355831423818</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23136,7 +23178,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>61877.953764616803</v>
+        <v>65503.608284992908</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23145,7 +23187,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>94498.558847265129</v>
+        <v>99085.964116416726</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23172,7 +23214,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>93774.558847265129</v>
+        <v>98361.964116416726</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23190,7 +23232,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>241.06570397754533</v>
+        <v>252.85851957947744</v>
       </c>
     </row>
   </sheetData>
@@ -29809,7 +29851,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>251.67</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29880,7 +29922,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>251.67</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31186,7 +31228,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>14.044084821428569</v>
+        <v>14.237165178571427</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31223,7 +31265,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.9368863111282248</v>
+        <v>3.9910112629957641</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31284,7 +31326,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.3219678680720843</v>
+        <v>8.4363796327779674</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31345,7 +31387,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>98151.299999999988</v>
+        <v>99500.7</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31406,7 +31448,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>98875.299999999988</v>
+        <v>100224.7</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31443,7 +31485,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.8072891798228721</v>
+        <v>3.8592491336157102</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31480,7 +31522,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>10.6650091683745</v>
+        <v>10.810559810160717</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31615,7 +31657,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>11.616913244170906</v>
+        <v>11.77662445259794</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31652,7 +31694,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>12.024015063024024</v>
+        <v>12.188112728730674</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31689,7 +31731,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>8.6081386593962597E-2</v>
+        <v>8.4913975479569498E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31726,7 +31768,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.1204354909206513E-2</v>
+        <v>7.0238701838278531E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31800,7 +31842,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>9.4700732440629931E-2</v>
+        <v>9.341642822613308E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31837,7 +31879,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.4700732440629931E-2</v>
+        <v>9.341642822613308E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32340,7 +32382,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.3763668947838699E-3</v>
+        <v>-7.2763307192813724E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33661,15 +33703,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>234</v>
       </c>
-      <c r="C4" s="242"/>
-      <c r="E4" s="242" t="s">
+      <c r="C4" s="245"/>
+      <c r="E4" s="245" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33677,7 +33719,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>251.67</v>
+        <v>255.13</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33693,7 +33735,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>98151.299999999988</v>
+        <v>99500.7</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33713,7 +33755,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>98875.299999999988</v>
+        <v>100224.7</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33733,7 +33775,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>14.044084821428569</v>
+        <v>14.237165178571427</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33753,7 +33795,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.9368863111282248</v>
+        <v>3.9910112629957641</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33773,7 +33815,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.3219678680720843</v>
+        <v>8.4363796327779674</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33793,7 +33835,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.8072891798228721</v>
+        <v>3.8592491336157102</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33802,18 +33844,18 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.6650091683745</v>
+        <v>10.810559810160717</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="245" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="242"/>
-      <c r="E15" s="242" t="s">
+      <c r="C15" s="245"/>
+      <c r="E15" s="245" t="s">
         <v>247</v>
       </c>
-      <c r="F15" s="242"/>
+      <c r="F15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33864,14 +33906,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="242" t="s">
+      <c r="B21" s="245" t="s">
         <v>246</v>
       </c>
-      <c r="C21" s="242"/>
-      <c r="E21" s="242" t="s">
+      <c r="C21" s="245"/>
+      <c r="E21" s="245" t="s">
         <v>250</v>
       </c>
-      <c r="F21" s="242"/>
+      <c r="F21" s="245"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33940,14 +33982,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="242" t="s">
+      <c r="B29" s="245" t="s">
         <v>251</v>
       </c>
-      <c r="C29" s="242"/>
-      <c r="E29" s="242" t="s">
+      <c r="C29" s="245"/>
+      <c r="E29" s="245" t="s">
         <v>257</v>
       </c>
-      <c r="F29" s="242"/>
+      <c r="F29" s="245"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34023,14 +34065,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="245" t="s">
         <v>269</v>
       </c>
-      <c r="C37" s="242"/>
-      <c r="E37" s="242" t="s">
+      <c r="C37" s="245"/>
+      <c r="E37" s="245" t="s">
         <v>272</v>
       </c>
-      <c r="F37" s="242"/>
+      <c r="F37" s="245"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34038,7 +34080,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.1204354909206513E-2</v>
+        <v>7.0238701838278531E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -34054,7 +34096,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>8.6081386593962597E-2</v>
+        <v>8.4913975479569498E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -34086,7 +34128,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.4700732440629931E-2</v>
+        <v>9.341642822613308E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34095,18 +34137,18 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.4700732440629931E-2</v>
+        <v>9.341642822613308E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="242" t="s">
+      <c r="B45" s="245" t="s">
         <v>280</v>
       </c>
-      <c r="C45" s="242"/>
-      <c r="E45" s="242" t="s">
+      <c r="C45" s="245"/>
+      <c r="E45" s="245" t="s">
         <v>286</v>
       </c>
-      <c r="F45" s="242"/>
+      <c r="F45" s="245"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34139,18 +34181,18 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.3763668947838699E-3</v>
+        <v>-7.2763307192813724E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="242" t="s">
+      <c r="B51" s="245" t="s">
         <v>283</v>
       </c>
-      <c r="C51" s="242"/>
-      <c r="E51" s="242" t="s">
+      <c r="C51" s="245"/>
+      <c r="E51" s="245" t="s">
         <v>304</v>
       </c>
-      <c r="F51" s="242"/>
+      <c r="F51" s="245"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34318,7 +34360,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>251.67</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34347,7 +34389,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>98151.299999999988</v>
+        <v>99500.7</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34376,7 +34418,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>98875.299999999988</v>
+        <v>100224.7</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34405,7 +34447,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>14.044084821428569</v>
+        <v>14.237165178571427</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34434,7 +34476,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.9368863111282248</v>
+        <v>3.9910112629957641</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34463,7 +34505,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.3219678680720843</v>
+        <v>8.4363796327779674</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34492,7 +34534,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.8072891798228721</v>
+        <v>3.8592491336157102</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34521,7 +34563,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.6650091683745</v>
+        <v>10.810559810160717</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35294,7 +35336,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.1204354909206513E-2</v>
+        <v>7.0238701838278531E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35323,7 +35365,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>8.6081386593962597E-2</v>
+        <v>8.4913975479569498E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35381,7 +35423,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.4700732440629931E-2</v>
+        <v>9.341642822613308E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35410,7 +35452,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.4700732440629931E-2</v>
+        <v>9.341642822613308E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35646,7 +35688,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.3763668947838699E-3</v>
+        <v>-7.2763307192813724E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36132,14 +36174,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="246" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36206,19 +36248,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="249">
         <f>Statement!AA89</f>
         <v>2.1456633423995165E-2</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="250"/>
+      <c r="F7" s="249">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12892451569806279</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -36245,19 +36287,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="249">
         <f>Statement!AA90</f>
         <v>6.7132867132867133E-2</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="250"/>
+      <c r="F9" s="249">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18847352024922118</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="250"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -36284,19 +36326,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="249">
         <f>Statement!AA91</f>
         <v>1.5924106386583092E-2</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="250"/>
+      <c r="F11" s="249">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12177328843995511</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="250"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -36323,19 +36365,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="249">
         <f>Statement!AA95</f>
         <v>-6.0027285129604369E-3</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="250"/>
+      <c r="F13" s="249">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.14812480302552788</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="250"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -36362,19 +36404,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="249">
         <f>Statement!AA96</f>
         <v>5.1831992850759609E-2</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="250"/>
+      <c r="F15" s="249">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>8.3294983893235156E-2</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="250"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -36401,19 +36443,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="249">
         <f>Statement!AA98</f>
         <v>6.7172897196261683E-2</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="250"/>
+      <c r="F17" s="249">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>3.1038374717832957E-2</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="250"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -36440,22 +36482,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="249">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.7412935323383085E-2</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="250"/>
+      <c r="F19" s="249">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.8396226415094338E-2</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="250"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -36482,22 +36524,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="249">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>8.7058823529411786E-2</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="250"/>
+      <c r="F21" s="249">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.10526315789473695</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="250"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36545,22 +36587,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="249">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.5872817955112218E-2</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="250"/>
+      <c r="F25" s="249">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13659126230357452</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="250"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36587,22 +36629,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="249">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.24719101123595505</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="250"/>
+      <c r="F27" s="249">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-1.4705882352941176E-2</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="250"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36629,22 +36671,22 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="246">
+      <c r="C29" s="249">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.7699115044247787E-2</v>
       </c>
-      <c r="D29" s="247"/>
-      <c r="F29" s="246">
+      <c r="D29" s="250"/>
+      <c r="F29" s="249">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.13953488372093023</v>
       </c>
-      <c r="G29" s="247"/>
+      <c r="G29" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="24">

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CC2F26-687D-FC40-9CD3-8C6D36491105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CA00E1-B894-794B-9DB0-E418B4C724BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -12823,7 +12793,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12862,9 +12832,11 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.3853</v>
-    <v>8.0399999999999991</v>
-    <v>3.2538999999999998E-2</v>
+    <v>1.3769</v>
+    <v>-6.73</v>
+    <v>-2.4874999999999998E-2</v>
+    <v>-0.78</v>
+    <v>-2.957E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12872,50 +12844,36 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>256.39</v>
+    <v>271.5</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46315.716707950778</v>
+    <v>46318.957594421096</v>
     <v>4</v>
-    <v>248.5</v>
-    <v>99296596000</v>
+    <v>262.77999999999997</v>
+    <v>102678744000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>249.58</v>
-    <v>14.2369</v>
-    <v>247.09</v>
-    <v>255.13</v>
+    <v>269.11</v>
+    <v>15.0974</v>
+    <v>270.55</v>
+    <v>263.82</v>
+    <v>263.04000000000002</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>2277515</v>
-    <v>4680929</v>
+    <v>3133024</v>
+    <v>4680118</v>
     <v>1997</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12929,28 +12887,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>10</v>
-    <v>50.9</v>
+    <v>7</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12984,6 +12942,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13005,6 +12965,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13014,11 +12975,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13054,7 +13010,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13065,13 +13021,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13172,13 +13131,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13259,6 +13224,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13266,6 +13234,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13788,7 +13759,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>99500.7</v>
+        <v>102889.8</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13796,7 +13767,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>309.03238676514036</v>
+        <v>316.3012528200224</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>421</v>
@@ -13815,7 +13786,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>100224.7</v>
+        <v>103613.8</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13823,7 +13794,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>403.48459080423686</v>
+        <v>406.73529000289335</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>422</v>
@@ -13835,7 +13806,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>255.13</v>
+        <v>263.82</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13850,7 +13821,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>304.62479417958991</v>
+        <v>307.66255821940695</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>423</v>
@@ -13860,16 +13831,16 @@
       <c r="B6" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="206" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="206" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>263.04000000000002</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>14.237165178571427</v>
+        <v>14.722098214285712</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13877,7 +13848,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>377.6967280495</v>
+        <v>380.71930098291159</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>424</v>
@@ -13889,14 +13860,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>8.0399999999999991</v>
+        <v>-6.73</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>3.9910112629957641</v>
+        <v>4.1269493646515212</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13904,23 +13875,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>374.90583571533699</v>
+        <v>377.90371967584122</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.78</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>8.4913975479569498E-2</v>
+        <v>8.2116983413321826E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13928,7 +13899,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>353.9488671027608</v>
+        <v>357.86442434021512</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13937,14 +13908,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.2538999999999998E-2</v>
+        <v>-2.4874999999999998E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>7.0238701838278531E-2</v>
+        <v>6.7925100447274664E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13952,23 +13923,23 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.38732750794795129</v>
+        <v>0.35647192911915371</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-2.957E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>9.341642822613308E-2</v>
+        <v>9.0339372804690066E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14016,7 +13987,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3853</v>
+        <v>1.3769</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -14039,7 +14010,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4680929</v>
+        <v>4680118</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -14053,7 +14024,7 @@
       </c>
       <c r="I14" s="240">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>252.85851957947744</v>
+        <v>258.56734345445233</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14062,7 +14033,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.2763307192813724E-3</v>
+        <v>-7.0366547510054443E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14095,7 +14066,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.10961862280413401</v>
+        <v>0.1076657797960327</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14117,7 +14088,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.11369850000000001</v>
+        <v>0.11149050000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14185,12 +14156,12 @@
       <c r="C26" s="168">
         <v>0.21</v>
       </c>
-      <c r="E26" s="183" t="e" vm="5">
+      <c r="E26" s="183" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14205,7 +14176,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20090,7 +20061,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>255.13</v>
+        <v>263.82</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20099,7 +20070,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>99500.7</v>
+        <v>102889.8</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20117,7 +20088,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20126,7 +20097,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3853</v>
+        <v>1.3769</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20169,7 +20140,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.010558860119191E-2</v>
+        <v>5.8241070251746407E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20178,7 +20149,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93989441139880814</v>
+        <v>0.94175892974825359</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20196,7 +20167,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11369850000000001</v>
+        <v>0.11149050000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20205,7 +20176,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10961862280413401</v>
+        <v>0.1076657797960327</v>
       </c>
     </row>
   </sheetData>
@@ -20456,7 +20427,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>141692.0351841005</v>
+        <v>144848.36711722999</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20510,23 +20481,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7224.8693569159122</v>
+        <v>7237.6069857796447</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7478.3624901525</v>
+        <v>7504.7548222793312</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7480.7991914992263</v>
+        <v>7520.4355083353284</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7429.9345254562386</v>
+        <v>7482.4699092855008</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7400.734898455069</v>
+        <v>7466.2037598534826</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20545,7 +20516,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>84231.930375925789</v>
+        <v>86870.01761427545</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20568,7 +20539,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10961862280413401</v>
+        <v>0.1076657797960327</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20583,7 +20554,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37014.700462478948</v>
+        <v>37211.470985533291</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20592,7 +20563,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>84231.930375925789</v>
+        <v>86870.01761427545</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20601,7 +20572,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>121246.63083840473</v>
+        <v>124081.48859980874</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20628,7 +20599,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>120522.63083840473</v>
+        <v>123357.48859980874</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20646,7 +20617,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>309.03238676514036</v>
+        <v>316.3012528200224</v>
       </c>
     </row>
   </sheetData>
@@ -20915,23 +20886,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7224.8693569159122</v>
+        <v>7237.6069857796447</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7478.3624901525</v>
+        <v>7504.7548222793312</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7480.7991914992263</v>
+        <v>7520.4355083353284</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7429.9345254562386</v>
+        <v>7482.4699092855008</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7400.734898455069</v>
+        <v>7466.2037598534826</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21717,7 +21688,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10961862280413401</v>
+        <v>0.1076657797960327</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21743,7 +21714,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>128469.02484962852</v>
+        <v>129605.4958754486</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21752,7 +21723,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>158082.99041365238</v>
+        <v>159350.7631011284</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21779,7 +21750,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>157358.99041365238</v>
+        <v>158626.7631011284</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21797,7 +21768,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>403.48459080423686</v>
+        <v>406.73529000289335</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21821,7 +21792,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11369850000000001</v>
+        <v>0.11149050000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21856,7 +21827,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>304.62479417958991</v>
+        <v>307.66255821940695</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21880,7 +21851,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10961862280413401</v>
+        <v>0.1076657797960327</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21906,7 +21877,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>118411.7583752811</v>
+        <v>119459.26015765572</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21915,7 +21886,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>148025.723939305</v>
+        <v>149204.52738333552</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21942,7 +21913,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>147301.723939305</v>
+        <v>148480.52738333552</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21960,7 +21931,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>377.6967280495</v>
+        <v>380.71930098291159</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21984,7 +21955,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10961862280413401</v>
+        <v>0.1076657797960327</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -22010,7 +21981,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>117323.31036495755</v>
+        <v>118361.18344789826</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -22019,7 +21990,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>146937.27592898143</v>
+        <v>148106.45067357807</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -22046,7 +22017,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>146213.27592898143</v>
+        <v>147382.45067357807</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -22064,7 +22035,7 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>374.90583571533699</v>
+        <v>377.90371967584122</v>
       </c>
     </row>
   </sheetData>
@@ -22129,7 +22100,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>309.03238676514036</v>
+        <v>316.3012528200224</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22138,7 +22109,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>403.48459080423686</v>
+        <v>406.73529000289335</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22147,7 +22118,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>304.62479417958991</v>
+        <v>307.66255821940695</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22156,7 +22127,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>377.6967280495</v>
+        <v>380.71930098291159</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22165,7 +22136,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>374.90583571533699</v>
+        <v>377.90371967584122</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22174,7 +22145,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>353.9488671027608</v>
+        <v>357.86442434021512</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22183,7 +22154,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>255.13</v>
+        <v>263.82</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22192,7 +22163,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.38732750794795129</v>
+        <v>0.35647192911915371</v>
       </c>
     </row>
   </sheetData>
@@ -22701,7 +22672,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11369850000000001</v>
+        <v>0.11149050000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22955,7 +22926,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>110187.90057856063</v>
+        <v>112642.44637422742</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23009,23 +22980,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7751.9215090626431</v>
+        <v>7765.5883443070352</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7195.6967828791694</v>
+        <v>7221.0915427116588</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6679.382928555814</v>
+        <v>6714.7730160650108</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6200.1162156295932</v>
+        <v>6243.9558327968971</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5755.2383952965938</v>
+        <v>5806.1507587289279</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23044,7 +23015,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>65503.608284992908</v>
+        <v>67555.137109172414</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23060,7 +23031,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>255.13</v>
+        <v>263.82</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23069,7 +23040,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>252.85851957947744</v>
+        <v>258.56734345445233</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23108,7 +23079,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10961862280413401</v>
+        <v>0.1076657797960327</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23126,7 +23097,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>99245.569999999992</v>
+        <v>102625.98</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23153,7 +23124,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>99969.569999999992</v>
+        <v>103349.98</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23169,7 +23140,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>33582.355831423818</v>
+        <v>33751.55949460953</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23178,7 +23149,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>65503.608284992908</v>
+        <v>67555.137109172414</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23187,7 +23158,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>99085.964116416726</v>
+        <v>101306.69660378195</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23214,7 +23185,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>98361.964116416726</v>
+        <v>100582.69660378195</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23232,7 +23203,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>252.85851957947744</v>
+        <v>258.56734345445233</v>
       </c>
     </row>
   </sheetData>
@@ -29851,7 +29822,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>255.13</v>
+        <v>263.82</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29922,7 +29893,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>255.13</v>
+        <v>263.82</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31228,7 +31199,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>14.237165178571427</v>
+        <v>14.722098214285712</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31265,7 +31236,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.9910112629957641</v>
+        <v>4.1269493646515212</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31326,7 +31297,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.4363796327779674</v>
+        <v>8.723731723903434</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31387,7 +31358,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>99500.7</v>
+        <v>102889.8</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31448,7 +31419,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>100224.7</v>
+        <v>103613.8</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31485,7 +31456,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.8592491336157102</v>
+        <v>3.9897497112052371</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31522,7 +31493,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>10.810559810160717</v>
+        <v>11.176119081005286</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31657,7 +31628,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>11.77662445259794</v>
+        <v>12.17774884601728</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31694,7 +31665,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>12.188112728730674</v>
+        <v>12.600253975837836</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31731,7 +31702,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>8.4913975479569498E-2</v>
+        <v>8.2116983413321826E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31768,7 +31739,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>7.0238701838278531E-2</v>
+        <v>6.7925100447274664E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31842,7 +31813,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>9.341642822613308E-2</v>
+        <v>9.0339372804690066E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31879,7 +31850,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.341642822613308E-2</v>
+        <v>9.0339372804690066E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32382,7 +32353,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.2763307192813724E-3</v>
+        <v>-7.0366547510054443E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33719,7 +33690,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>255.13</v>
+        <v>263.82</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33735,7 +33706,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>99500.7</v>
+        <v>102889.8</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33755,7 +33726,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>100224.7</v>
+        <v>103613.8</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33775,7 +33746,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>14.237165178571427</v>
+        <v>14.722098214285712</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33795,7 +33766,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.9910112629957641</v>
+        <v>4.1269493646515212</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33815,7 +33786,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.4363796327779674</v>
+        <v>8.723731723903434</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33835,7 +33806,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.8592491336157102</v>
+        <v>3.9897497112052371</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33844,7 +33815,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.810559810160717</v>
+        <v>11.176119081005286</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34080,7 +34051,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.0238701838278531E-2</v>
+        <v>6.7925100447274664E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -34096,7 +34067,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>8.4913975479569498E-2</v>
+        <v>8.2116983413321826E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -34128,7 +34099,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.341642822613308E-2</v>
+        <v>9.0339372804690066E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34137,7 +34108,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.341642822613308E-2</v>
+        <v>9.0339372804690066E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34181,7 +34152,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.2763307192813724E-3</v>
+        <v>-7.0366547510054443E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34360,7 +34331,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>255.13</v>
+        <v>263.82</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34389,7 +34360,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>99500.7</v>
+        <v>102889.8</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34418,7 +34389,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>100224.7</v>
+        <v>103613.8</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34447,7 +34418,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>14.237165178571427</v>
+        <v>14.722098214285712</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34476,7 +34447,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>3.9910112629957641</v>
+        <v>4.1269493646515212</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34505,7 +34476,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.4363796327779674</v>
+        <v>8.723731723903434</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34534,7 +34505,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.8592491336157102</v>
+        <v>3.9897497112052371</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34563,7 +34534,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.810559810160717</v>
+        <v>11.176119081005286</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35336,7 +35307,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>7.0238701838278531E-2</v>
+        <v>6.7925100447274664E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35365,7 +35336,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>8.4913975479569498E-2</v>
+        <v>8.2116983413321826E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35423,7 +35394,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.341642822613308E-2</v>
+        <v>9.0339372804690066E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35452,7 +35423,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.341642822613308E-2</v>
+        <v>9.0339372804690066E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35688,7 +35659,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.2763307192813724E-3</v>
+        <v>-7.0366547510054443E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CA00E1-B894-794B-9DB0-E418B4C724BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665A4789-E653-8947-980D-2BDBEAE5C7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2386,6 +2386,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2393,12 +2399,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2419,14 +2419,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12832,11 +12832,11 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.3769</v>
-    <v>-6.73</v>
-    <v>-2.4874999999999998E-2</v>
-    <v>-0.78</v>
-    <v>-2.957E-3</v>
+    <v>1.3727</v>
+    <v>-5.2</v>
+    <v>-1.9710000000000002E-2</v>
+    <v>-1.6980999999999999</v>
+    <v>-6.5659999999999998E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12844,26 +12844,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>271.5</v>
+    <v>263.35000000000002</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46318.957594421096</v>
+    <v>46321.855197164063</v>
     <v>4</v>
-    <v>262.77999999999997</v>
-    <v>102678744000</v>
+    <v>254.06</v>
+    <v>100654904000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>269.11</v>
-    <v>15.0974</v>
-    <v>270.55</v>
+    <v>262.88</v>
+    <v>14.431699999999999</v>
     <v>263.82</v>
-    <v>263.04000000000002</v>
+    <v>258.62</v>
+    <v>256.92189999999999</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>3133024</v>
-    <v>4680118</v>
+    <v>3224276</v>
+    <v>4397472</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12887,17 +12887,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>7</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>102889.8</v>
+        <v>100861.8</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13767,7 +13767,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>316.3012528200224</v>
+        <v>316.00046781036622</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>421</v>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>103613.8</v>
+        <v>101585.8</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>406.73529000289335</v>
+        <v>406.60296298128981</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>422</v>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>263.82</v>
+        <v>258.62</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>307.66255821940695</v>
+        <v>307.43982957616237</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>423</v>
@@ -13833,14 +13833,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>263.04000000000002</v>
+        <v>256.92189999999999</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>14.722098214285712</v>
+        <v>14.431919642857142</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13848,7 +13848,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>380.71930098291159</v>
+        <v>380.59626197203596</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>424</v>
@@ -13860,14 +13860,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-6.73</v>
+        <v>-5.2</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>4.1269493646515212</v>
+        <v>4.0456055063534846</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>377.90371967584122</v>
+        <v>377.78168586024623</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13884,14 +13884,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.78</v>
+        <v>-1.6980999999999999</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>8.2116983413321826E-2</v>
+        <v>8.3768086629427585E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>357.86442434021512</v>
+        <v>357.6842416400201</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13908,14 +13908,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.4874999999999998E-2</v>
+        <v>-1.9710000000000002E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>6.7925100447274664E-2</v>
+        <v>6.9290851442270512E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.35647192911915371</v>
+        <v>0.38304942247320428</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13932,14 +13932,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.957E-3</v>
+        <v>-6.5659999999999998E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>9.0339372804690066E-2</v>
+        <v>9.2155801304359033E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3769</v>
+        <v>1.3727</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4680118</v>
+        <v>4397472</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="I14" s="240">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>258.56734345445233</v>
+        <v>258.33114422259411</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.0366547510054443E-3</v>
+        <v>-7.1781387998231241E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.1076657797960327</v>
+        <v>0.10774488665588558</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.11149050000000001</v>
+        <v>0.1116515</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18858,6 +18858,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18865,12 +18871,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19930,16 +19930,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>263.82</v>
+        <v>258.62</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>102889.8</v>
+        <v>100861.8</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20088,7 +20088,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3769</v>
+        <v>1.3727</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.8241070251746407E-2</v>
+        <v>5.9342614768225263E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.94175892974825359</v>
+        <v>0.94065738523177478</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11149050000000001</v>
+        <v>0.1116515</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1076657797960327</v>
+        <v>0.10774488665588558</v>
       </c>
     </row>
   </sheetData>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>144848.36711722999</v>
+        <v>144717.77831696862</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20481,23 +20481,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7237.6069857796447</v>
+        <v>7237.0901299869511</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7504.7548222793312</v>
+        <v>7503.6829935629903</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7520.4355083353284</v>
+        <v>7518.8244635143528</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7482.4699092855008</v>
+        <v>7480.3327699371521</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7466.2037598534826</v>
+        <v>7463.5382382557873</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20516,7 +20516,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>86870.01761427545</v>
+        <v>86760.713850785585</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1076657797960327</v>
+        <v>0.10774488665588558</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37211.470985533291</v>
+        <v>37203.468595257233</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>86870.01761427545</v>
+        <v>86760.713850785585</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>124081.48859980874</v>
+        <v>123964.18244604282</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>123357.48859980874</v>
+        <v>123240.18244604282</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>316.3012528200224</v>
+        <v>316.00046781036622</v>
       </c>
     </row>
   </sheetData>
@@ -20886,23 +20886,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7237.6069857796447</v>
+        <v>7237.0901299869511</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7504.7548222793312</v>
+        <v>7503.6829935629903</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7520.4355083353284</v>
+        <v>7518.8244635143528</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7482.4699092855008</v>
+        <v>7480.3327699371521</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7466.2037598534826</v>
+        <v>7463.5382382557873</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21688,7 +21688,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1076657797960327</v>
+        <v>0.10774488665588558</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>129605.4958754486</v>
+        <v>129559.2252057016</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>159350.7631011284</v>
+        <v>159299.15556270303</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>158626.7631011284</v>
+        <v>158575.15556270303</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>406.73529000289335</v>
+        <v>406.60296298128981</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11149050000000001</v>
+        <v>0.1116515</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>307.66255821940695</v>
+        <v>307.43982957616237</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1076657797960327</v>
+        <v>0.10774488665588558</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21877,7 +21877,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>119459.26015765572</v>
+        <v>119416.6118120926</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>149204.52738333552</v>
+        <v>149156.54216909403</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>148480.52738333552</v>
+        <v>148432.54216909403</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>380.71930098291159</v>
+        <v>380.59626197203596</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21955,7 +21955,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1076657797960327</v>
+        <v>0.10774488665588558</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21981,7 +21981,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>118361.18344789826</v>
+        <v>118318.9271284946</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>148106.45067357807</v>
+        <v>148058.85748549603</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>147382.45067357807</v>
+        <v>147334.85748549603</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -22035,22 +22035,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>377.90371967584122</v>
+        <v>377.78168586024623</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>316.3012528200224</v>
+        <v>316.00046781036622</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>406.73529000289335</v>
+        <v>406.60296298128981</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22118,7 +22118,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>307.66255821940695</v>
+        <v>307.43982957616237</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22127,7 +22127,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>380.71930098291159</v>
+        <v>380.59626197203596</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>377.90371967584122</v>
+        <v>377.78168586024623</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>357.86442434021512</v>
+        <v>357.6842416400201</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>263.82</v>
+        <v>258.62</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.35647192911915371</v>
+        <v>0.38304942247320428</v>
       </c>
     </row>
   </sheetData>
@@ -22672,7 +22672,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11149050000000001</v>
+        <v>0.1116515</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22926,7 +22926,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>112642.44637422742</v>
+        <v>112540.8929896552</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22980,23 +22980,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7765.5883443070352</v>
+        <v>7765.0337840321663</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7221.0915427116588</v>
+        <v>7220.0602267710192</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6714.7730160650108</v>
+        <v>6713.3345620978753</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6243.9558327968971</v>
+        <v>6242.1724372254612</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5806.1507587289279</v>
+        <v>5804.0778953642703</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23015,15 +23015,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>67555.137109172414</v>
+        <v>67470.136197098327</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="257" t="s">
+      <c r="B14" s="258" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="258"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -23031,7 +23031,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>263.82</v>
+        <v>258.62</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>258.56734345445233</v>
+        <v>258.33114422259411</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23050,20 +23050,20 @@
       <c r="C17" s="158">
         <v>0.03</v>
       </c>
-      <c r="E17" s="259" t="s">
+      <c r="E17" s="257" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="257" t="s">
+      <c r="B19" s="258" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="258"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1076657797960327</v>
+        <v>0.10774488665588558</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23097,7 +23097,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>102625.98</v>
+        <v>100603.18000000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23124,15 +23124,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>103349.98</v>
+        <v>101327.18000000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="257" t="s">
+      <c r="B28" s="258" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="258"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>33751.55949460953</v>
+        <v>33744.678905490793</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23149,7 +23149,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>67555.137109172414</v>
+        <v>67470.136197098327</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23158,7 +23158,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>101306.69660378195</v>
+        <v>101214.81510258911</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23185,7 +23185,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>100582.69660378195</v>
+        <v>100490.81510258911</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23203,21 +23203,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>258.56734345445233</v>
+        <v>258.33114422259411</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29822,7 +29822,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>263.82</v>
+        <v>258.62</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29893,7 +29893,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>263.82</v>
+        <v>258.62</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31199,7 +31199,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>14.722098214285712</v>
+        <v>14.431919642857142</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31236,7 +31236,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.1269493646515212</v>
+        <v>4.0456055063534846</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.723731723903434</v>
+        <v>8.5517834070044199</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31358,7 +31358,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>102889.8</v>
+        <v>100861.8</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>103613.8</v>
+        <v>101585.8</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31456,7 +31456,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.9897497112052371</v>
+        <v>3.9116596072391223</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31493,7 +31493,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>11.176119081005286</v>
+        <v>10.957372451731205</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31628,7 +31628,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>12.17774884601728</v>
+        <v>11.937720440288793</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31665,7 +31665,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>12.600253975837836</v>
+        <v>12.353633206567729</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31702,7 +31702,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>8.2116983413321826E-2</v>
+        <v>8.3768086629427585E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31739,7 +31739,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>6.7925100447274664E-2</v>
+        <v>6.9290851442270512E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31813,7 +31813,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>9.0339372804690066E-2</v>
+        <v>9.2155801304359033E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31850,7 +31850,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.0339372804690066E-2</v>
+        <v>9.2155801304359033E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32353,7 +32353,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.0366547510054443E-3</v>
+        <v>-7.1781387998231241E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33690,7 +33690,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>263.82</v>
+        <v>258.62</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33706,7 +33706,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>102889.8</v>
+        <v>100861.8</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33726,7 +33726,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>103613.8</v>
+        <v>101585.8</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33746,7 +33746,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>14.722098214285712</v>
+        <v>14.431919642857142</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33766,7 +33766,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>4.1269493646515212</v>
+        <v>4.0456055063534846</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.723731723903434</v>
+        <v>8.5517834070044199</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33806,7 +33806,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.9897497112052371</v>
+        <v>3.9116596072391223</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>11.176119081005286</v>
+        <v>10.957372451731205</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34051,7 +34051,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>6.7925100447274664E-2</v>
+        <v>6.9290851442270512E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -34067,7 +34067,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>8.2116983413321826E-2</v>
+        <v>8.3768086629427585E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -34099,7 +34099,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.0339372804690066E-2</v>
+        <v>9.2155801304359033E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.0339372804690066E-2</v>
+        <v>9.2155801304359033E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34152,7 +34152,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.0366547510054443E-3</v>
+        <v>-7.1781387998231241E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34331,7 +34331,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>263.82</v>
+        <v>258.62</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34360,7 +34360,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>102889.8</v>
+        <v>100861.8</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34389,7 +34389,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>103613.8</v>
+        <v>101585.8</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>14.722098214285712</v>
+        <v>14.431919642857142</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34447,7 +34447,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>4.1269493646515212</v>
+        <v>4.0456055063534846</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34476,7 +34476,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.723731723903434</v>
+        <v>8.5517834070044199</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34505,7 +34505,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.9897497112052371</v>
+        <v>3.9116596072391223</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>11.176119081005286</v>
+        <v>10.957372451731205</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35307,7 +35307,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>6.7925100447274664E-2</v>
+        <v>6.9290851442270512E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35336,7 +35336,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>8.2116983413321826E-2</v>
+        <v>8.3768086629427585E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35394,7 +35394,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.0339372804690066E-2</v>
+        <v>9.2155801304359033E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35423,7 +35423,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.0339372804690066E-2</v>
+        <v>9.2155801304359033E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35659,7 +35659,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.0366547510054443E-3</v>
+        <v>-7.1781387998231241E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36145,14 +36145,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="248" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36219,19 +36219,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="249">
+      <c r="C7" s="246">
         <f>Statement!AA89</f>
         <v>2.1456633423995165E-2</v>
       </c>
-      <c r="D7" s="250"/>
-      <c r="F7" s="249">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12892451569806279</v>
       </c>
-      <c r="G7" s="250"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -36258,19 +36258,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="249">
+      <c r="C9" s="246">
         <f>Statement!AA90</f>
         <v>6.7132867132867133E-2</v>
       </c>
-      <c r="D9" s="250"/>
-      <c r="F9" s="249">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18847352024922118</v>
       </c>
-      <c r="G9" s="250"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -36297,19 +36297,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="249">
+      <c r="C11" s="246">
         <f>Statement!AA91</f>
         <v>1.5924106386583092E-2</v>
       </c>
-      <c r="D11" s="250"/>
-      <c r="F11" s="249">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12177328843995511</v>
       </c>
-      <c r="G11" s="250"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -36336,19 +36336,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="249">
+      <c r="C13" s="246">
         <f>Statement!AA95</f>
         <v>-6.0027285129604369E-3</v>
       </c>
-      <c r="D13" s="250"/>
-      <c r="F13" s="249">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.14812480302552788</v>
       </c>
-      <c r="G13" s="250"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -36375,19 +36375,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="249">
+      <c r="C15" s="246">
         <f>Statement!AA96</f>
         <v>5.1831992850759609E-2</v>
       </c>
-      <c r="D15" s="250"/>
-      <c r="F15" s="249">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>8.3294983893235156E-2</v>
       </c>
-      <c r="G15" s="250"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -36414,19 +36414,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="249">
+      <c r="C17" s="246">
         <f>Statement!AA98</f>
         <v>6.7172897196261683E-2</v>
       </c>
-      <c r="D17" s="250"/>
-      <c r="F17" s="249">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>3.1038374717832957E-2</v>
       </c>
-      <c r="G17" s="250"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -36453,22 +36453,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.7412935323383085E-2</v>
       </c>
-      <c r="D19" s="250"/>
-      <c r="F19" s="249">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.8396226415094338E-2</v>
       </c>
-      <c r="G19" s="250"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -36495,22 +36495,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="249">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>8.7058823529411786E-2</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="F21" s="249">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.10526315789473695</v>
       </c>
-      <c r="G21" s="250"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36558,22 +36558,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="249">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.5872817955112218E-2</v>
       </c>
-      <c r="D25" s="250"/>
-      <c r="F25" s="249">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13659126230357452</v>
       </c>
-      <c r="G25" s="250"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36600,22 +36600,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="249">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.24719101123595505</v>
       </c>
-      <c r="D27" s="250"/>
-      <c r="F27" s="249">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-1.4705882352941176E-2</v>
       </c>
-      <c r="G27" s="250"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36642,49 +36642,49 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="249">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.7699115044247787E-2</v>
       </c>
-      <c r="D29" s="250"/>
-      <c r="F29" s="249">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.13953488372093023</v>
       </c>
-      <c r="G29" s="250"/>
+      <c r="G29" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665A4789-E653-8947-980D-2BDBEAE5C7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6C77BE-016C-1241-8788-4E88E7C863CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="431">
   <si>
     <t>Ticker</t>
   </si>
@@ -1433,6 +1433,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2386,12 +2398,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2399,6 +2405,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2419,14 +2431,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12832,11 +12844,11 @@
     <v>Powered by Refinitiv</v>
     <v>363.7</v>
     <v>190.12</v>
-    <v>1.3727</v>
-    <v>-5.2</v>
-    <v>-1.9710000000000002E-2</v>
-    <v>-1.6980999999999999</v>
-    <v>-6.5659999999999998E-3</v>
+    <v>1.3817999999999999</v>
+    <v>-10.26</v>
+    <v>-3.9671999999999999E-2</v>
+    <v>-0.71399999999999997</v>
+    <v>-2.875E-3</v>
     <v>USD</v>
     <v>Adobe Inc. is a global technology company. The Company's Solutions enable digital experiences, starting with the first creative spark, to the creation and development of all content and media, to the personalized delivery across every channel. Its segments include Digital Media, Digital Experience, and Publishing and Advertising. The Digital Media segment provides products and services that allow individuals, teams, businesses, and enterprises to create, publish, and promote content, and to work with documents and creative content across different workflows. The Digital Experience segment provides an integrated platform set of products, services and solutions that enable businesses to create, manage, execute, measure, monetize &amp; optimize customer experiences. The Publishing and Advertising segment contains legacy products and services that address diverse market opportunities, including eLearning solutions, technical document publishing, web conferencing, document and forms platforms.</v>
     <v>31360</v>
@@ -12844,26 +12856,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>345 Park Avenue, SAN JOSE, CA, 95110-2704 US</v>
-    <v>263.35000000000002</v>
+    <v>256.83999999999997</v>
     <v>3</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46321.855197164063</v>
+    <v>46322.935889212502</v>
     <v>4</v>
-    <v>254.06</v>
-    <v>100654904000</v>
+    <v>247.79</v>
+    <v>96661712000</v>
     <v>ADOBE INC.</v>
     <v>ADOBE INC.</v>
-    <v>262.88</v>
-    <v>14.431699999999999</v>
-    <v>263.82</v>
+    <v>255.1</v>
+    <v>13.8591</v>
     <v>258.62</v>
-    <v>256.92189999999999</v>
+    <v>248.36</v>
+    <v>247.64599999999999</v>
     <v>389200000</v>
     <v>ADBE</v>
     <v>ADOBE INC. (XNAS:ADBE)</v>
-    <v>3224276</v>
-    <v>4397472</v>
+    <v>4710300</v>
+    <v>4323544</v>
     <v>1997</v>
   </rv>
   <rv s="4">
@@ -12887,17 +12899,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
     <v>7</v>
-    <v>49.55</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
+    <v>50.03</v>
     <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13759,7 +13771,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC153</f>
-        <v>100861.8</v>
+        <v>96860.400000000009</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -13767,7 +13779,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>316.00046781036622</v>
+        <v>315.18931701495205</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>421</v>
@@ -13786,7 +13798,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC154</f>
-        <v>101585.8</v>
+        <v>97584.400000000009</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -13794,7 +13806,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>406.60296298128981</v>
+        <v>406.24517865153035</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>422</v>
@@ -13806,7 +13818,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>258.62</v>
+        <v>248.36</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>244</v>
@@ -13821,7 +13833,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>307.43982957616237</v>
+        <v>306.90179204873624</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>423</v>
@@ -13833,14 +13845,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>256.92189999999999</v>
+        <v>247.64599999999999</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC150</f>
-        <v>14.431919642857142</v>
+        <v>13.859375</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -13848,7 +13860,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>380.59626197203596</v>
+        <v>380.263589777172</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>424</v>
@@ -13860,14 +13872,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-5.2</v>
+        <v>-10.26</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>202</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC151</f>
-        <v>4.0456055063534846</v>
+        <v>3.8851078167115904</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13875,7 +13887,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>377.78168586024623</v>
+        <v>377.45173142704562</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13884,14 +13896,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.6980999999999999</v>
+        <v>-0.71399999999999997</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC161</f>
-        <v>8.3768086629427585E-2</v>
+        <v>8.722863006966726E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -13899,7 +13911,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>357.6842416400201</v>
+        <v>357.21032178388725</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13908,14 +13920,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.9710000000000002E-2</v>
+        <v>-3.9671999999999999E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>6.9290851442270512E-2</v>
+        <v>7.2153325817361891E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -13923,7 +13935,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.38304942247320428</v>
+        <v>0.43827638018959264</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13932,14 +13944,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-6.5659999999999998E-3</v>
+        <v>-2.875E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>294</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC164</f>
-        <v>9.2155801304359033E-2</v>
+        <v>9.5962849626885699E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13987,7 +13999,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3727</v>
+        <v>1.3817999999999999</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>105</v>
@@ -14010,7 +14022,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>4397472</v>
+        <v>4323544</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>106</v>
@@ -14024,7 +14036,7 @@
       </c>
       <c r="I14" s="240">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>258.33114422259411</v>
+        <v>257.69415373452398</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14033,7 +14045,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC176</f>
-        <v>-7.1781387998231241E-3</v>
+        <v>-7.4746748929387027E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14066,7 +14078,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.10774488665588558</v>
+        <v>0.10795893892663873</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14088,7 +14100,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.1116515</v>
+        <v>0.112041</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14161,7 +14173,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14176,7 +14188,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18858,12 +18870,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18871,6 +18877,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19930,16 +19942,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20061,7 +20073,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>258.62</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20070,7 +20082,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>100861.8</v>
+        <v>96860.400000000009</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20088,7 +20100,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20097,7 +20109,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3727</v>
+        <v>1.3817999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20140,7 +20152,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.9342614768225263E-2</v>
+        <v>6.1642999552427059E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20149,7 +20161,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.94065738523177478</v>
+        <v>0.93835700044757298</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20167,7 +20179,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1116515</v>
+        <v>0.112041</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20176,7 +20188,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10774488665588558</v>
+        <v>0.10795893892663873</v>
       </c>
     </row>
   </sheetData>
@@ -20427,7 +20439,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>144717.77831696862</v>
+        <v>144365.60070494749</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20481,23 +20493,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>7237.0901299869511</v>
+        <v>7235.6919594216515</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>7503.6829935629903</v>
+        <v>7500.7839236169057</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7518.8244635143528</v>
+        <v>7514.4675045669246</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7480.3327699371521</v>
+        <v>7474.5537894785602</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>7463.5382382557873</v>
+        <v>7456.3314272508151</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20516,7 +20528,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>86760.713850785585</v>
+        <v>86466.005031496446</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20539,7 +20551,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10774488665588558</v>
+        <v>0.10795893892663873</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20554,7 +20566,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>37203.468595257233</v>
+        <v>37181.828604334856</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20563,7 +20575,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>86760.713850785585</v>
+        <v>86466.005031496446</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20572,7 +20584,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>123964.18244604282</v>
+        <v>123647.83363583131</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20599,7 +20611,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>123240.18244604282</v>
+        <v>122923.83363583131</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20617,7 +20629,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>316.00046781036622</v>
+        <v>315.18931701495205</v>
       </c>
     </row>
   </sheetData>
@@ -20886,23 +20898,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>7237.0901299869511</v>
+        <v>7235.6919594216515</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>7503.6829935629903</v>
+        <v>7500.7839236169057</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>7518.8244635143528</v>
+        <v>7514.4675045669246</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7480.3327699371521</v>
+        <v>7474.5537894785602</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>7463.5382382557873</v>
+        <v>7456.3314272508151</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21688,7 +21700,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10774488665588558</v>
+        <v>0.10795893892663873</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21714,7 +21726,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>129559.2252057016</v>
+        <v>129434.12249701281</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21723,7 +21735,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>159299.15556270303</v>
+        <v>159159.61967409684</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21750,7 +21762,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>158575.15556270303</v>
+        <v>158435.61967409684</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21768,7 +21780,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>406.60296298128981</v>
+        <v>406.24517865153035</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21792,7 +21804,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1116515</v>
+        <v>0.112041</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21827,7 +21839,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>307.43982957616237</v>
+        <v>306.90179204873624</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21851,7 +21863,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10774488665588558</v>
+        <v>0.10795893892663873</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21877,7 +21889,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>119416.6118120926</v>
+        <v>119301.30283601304</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21886,7 +21898,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>149156.54216909403</v>
+        <v>149026.80001309709</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21913,7 +21925,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>148432.54216909403</v>
+        <v>148302.80001309709</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21931,7 +21943,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>380.59626197203596</v>
+        <v>380.263589777172</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21955,7 +21967,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10774488665588558</v>
+        <v>0.10795893892663873</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21981,7 +21993,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>118318.9271284946</v>
+        <v>118204.67807946375</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21990,7 +22002,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>148058.85748549603</v>
+        <v>147930.17525654778</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -22017,7 +22029,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>147334.85748549603</v>
+        <v>147206.17525654778</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -22035,22 +22047,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>377.78168586024623</v>
+        <v>377.45173142704562</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22100,7 +22112,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>316.00046781036622</v>
+        <v>315.18931701495205</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22109,7 +22121,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>406.60296298128981</v>
+        <v>406.24517865153035</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22118,7 +22130,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>307.43982957616237</v>
+        <v>306.90179204873624</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22127,7 +22139,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>380.59626197203596</v>
+        <v>380.263589777172</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22136,7 +22148,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>377.78168586024623</v>
+        <v>377.45173142704562</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22145,7 +22157,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>357.6842416400201</v>
+        <v>357.21032178388725</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22154,7 +22166,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>258.62</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22163,7 +22175,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.38304942247320428</v>
+        <v>0.43827638018959264</v>
       </c>
     </row>
   </sheetData>
@@ -22672,7 +22684,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1116515</v>
+        <v>0.112041</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22926,7 +22938,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>112540.8929896552</v>
+        <v>112267.01936190357</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22980,23 +22992,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>7765.0337840321663</v>
+        <v>7763.5336173242231</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>7220.0602267710192</v>
+        <v>7217.27073531325</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6713.3345620978753</v>
+        <v>6709.4443631406648</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>6242.1724372254612</v>
+        <v>6237.3500057049187</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>5804.0778953642703</v>
+        <v>5798.4734633757498</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23015,15 +23027,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>67470.136197098327</v>
+        <v>67240.953617871026</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="257" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="258"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -23031,7 +23043,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>258.62</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23040,7 +23052,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>258.33114422259411</v>
+        <v>257.69415373452398</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23050,20 +23062,20 @@
       <c r="C17" s="158">
         <v>0.03</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="259" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="257" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="258"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -23079,7 +23091,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10774488665588558</v>
+        <v>0.10795893892663873</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23097,7 +23109,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>100603.18000000001</v>
+        <v>96612.040000000008</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23124,15 +23136,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>101327.18000000001</v>
+        <v>97336.040000000008</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="257" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="258"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -23140,7 +23152,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>33744.678905490793</v>
+        <v>33726.0721848588</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23149,7 +23161,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>67470.136197098327</v>
+        <v>67240.953617871026</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23158,7 +23170,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>101214.81510258911</v>
+        <v>100967.02580272983</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23185,7 +23197,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>100490.81510258911</v>
+        <v>100243.02580272983</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23203,21 +23215,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>258.33114422259411</v>
+        <v>257.69415373452398</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29822,7 +29834,7 @@
       </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>258.62</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29893,7 +29905,7 @@
       </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>258.62</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31199,7 +31211,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>14.431919642857142</v>
+        <v>13.859375</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31236,7 +31248,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>4.0456055063534846</v>
+        <v>3.8851078167115904</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31297,7 +31309,7 @@
       </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>8.5517834070044199</v>
+        <v>8.2125161509690585</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31358,7 +31370,7 @@
       </c>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>100861.8</v>
+        <v>96860.400000000009</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31419,7 +31431,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>101585.8</v>
+        <v>97584.400000000009</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31456,7 +31468,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="181">
         <f ca="1">AC154/AC5</f>
-        <v>3.9116596072391223</v>
+        <v>3.7575818251829038</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31493,7 +31505,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC154/AC12</f>
-        <v>10.957372451731205</v>
+        <v>10.525768525509655</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31628,7 +31640,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>11.937720440288793</v>
+        <v>11.464125932062966</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31665,7 +31677,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>12.353633206567729</v>
+        <v>11.8670314579694</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31702,7 +31714,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>8.3768086629427585E-2</v>
+        <v>8.722863006966726E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31739,7 +31751,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>6.9290851442270512E-2</v>
+        <v>7.2153325817361891E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31813,7 +31825,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="154">
         <f ca="1">-AC63/AC153</f>
-        <v>9.2155801304359033E-2</v>
+        <v>9.5962849626885699E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31850,7 +31862,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>9.2155801304359033E-2</v>
+        <v>9.5962849626885699E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32353,7 +32365,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-7.1781387998231241E-3</v>
+        <v>-7.4746748929387027E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33657,7 +33669,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -33690,7 +33702,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>258.62</v>
+        <v>248.36</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -33706,7 +33718,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>100861.8</v>
+        <v>96860.400000000009</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33726,7 +33738,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>101585.8</v>
+        <v>97584.400000000009</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -33746,7 +33758,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>14.431919642857142</v>
+        <v>13.859375</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33766,7 +33778,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>4.0456055063534846</v>
+        <v>3.8851078167115904</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33786,7 +33798,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.5517834070044199</v>
+        <v>8.2125161509690585</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33806,7 +33818,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.9116596072391223</v>
+        <v>3.7575818251829038</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33815,7 +33827,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.957372451731205</v>
+        <v>10.525768525509655</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34051,7 +34063,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>6.9290851442270512E-2</v>
+        <v>7.2153325817361891E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -34067,7 +34079,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>8.3768086629427585E-2</v>
+        <v>8.722863006966726E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -34099,7 +34111,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.2155801304359033E-2</v>
+        <v>9.5962849626885699E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34108,7 +34120,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.2155801304359033E-2</v>
+        <v>9.5962849626885699E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34152,7 +34164,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC176</f>
-        <v>-7.1781387998231241E-3</v>
+        <v>-7.4746748929387027E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34206,8 +34218,51 @@
         <v>0.37336814621409919</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="245" t="s">
+        <v>427</v>
+      </c>
+      <c r="C57" s="245"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C58" s="172">
+        <f ca="1">Statement!AC159</f>
+        <v>11.464125932062966</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C59" s="172">
+        <f ca="1">Statement!AC160</f>
+        <v>11.8670314579694</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="C60" s="173">
+        <f>Statement!AC166</f>
+        <v>0.31664042001502146</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="C61" s="173">
+        <f>Statement!AC167</f>
+        <v>0.32533692722371965</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -34232,7 +34287,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I94"/>
+  <dimension ref="B1:I100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -34331,7 +34386,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC116</f>
-        <v>258.62</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34360,7 +34415,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC153</f>
-        <v>100861.8</v>
+        <v>96860.400000000009</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34389,7 +34444,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>101585.8</v>
+        <v>97584.400000000009</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34418,7 +34473,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC150</f>
-        <v>14.431919642857142</v>
+        <v>13.859375</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34447,7 +34502,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>4.0456055063534846</v>
+        <v>3.8851078167115904</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34476,7 +34531,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>8.5517834070044199</v>
+        <v>8.2125161509690585</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34505,7 +34560,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC155</f>
-        <v>3.9116596072391223</v>
+        <v>3.7575818251829038</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34534,7 +34589,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>10.957372451731205</v>
+        <v>10.525768525509655</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35307,7 +35362,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>6.9290851442270512E-2</v>
+        <v>7.2153325817361891E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35336,7 +35391,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC161</f>
-        <v>8.3768086629427585E-2</v>
+        <v>8.722863006966726E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35394,7 +35449,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC164</f>
-        <v>9.2155801304359033E-2</v>
+        <v>9.5962849626885699E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35423,7 +35478,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>9.2155801304359033E-2</v>
+        <v>9.5962849626885699E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35659,7 +35714,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC176</f>
-        <v>-7.1781387998231241E-3</v>
+        <v>-7.4746748929387027E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35996,98 +36051,136 @@
       </c>
       <c r="I85" s="195"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C88" s="172">
+        <f>Statement!M159</f>
+        <v>55.017182177877174</v>
+      </c>
+      <c r="D88" s="172">
+        <f>Statement!N159</f>
+        <v>26.518886836803226</v>
+      </c>
+      <c r="E88" s="172">
+        <f>Statement!O159</f>
+        <v>53.100792496171515</v>
+      </c>
+      <c r="F88" s="172">
+        <f>Statement!P159</f>
+        <v>37.264807947019868</v>
+      </c>
+      <c r="G88" s="172">
+        <f>Statement!Q159</f>
+        <v>16.538336283185838</v>
+      </c>
+      <c r="I88" s="172">
+        <f ca="1">Statement!AC159</f>
+        <v>11.464125932062966</v>
+      </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="C89" s="173">
-        <f>Statement!M197</f>
-        <v>1</v>
-      </c>
-      <c r="D89" s="173">
-        <f>Statement!N197</f>
-        <v>0.1245453921635902</v>
-      </c>
-      <c r="E89" s="173">
-        <f>Statement!O197</f>
-        <v>0.11569441054430071</v>
-      </c>
-      <c r="F89" s="173">
-        <f>Statement!P197</f>
-        <v>0.12234740756945964</v>
-      </c>
-      <c r="G89" s="173">
-        <f>Statement!Q197</f>
-        <v>0.11612494517811023</v>
-      </c>
-      <c r="I89" s="195"/>
+        <v>265</v>
+      </c>
+      <c r="C89" s="172">
+        <f>Statement!M160</f>
+        <v>56.447947476875164</v>
+      </c>
+      <c r="D89" s="172">
+        <f>Statement!N160</f>
+        <v>27.967121726551518</v>
+      </c>
+      <c r="E89" s="172">
+        <f>Statement!O160</f>
+        <v>49.979558824736309</v>
+      </c>
+      <c r="F89" s="172">
+        <f>Statement!P160</f>
+        <v>35.791254971608261</v>
+      </c>
+      <c r="G89" s="172">
+        <f>Statement!Q160</f>
+        <v>15.618610823671041</v>
+      </c>
+      <c r="I89" s="172">
+        <f ca="1">Statement!AC160</f>
+        <v>11.8670314579694</v>
+      </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="20" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="C90" s="173">
-        <f>Statement!M198</f>
-        <v>1</v>
+        <f>Statement!M166</f>
+        <v>0.35704698627509168</v>
       </c>
       <c r="D90" s="173">
-        <f>Statement!N198</f>
-        <v>-4.1441441441441441E-2</v>
+        <f>Statement!N166</f>
+        <v>0.3167809273348739</v>
       </c>
       <c r="E90" s="173">
-        <f>Statement!O198</f>
-        <v>-0.13533834586466165</v>
+        <f>Statement!O166</f>
+        <v>0.28162426955845121</v>
       </c>
       <c r="F90" s="173">
-        <f>Statement!P198</f>
-        <v>-0.16086956521739129</v>
+        <f>Statement!P166</f>
+        <v>0.28949469059800309</v>
       </c>
       <c r="G90" s="173">
-        <f>Statement!Q198</f>
-        <v>-0.15803108808290156</v>
-      </c>
-      <c r="I90" s="195"/>
+        <f>Statement!Q166</f>
+        <v>0.35134596335080465</v>
+      </c>
+      <c r="I90" s="173">
+        <f>Statement!AC166</f>
+        <v>0.31664042001502146</v>
+      </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="C91" s="173">
-        <f>Statement!M199</f>
-        <v>1</v>
+        <f>Statement!M167</f>
+        <v>0.36826100728539751</v>
       </c>
       <c r="D91" s="173">
-        <f>Statement!N199</f>
-        <v>4.4140030441400302E-2</v>
+        <f>Statement!N167</f>
+        <v>0.3382937634897194</v>
       </c>
       <c r="E91" s="173">
-        <f>Statement!O199</f>
-        <v>-3.0612244897959183E-2</v>
+        <f>Statement!O167</f>
+        <v>0.26915348549641921</v>
       </c>
       <c r="F91" s="173">
-        <f>Statement!P199</f>
-        <v>-0.10075187969924812</v>
+        <f>Statement!P167</f>
+        <v>0.28086491513601486</v>
       </c>
       <c r="G91" s="173">
-        <f>Statement!Q199</f>
-        <v>-9.6989966555183951E-2</v>
-      </c>
-      <c r="I91" s="195"/>
+        <f>Statement!Q167</f>
+        <v>0.33278640245698177</v>
+      </c>
+      <c r="I91" s="173">
+        <f>Statement!AC167</f>
+        <v>0.32533692722371965</v>
+      </c>
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
-        <v>313</v>
+        <v>430</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -36121,6 +36214,95 @@
         <v>0</v>
       </c>
       <c r="I94" s="195"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="C98" s="173">
+        <f>Statement!M197</f>
+        <v>1</v>
+      </c>
+      <c r="D98" s="173">
+        <f>Statement!N197</f>
+        <v>0.1245453921635902</v>
+      </c>
+      <c r="E98" s="173">
+        <f>Statement!O197</f>
+        <v>0.11569441054430071</v>
+      </c>
+      <c r="F98" s="173">
+        <f>Statement!P197</f>
+        <v>0.12234740756945964</v>
+      </c>
+      <c r="G98" s="173">
+        <f>Statement!Q197</f>
+        <v>0.11612494517811023</v>
+      </c>
+      <c r="I98" s="195"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="C99" s="173">
+        <f>Statement!M198</f>
+        <v>1</v>
+      </c>
+      <c r="D99" s="173">
+        <f>Statement!N198</f>
+        <v>-4.1441441441441441E-2</v>
+      </c>
+      <c r="E99" s="173">
+        <f>Statement!O198</f>
+        <v>-0.13533834586466165</v>
+      </c>
+      <c r="F99" s="173">
+        <f>Statement!P198</f>
+        <v>-0.16086956521739129</v>
+      </c>
+      <c r="G99" s="173">
+        <f>Statement!Q198</f>
+        <v>-0.15803108808290156</v>
+      </c>
+      <c r="I99" s="195"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="C100" s="173">
+        <f>Statement!M199</f>
+        <v>1</v>
+      </c>
+      <c r="D100" s="173">
+        <f>Statement!N199</f>
+        <v>4.4140030441400302E-2</v>
+      </c>
+      <c r="E100" s="173">
+        <f>Statement!O199</f>
+        <v>-3.0612244897959183E-2</v>
+      </c>
+      <c r="F100" s="173">
+        <f>Statement!P199</f>
+        <v>-0.10075187969924812</v>
+      </c>
+      <c r="G100" s="173">
+        <f>Statement!Q199</f>
+        <v>-9.6989966555183951E-2</v>
+      </c>
+      <c r="I100" s="195"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36145,14 +36327,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="246" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="F3" s="250" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="249"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36219,19 +36401,19 @@
       <c r="B7" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="249">
         <f>Statement!AA89</f>
         <v>2.1456633423995165E-2</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="250"/>
+      <c r="F7" s="249">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12892451569806279</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -36258,19 +36440,19 @@
       <c r="B9" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="249">
         <f>Statement!AA90</f>
         <v>6.7132867132867133E-2</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="250"/>
+      <c r="F9" s="249">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.18847352024922118</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="250"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -36297,19 +36479,19 @@
       <c r="B11" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="249">
         <f>Statement!AA91</f>
         <v>1.5924106386583092E-2</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="250"/>
+      <c r="F11" s="249">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12177328843995511</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="250"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -36336,19 +36518,19 @@
       <c r="B13" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="249">
         <f>Statement!AA95</f>
         <v>-6.0027285129604369E-3</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="250"/>
+      <c r="F13" s="249">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.14812480302552788</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="250"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -36375,19 +36557,19 @@
       <c r="B15" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="249">
         <f>Statement!AA96</f>
         <v>5.1831992850759609E-2</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="250"/>
+      <c r="F15" s="249">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>8.3294983893235156E-2</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="250"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -36414,19 +36596,19 @@
       <c r="B17" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="249">
         <f>Statement!AA98</f>
         <v>6.7172897196261683E-2</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="250"/>
+      <c r="F17" s="249">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>3.1038374717832957E-2</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="250"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -36453,22 +36635,22 @@
       <c r="B19" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="249">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.7412935323383085E-2</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="250"/>
+      <c r="F19" s="249">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-6.8396226415094338E-2</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="250"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -36495,22 +36677,22 @@
       <c r="B21" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="249">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>8.7058823529411786E-2</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="250"/>
+      <c r="F21" s="249">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.10526315789473695</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="250"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36558,22 +36740,22 @@
       <c r="B25" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="249">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>2.5872817955112218E-2</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="250"/>
+      <c r="F25" s="249">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.13659126230357452</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="250"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36600,22 +36782,22 @@
       <c r="B27" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="249">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-0.24719101123595505</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="250"/>
+      <c r="F27" s="249">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-1.4705882352941176E-2</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="250"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36642,49 +36824,49 @@
       <c r="B29" s="204" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="246">
+      <c r="C29" s="249">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.7699115044247787E-2</v>
       </c>
-      <c r="D29" s="247"/>
-      <c r="F29" s="246">
+      <c r="D29" s="250"/>
+      <c r="F29" s="249">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>-0.13953488372093023</v>
       </c>
-      <c r="G29" s="247"/>
+      <c r="G29" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
